--- a/kinetics/fit_velocities.xlsx
+++ b/kinetics/fit_velocities.xlsx
@@ -471,16 +471,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00040455413616455</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05536094556033213</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00218872494545752</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01679518975996502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +511,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>2.207592676080815e-05</v>
+        <v>0.000478302634916474</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02697868962291637</v>
+        <v>-0.05652776651218976</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003677576691569583</v>
+        <v>0.0003364371204552723</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006002088803519163</v>
+        <v>0.2519772311255672</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009918732454877407</v>
+        <v>0.001099771855965461</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0008786850882566213</v>
+        <v>-0.008971080874085678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002796517194686669</v>
+        <v>0.0003657647952952742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6770704705996078</v>
+        <v>0.6438920500322148</v>
       </c>
     </row>
     <row r="6">
@@ -551,16 +551,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.0002011438509456745</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.1296813323035764</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.0004567294155905606</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.03131321635979728</v>
       </c>
     </row>
     <row r="7">
@@ -571,16 +571,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00110015189170905</v>
+        <v>0.001508393386927035</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0260867396401473</v>
+        <v>-0.00151189877664136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003612762192180836</v>
+        <v>0.0005835356216511127</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6071533264410046</v>
+        <v>0.6255318288762433</v>
       </c>
     </row>
     <row r="8">
@@ -591,16 +591,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001978542453918304</v>
+        <v>0.0004744650518994195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1242247965545565</v>
+        <v>0.1229360042798103</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001640877024433273</v>
+        <v>0.0003597557657813422</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4209467644475344</v>
+        <v>0.1365352687142509</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>1.798015359480815e-05</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.04057409333603321</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.793968137682625e-06</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2967977665002407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -651,16 +651,16 @@
         <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>6.580146907607971e-05</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003939417145024646</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.786378003526636e-06</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.850767506110764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -671,16 +671,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001684283121567559</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01314043176273172</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.442091685064504e-06</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9523495428577758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -691,16 +691,16 @@
         <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000105407948438345</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005655674368188868</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.989511879421411e-06</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8393210708448401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -711,16 +711,16 @@
         <v>160</v>
       </c>
       <c r="C14" t="n">
-        <v>3.820712802192529e-05</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.03180624704874339</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3.560077389343129e-06</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3261190314740751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -751,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>5.138259296640837e-05</v>
+        <v>1.785982204787331e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06316358345426834</v>
+        <v>-0.03561647620979188</v>
       </c>
       <c r="E16" t="n">
-        <v>1.856613366881279e-06</v>
+        <v>4.453398800974768e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7629316815319974</v>
+        <v>0.113195328940834</v>
       </c>
     </row>
     <row r="17">
@@ -771,16 +771,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002128822335772937</v>
+        <v>0.0002087560199436228</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.01833711021743595</v>
+        <v>-0.01795821658051203</v>
       </c>
       <c r="E17" t="n">
-        <v>1.860391985209278e-06</v>
+        <v>4.746240406804877e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9821481171283918</v>
+        <v>0.9388510915508703</v>
       </c>
     </row>
     <row r="18">
@@ -791,16 +791,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004247609324866343</v>
+        <v>0.0004252064298049887</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.04418565753966186</v>
+        <v>-0.04524108253038911</v>
       </c>
       <c r="E18" t="n">
-        <v>4.860980756298335e-06</v>
+        <v>4.830444861152769e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9837661660390636</v>
+        <v>0.9839992650574655</v>
       </c>
     </row>
     <row r="19">
@@ -811,16 +811,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0007256801620756466</v>
+        <v>0.0007282179987246794</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07022478521595588</v>
+        <v>-0.0731321694487217</v>
       </c>
       <c r="E19" t="n">
-        <v>5.965308847684862e-06</v>
+        <v>5.858315089204914e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.991557639837634</v>
+        <v>0.991911534803762</v>
       </c>
     </row>
     <row r="20">
@@ -831,16 +831,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.000897930436002321</v>
+        <v>0.0008962771724840513</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002278639874260691</v>
+        <v>0.002995047908387782</v>
       </c>
       <c r="E20" t="n">
-        <v>9.841552410423922e-06</v>
+        <v>9.918642762637691e-06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9850896399431724</v>
+        <v>0.9848036247209059</v>
       </c>
     </row>
     <row r="21">
@@ -851,16 +851,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008305976706377661</v>
+        <v>0.0008255629111637564</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2529280392913571</v>
+        <v>0.2592153703934635</v>
       </c>
       <c r="E21" t="n">
-        <v>1.377738717042347e-05</v>
+        <v>1.349333154548062e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9664940423739194</v>
+        <v>0.9674365020607256</v>
       </c>
     </row>
     <row r="22">
@@ -871,16 +871,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0003085698864542946</v>
+        <v>0.0002932697034450693</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4633877042366994</v>
+        <v>0.4780884632808361</v>
       </c>
       <c r="E22" t="n">
-        <v>2.067505404011238e-05</v>
+        <v>2.067012642947798e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6387075849514779</v>
+        <v>0.6150344571569135</v>
       </c>
     </row>
     <row r="23">
@@ -891,16 +891,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>5.788617140828562e-05</v>
+        <v>6.029795801763322e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05198348973617307</v>
+        <v>-0.05436702801731529</v>
       </c>
       <c r="E23" t="n">
-        <v>3.705636928069713e-06</v>
+        <v>3.687667688445999e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.659477089650455</v>
+        <v>0.6831587757846261</v>
       </c>
     </row>
     <row r="24">
@@ -911,16 +911,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002321808512417102</v>
+        <v>0.0002340085107049614</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03545328492594266</v>
+        <v>-0.03722282324636483</v>
       </c>
       <c r="E24" t="n">
-        <v>4.90801180255446e-06</v>
+        <v>4.90505840341965e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.946698360372256</v>
+        <v>0.947544020521632</v>
       </c>
     </row>
     <row r="25">
@@ -931,16 +931,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000631263885472248</v>
+        <v>0.0006342249354125421</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08548626986712848</v>
+        <v>-0.08881462964274656</v>
       </c>
       <c r="E25" t="n">
-        <v>5.913374779381708e-06</v>
+        <v>5.783247634426094e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9890643646276737</v>
+        <v>0.9896318526124485</v>
       </c>
     </row>
     <row r="26">
@@ -951,16 +951,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001277183524435614</v>
+        <v>0.001296220162453696</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05197442152576937</v>
+        <v>-0.0645252731309145</v>
       </c>
       <c r="E26" t="n">
-        <v>6.536316391845285e-06</v>
+        <v>7.302735100593686e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9967107324764501</v>
+        <v>0.9964576585444301</v>
       </c>
     </row>
     <row r="27">
@@ -971,16 +971,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001988959226406629</v>
+        <v>0.0020328831988604</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.06122239317398437</v>
+        <v>-0.07905705463012147</v>
       </c>
       <c r="E27" t="n">
-        <v>2.252492486248165e-05</v>
+        <v>1.580037380195139e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9921109109746117</v>
+        <v>0.9951306053751406</v>
       </c>
     </row>
     <row r="28">
@@ -991,16 +991,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002326861761781762</v>
+        <v>0.002335400531598719</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08712767445681724</v>
+        <v>-0.09457011908927027</v>
       </c>
       <c r="E28" t="n">
-        <v>2.762641162832023e-05</v>
+        <v>2.649180922918144e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9913359621279403</v>
+        <v>0.9920851782360345</v>
       </c>
     </row>
     <row r="29">
@@ -1011,16 +1011,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001608720148898064</v>
+        <v>0.001571090486478261</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3557950142143778</v>
+        <v>0.374349996204941</v>
       </c>
       <c r="E29" t="n">
-        <v>4.816707023444801e-05</v>
+        <v>4.775135426978585e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9473450345343329</v>
+        <v>0.9458282389316479</v>
       </c>
     </row>
     <row r="30">
@@ -1031,16 +1031,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001557359512386693</v>
+        <v>0.0001704272153634825</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.05962023886449931</v>
+        <v>-0.06683392403166011</v>
       </c>
       <c r="E30" t="n">
-        <v>1.430885758691015e-05</v>
+        <v>8.653868558899004e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6564315380703507</v>
+        <v>0.8254740633360486</v>
       </c>
     </row>
     <row r="31">
@@ -1051,16 +1051,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005704326715591875</v>
+        <v>0.0005863258384838786</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0993583234283375</v>
+        <v>-0.1085232359940234</v>
       </c>
       <c r="E31" t="n">
-        <v>1.478445229768593e-05</v>
+        <v>7.640414537697913e-06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9600172710445466</v>
+        <v>0.9851121677088666</v>
       </c>
     </row>
     <row r="32">
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001473170888715977</v>
+        <v>0.001487240994550972</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.04590010218096319</v>
+        <v>-0.05209869324874161</v>
       </c>
       <c r="E32" t="n">
-        <v>1.329632067030924e-05</v>
+        <v>1.260834493596635e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9949747179764092</v>
+        <v>0.9954213190807712</v>
       </c>
     </row>
     <row r="33">
@@ -1091,16 +1091,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003112981286328555</v>
+        <v>0.003136557019145229</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1220795237807575</v>
+        <v>-0.1338278000200972</v>
       </c>
       <c r="E33" t="n">
-        <v>2.525103477038531e-05</v>
+        <v>2.866600340313802e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9959371670177402</v>
+        <v>0.9953442541689717</v>
       </c>
     </row>
     <row r="34">
@@ -1111,16 +1111,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005133070228910817</v>
+        <v>0.005164683274213436</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07277976940566289</v>
+        <v>-0.0857805892262089</v>
       </c>
       <c r="E34" t="n">
-        <v>2.737890852823443e-05</v>
+        <v>2.957688416213837e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9982392237593557</v>
+        <v>0.9981341307134131</v>
       </c>
     </row>
     <row r="35">
@@ -1131,16 +1131,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005901955093417277</v>
+        <v>0.005891830832750924</v>
       </c>
       <c r="D35" t="n">
-        <v>0.005121083777652524</v>
+        <v>0.002727339536637174</v>
       </c>
       <c r="E35" t="n">
-        <v>9.70071398375188e-05</v>
+        <v>7.751994605327562e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9919604597379778</v>
+        <v>0.9938065768474211</v>
       </c>
     </row>
     <row r="36">
@@ -1151,16 +1151,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005705253774844659</v>
+        <v>0.0057652215976994</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0797123430590414</v>
+        <v>-0.1048495559973901</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001314072377368927</v>
+        <v>0.000120017009781955</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9843342039021774</v>
+        <v>0.9871659123909748</v>
       </c>
     </row>
     <row r="37">
@@ -1171,16 +1171,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00102595876285951</v>
+        <v>0.001098100552301054</v>
       </c>
       <c r="D37" t="n">
-        <v>0.002333602863173259</v>
+        <v>-0.003704113102340589</v>
       </c>
       <c r="E37" t="n">
-        <v>8.646043987561301e-05</v>
+        <v>8.215878731992411e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9095649423886744</v>
+        <v>0.9225362495304232</v>
       </c>
     </row>
     <row r="38">
@@ -1191,16 +1191,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.002210197033083216</v>
+        <v>0.002111442394386372</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05637137827491062</v>
+        <v>0.07200756820683007</v>
       </c>
       <c r="E38" t="n">
-        <v>0.000122746631818973</v>
+        <v>0.0001072672848888687</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9586070993360108</v>
+        <v>0.9651270547951992</v>
       </c>
     </row>
     <row r="39">
@@ -1211,16 +1211,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.005374793666899621</v>
+        <v>0.005309864779760402</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04665673335751375</v>
+        <v>0.05778493681801278</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001436757598461155</v>
+        <v>0.0001363062167551276</v>
       </c>
       <c r="F39" t="n">
-        <v>0.990095139215451</v>
+        <v>0.9908587791390311</v>
       </c>
     </row>
     <row r="40">
@@ -1231,16 +1231,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.009972988471972389</v>
+        <v>0.009886122940502593</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.02077476760704089</v>
+        <v>-0.01755458898130091</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002289866702139264</v>
+        <v>0.0002416494101240257</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9926733713913378</v>
+        <v>0.9917047421436169</v>
       </c>
     </row>
     <row r="41">
@@ -1251,16 +1251,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01701544414391577</v>
+        <v>0.01672856515487804</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1285216483659899</v>
+        <v>0.1665822309957221</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002205238809878187</v>
+        <v>0.0001798853970874118</v>
       </c>
       <c r="F41" t="n">
-        <v>0.997653974936683</v>
+        <v>0.9982685375530441</v>
       </c>
     </row>
     <row r="42">
@@ -1271,16 +1271,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02266560342250378</v>
+        <v>0.02178229184401826</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3526144955146293</v>
+        <v>0.4667254223592683</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0004920789556532591</v>
+        <v>0.0004169971657031811</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9934444874501255</v>
+        <v>0.9948953672152042</v>
       </c>
     </row>
     <row r="43">
@@ -1291,16 +1291,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.02561597951300466</v>
+        <v>0.02415986008531077</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3999097658821769</v>
+        <v>0.5561283192825321</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0006488372489791191</v>
+        <v>0.0008232636006541199</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9910978647101609</v>
+        <v>0.9840039092956276</v>
       </c>
     </row>
     <row r="44">
@@ -1311,16 +1311,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001762413948074568</v>
+        <v>0.00189415084345195</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01342335026444681</v>
+        <v>-0.02345423517109729</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0002097387000416108</v>
+        <v>0.0001943309573332065</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9216799939224994</v>
+        <v>0.9405968304334549</v>
       </c>
     </row>
     <row r="45">
@@ -1331,16 +1331,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.004018346887248028</v>
+        <v>0.003959776405379444</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005988805854920315</v>
+        <v>-0.005651660402169134</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001620501534752195</v>
+        <v>0.0001743428716327566</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9903364200358433</v>
+        <v>0.9885026918953527</v>
       </c>
     </row>
     <row r="46">
@@ -1351,16 +1351,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00885775587149466</v>
+        <v>0.00911553263511417</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.03334820111355152</v>
+        <v>-0.05705080554274033</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0003227668651441137</v>
+        <v>0.0002882535352447337</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9920962077696898</v>
+        <v>0.9930488948746661</v>
       </c>
     </row>
     <row r="47">
@@ -1371,16 +1371,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01768304580982624</v>
+        <v>0.01723067399952703</v>
       </c>
       <c r="D47" t="n">
-        <v>0.05900594188401331</v>
+        <v>0.09323560845379464</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0005830224752495374</v>
+        <v>0.0005183320118346973</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9935198620098215</v>
+        <v>0.9945997838639774</v>
       </c>
     </row>
     <row r="48">
@@ -1391,16 +1391,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02544544042696292</v>
+        <v>0.02295695362902065</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1650838067548952</v>
+        <v>0.3172324373760587</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001318021503089539</v>
+        <v>0.001257044723888447</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9841568829342399</v>
+        <v>0.9823281992253925</v>
       </c>
     </row>
     <row r="49">
@@ -1411,16 +1411,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03825256439971473</v>
+        <v>0.03391835505664999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5307766392998574</v>
+        <v>0.860354049405057</v>
       </c>
       <c r="E49" t="n">
-        <v>0.002964648763695965</v>
+        <v>0.00144665246362715</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9652143281163967</v>
+        <v>0.9892031861240218</v>
       </c>
     </row>
     <row r="50">
@@ -1431,16 +1431,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03743799790642453</v>
+        <v>0.03258927876527163</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6784469493203307</v>
+        <v>1.045753653182488</v>
       </c>
       <c r="E50" t="n">
-        <v>0.002922312076682579</v>
+        <v>0.0005564460082692587</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9647316038290692</v>
+        <v>0.9982538208601266</v>
       </c>
     </row>
     <row r="51">
@@ -1451,16 +1451,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002292236569320348</v>
+        <v>0.002602955416039446</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01667193061120403</v>
+        <v>-0.032667021084142</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0005175561604719982</v>
+        <v>0.002517134442321767</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7657686901755635</v>
+        <v>0.348396637926584</v>
       </c>
     </row>
     <row r="52">
@@ -1471,16 +1471,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.005747302276560035</v>
+        <v>0.006796595050849956</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.006428155149323073</v>
+        <v>-0.03831660190928815</v>
       </c>
       <c r="E52" t="n">
-        <v>0.001560865870484783</v>
+        <v>0.001551658832806882</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8714491024649937</v>
+        <v>0.9055991926690973</v>
       </c>
     </row>
     <row r="53">
@@ -1491,16 +1491,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01023868404562179</v>
+        <v>0.01059476060694278</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.004707477435123786</v>
+        <v>-0.02133002579317989</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0002050454517870353</v>
+        <v>0.0005397331825440457</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9975994020621817</v>
+        <v>0.9922744570958819</v>
       </c>
     </row>
     <row r="54">
@@ -1511,16 +1511,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02676310308295157</v>
+        <v>0.01743958534911457</v>
       </c>
       <c r="D54" t="n">
-        <v>0.08919282355799296</v>
+        <v>0.3747755366013105</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00319558185696926</v>
+        <v>0.002560991338361036</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9722765815049113</v>
+        <v>0.9586537906506466</v>
       </c>
     </row>
     <row r="55">
@@ -1531,16 +1531,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.04732323654130814</v>
+        <v>0.03832872015289975</v>
       </c>
       <c r="D55" t="n">
-        <v>0.09857414539042542</v>
+        <v>0.372433468607366</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003011737924075016</v>
+        <v>0.001488061831749408</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9919645239153858</v>
+        <v>0.9954985213670325</v>
       </c>
     </row>
     <row r="56">
@@ -1551,16 +1551,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.04172089272499374</v>
+        <v>0.05080560003201921</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.1066638101177402</v>
+        <v>-0.4823684941987576</v>
       </c>
       <c r="E56" t="n">
-        <v>0.002177258113564654</v>
+        <v>0.006419894881066486</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9839222714711109</v>
+        <v>0.9690535775972782</v>
       </c>
     </row>
     <row r="57">
@@ -1571,16 +1571,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.06725438605223877</v>
+        <v>0.07841921019065964</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.004384936414043805</v>
+        <v>-0.3907933311735032</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00622986418715259</v>
+        <v>0.0007111157905048245</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9831284038097375</v>
+        <v>0.9998355649883426</v>
       </c>
     </row>
   </sheetData>
@@ -1637,16 +1637,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>2.382420861572343e-05</v>
+        <v>6.209594303830201e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00142314115853995</v>
+        <v>-0.006412673145205544</v>
       </c>
       <c r="E2" t="n">
-        <v>1.562278391437525e-05</v>
+        <v>2.884766245330071e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07194068892401959</v>
+        <v>0.196055004913752</v>
       </c>
     </row>
     <row r="3">
@@ -1657,16 +1657,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>3.320032466103163e-05</v>
+        <v>0.0001257183073095175</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01013127947831866</v>
+        <v>-0.01861712949268713</v>
       </c>
       <c r="E3" t="n">
-        <v>3.827538709729841e-05</v>
+        <v>7.180165638959597e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05100150212100032</v>
+        <v>0.2770445784243408</v>
       </c>
     </row>
     <row r="4">
@@ -1677,16 +1677,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005995496685010061</v>
+        <v>0.0009984601995747884</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06318568385786154</v>
+        <v>-0.1047803916027477</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002773846979366057</v>
+        <v>0.0003035024839455897</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2502066656092082</v>
+        <v>0.4742084980621581</v>
       </c>
     </row>
     <row r="5">
@@ -1697,16 +1697,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001020714374299126</v>
+        <v>0.000326458562780244</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001778909041264638</v>
+        <v>-0.01200685199019024</v>
       </c>
       <c r="E5" t="n">
-        <v>6.534056734135802e-05</v>
+        <v>0.0002780082963968378</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1484338678940179</v>
+        <v>0.2563569728014092</v>
       </c>
     </row>
     <row r="6">
@@ -1717,16 +1717,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001755186484931257</v>
+        <v>0.0001520676920305501</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02795811232660692</v>
+        <v>0.06240977496141587</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006113916856839109</v>
+        <v>0.0001872671434176062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8047165447434651</v>
+        <v>0.07614875367753955</v>
       </c>
     </row>
     <row r="7">
@@ -1737,16 +1737,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>7.592982360567517e-05</v>
+        <v>0.0001421196642303034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07301935699444793</v>
+        <v>0.07107077271207084</v>
       </c>
       <c r="E7" t="n">
-        <v>9.626518593790922e-05</v>
+        <v>0.0001954056569086212</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04254763401646012</v>
+        <v>0.05551213782667042</v>
       </c>
     </row>
     <row r="8">
@@ -1757,16 +1757,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001561048306008007</v>
+        <v>0.0004649420157516727</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2147959595568285</v>
+        <v>0.2156945764300531</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006385467966638506</v>
+        <v>0.0005267056494834522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009862600420885562</v>
+        <v>0.1001671752355073</v>
       </c>
     </row>
     <row r="9">
@@ -1917,16 +1917,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>7.112213733057246e-06</v>
+        <v>2.411881232082187e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0572971328000956</v>
+        <v>-0.05425479219142621</v>
       </c>
       <c r="E16" t="n">
-        <v>1.344611129066174e-06</v>
+        <v>3.614776919342887e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.105189049103874</v>
+        <v>0.003520841783216418</v>
       </c>
     </row>
     <row r="17">
@@ -1937,16 +1937,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>4.580987992056485e-05</v>
+        <v>4.672664280418188e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02475176148126029</v>
+        <v>-0.02576524357955568</v>
       </c>
       <c r="E17" t="n">
-        <v>4.179462055758129e-06</v>
+        <v>4.163952341648628e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4880903979440749</v>
+        <v>0.499854426448087</v>
       </c>
     </row>
     <row r="18">
@@ -1957,16 +1957,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>5.938380911222198e-05</v>
+        <v>6.188118152200374e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07544155268524905</v>
+        <v>-0.07831265593113737</v>
       </c>
       <c r="E18" t="n">
-        <v>4.231228251251504e-06</v>
+        <v>4.08064104168906e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6098725900112486</v>
+        <v>0.6460319128190359</v>
       </c>
     </row>
     <row r="19">
@@ -1977,16 +1977,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>8.489547614818244e-05</v>
+        <v>8.158483334156716e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06512554727209036</v>
+        <v>0.06812193358724206</v>
       </c>
       <c r="E19" t="n">
-        <v>5.436532408102335e-06</v>
+        <v>5.494806372388042e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6593225745605525</v>
+        <v>0.6363132724301142</v>
       </c>
     </row>
     <row r="20">
@@ -1997,16 +1997,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.033180810614429e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.0627236862814774</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>6.510975997369133e-06</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0001998035253734738</v>
       </c>
     </row>
     <row r="21">
@@ -2057,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001138527962372492</v>
+        <v>0.0001178679120737686</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05418569620249103</v>
+        <v>-0.05713984124309128</v>
       </c>
       <c r="E23" t="n">
-        <v>3.622387748159037e-06</v>
+        <v>5.917179917407381e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8868803512027921</v>
+        <v>0.8167935792586754</v>
       </c>
     </row>
     <row r="24">
@@ -2077,16 +2077,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002194608016218715</v>
+        <v>0.0002217476949400288</v>
       </c>
       <c r="D24" t="n">
-        <v>0.009674058623532072</v>
+        <v>0.008841576444053312</v>
       </c>
       <c r="E24" t="n">
-        <v>4.344375813913908e-06</v>
+        <v>6.610358084213259e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9529477406819818</v>
+        <v>0.9229065754859566</v>
       </c>
     </row>
     <row r="25">
@@ -2097,16 +2097,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007718284864527112</v>
+        <v>0.007797272755529897</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.179258750077693</v>
+        <v>-2.245331787826456</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0008562895696737899</v>
+        <v>0.0009973904245682631</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3920259393051599</v>
+        <v>0.3490030208179414</v>
       </c>
     </row>
     <row r="26">
@@ -2117,16 +2117,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0007842167826253947</v>
+        <v>0.0007721726105941707</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1081840487302492</v>
+        <v>0.1152010516155826</v>
       </c>
       <c r="E26" t="n">
-        <v>2.235298011661702e-05</v>
+        <v>2.162514060167383e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9520435418973305</v>
+        <v>0.9536275977592287</v>
       </c>
     </row>
     <row r="27">
@@ -2137,16 +2137,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005459299151155997</v>
+        <v>0.0005222595554624347</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1509938202787462</v>
+        <v>0.1627023554206921</v>
       </c>
       <c r="E27" t="n">
-        <v>2.547939676237555e-05</v>
+        <v>2.51306199864678e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8810180714839072</v>
+        <v>0.8744642642204643</v>
       </c>
     </row>
     <row r="28">
@@ -2157,16 +2157,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003641574810850646</v>
+        <v>0.0003233247855342739</v>
       </c>
       <c r="D28" t="n">
-        <v>0.236236560570168</v>
+        <v>0.2551053734529309</v>
       </c>
       <c r="E28" t="n">
-        <v>3.670407978660341e-05</v>
+        <v>3.756820165193303e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6135507937046042</v>
+        <v>0.5443492241177484</v>
       </c>
     </row>
     <row r="29">
@@ -2197,16 +2197,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000274697600079979</v>
+        <v>0.0002867274857200216</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00228546290548369</v>
+        <v>-0.0045821941585035</v>
       </c>
       <c r="E30" t="n">
-        <v>2.098825976712181e-05</v>
+        <v>1.818077211860912e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8509685591566457</v>
+        <v>0.8828632017335215</v>
       </c>
     </row>
     <row r="31">
@@ -2217,16 +2217,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0007293929549286815</v>
+        <v>0.0007496363205057472</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00601469993649148</v>
+        <v>0.00284158421711378</v>
       </c>
       <c r="E31" t="n">
-        <v>2.931666759722731e-05</v>
+        <v>2.944434728437061e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9537753708572581</v>
+        <v>0.9543568999435621</v>
       </c>
     </row>
     <row r="32">
@@ -2237,16 +2237,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0008561990973374757</v>
+        <v>0.0008655556727159334</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02387725597558643</v>
+        <v>-0.03017576531164468</v>
       </c>
       <c r="E32" t="n">
-        <v>2.189382028726859e-05</v>
+        <v>2.566099939298885e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9238830931927586</v>
+        <v>0.9074768011424375</v>
       </c>
     </row>
     <row r="33">
@@ -2257,16 +2257,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002455657127655252</v>
+        <v>0.002437030902672767</v>
       </c>
       <c r="D33" t="n">
-        <v>0.06694840666629365</v>
+        <v>0.07366674912094495</v>
       </c>
       <c r="E33" t="n">
-        <v>5.041232445062878e-05</v>
+        <v>4.85314512615775e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9875145912422491</v>
+        <v>0.9882426530682312</v>
       </c>
     </row>
     <row r="34">
@@ -2277,16 +2277,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002554696137585798</v>
+        <v>0.002495975548750779</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1025162742812357</v>
+        <v>0.1172384620212398</v>
       </c>
       <c r="E34" t="n">
-        <v>8.24850348824289e-05</v>
+        <v>8.148349526454975e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.969673749668542</v>
+        <v>0.9690178412634881</v>
       </c>
     </row>
     <row r="35">
@@ -2297,16 +2297,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001693242234872524</v>
+        <v>0.001587505497167043</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2942021996098321</v>
+        <v>0.3267654403083639</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001358146958590824</v>
+        <v>0.0001227535583571808</v>
       </c>
       <c r="F35" t="n">
-        <v>0.838216943657637</v>
+        <v>0.8479076075967945</v>
       </c>
     </row>
     <row r="36">
@@ -2317,16 +2317,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001009956733979327</v>
+        <v>0.0008719794750613077</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2202647156769284</v>
+        <v>0.2471417998592124</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001078532978239687</v>
+        <v>0.0001243275685572527</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7450880599703606</v>
+        <v>0.6211647336653245</v>
       </c>
     </row>
     <row r="37">
@@ -2337,16 +2337,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0001288179617990363</v>
+        <v>0.0001521637414711799</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.002659330225052787</v>
+        <v>-0.005751382797838562</v>
       </c>
       <c r="E37" t="n">
-        <v>1.323613875036515e-05</v>
+        <v>1.882703615585702e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.759456370485719</v>
+        <v>0.7655934423725234</v>
       </c>
     </row>
     <row r="38">
@@ -2357,16 +2357,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0003923079225095354</v>
+        <v>0.0004051157036444823</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.008653777772750504</v>
+        <v>-0.0108709992078756</v>
       </c>
       <c r="E38" t="n">
-        <v>1.547104412602726e-05</v>
+        <v>1.991426035954873e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9554238628286393</v>
+        <v>0.9517060921314737</v>
       </c>
     </row>
     <row r="39">
@@ -2377,16 +2377,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0005890041626790145</v>
+        <v>0.0005965366668375799</v>
       </c>
       <c r="D39" t="n">
-        <v>0.003390289212237302</v>
+        <v>0.002590415193054474</v>
       </c>
       <c r="E39" t="n">
-        <v>5.797654823941325e-05</v>
+        <v>5.804087190416274e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8805587463959232</v>
+        <v>0.8829770550589137</v>
       </c>
     </row>
     <row r="40">
@@ -2397,16 +2397,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001167572153099067</v>
+        <v>0.001158969921057227</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02564732923680782</v>
+        <v>0.02840474032368476</v>
       </c>
       <c r="E40" t="n">
-        <v>7.262860785817208e-05</v>
+        <v>7.164900948817428e-05</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9486116725772377</v>
+        <v>0.9492113121152258</v>
       </c>
     </row>
     <row r="41">
@@ -2417,16 +2417,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.002128550541535824</v>
+        <v>0.002169824324658339</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01510200949324719</v>
+        <v>0.007524796643692211</v>
       </c>
       <c r="E41" t="n">
-        <v>9.381376954236971e-05</v>
+        <v>8.289679172795167e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9735247379532616</v>
+        <v>0.9730163897535241</v>
       </c>
     </row>
     <row r="42">
@@ -2437,16 +2437,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.002877488678066769</v>
+        <v>0.002905365855796949</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04602732872169202</v>
+        <v>0.04053299138055666</v>
       </c>
       <c r="E42" t="n">
-        <v>5.00100381953995e-05</v>
+        <v>5.147047277240375e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9910197036323414</v>
+        <v>0.9906724837713394</v>
       </c>
     </row>
     <row r="43">
@@ -2457,16 +2457,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.002935807458581078</v>
+        <v>0.003033476652225692</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1109190239585506</v>
+        <v>0.09877549581390038</v>
       </c>
       <c r="E43" t="n">
-        <v>6.665463990441879e-05</v>
+        <v>0.0002112133026626807</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9847713193173848</v>
+        <v>0.9364420111609991</v>
       </c>
     </row>
     <row r="44">
@@ -2477,16 +2477,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0004652586187150338</v>
+        <v>0.000473446184572259</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.001709563750988623</v>
+        <v>-0.003766435078712882</v>
       </c>
       <c r="E44" t="n">
-        <v>6.09604313062912e-05</v>
+        <v>2.249394257714965e-05</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8062272449650431</v>
+        <v>0.9445636655951232</v>
       </c>
     </row>
     <row r="45">
@@ -2497,16 +2497,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0009096820438722603</v>
+        <v>0.0008647858611495035</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0128171250913075</v>
+        <v>0.01773506651739286</v>
       </c>
       <c r="E45" t="n">
-        <v>8.15043601607992e-05</v>
+        <v>4.900236615642623e-05</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9540480506944901</v>
+        <v>0.9780182660449773</v>
       </c>
     </row>
     <row r="46">
@@ -2517,16 +2517,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.001422047174311796</v>
+        <v>0.001465986781903427</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.006607161996837835</v>
+        <v>-0.01193462296605419</v>
       </c>
       <c r="E46" t="n">
-        <v>6.075739962240614e-05</v>
+        <v>5.374331485776544e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9750805262059302</v>
+        <v>0.9802388613186047</v>
       </c>
     </row>
     <row r="47">
@@ -2537,16 +2537,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003410969672741011</v>
+        <v>0.003293311088063584</v>
       </c>
       <c r="D47" t="n">
-        <v>0.004609953163375008</v>
+        <v>0.00823581351713662</v>
       </c>
       <c r="E47" t="n">
-        <v>8.344200074700834e-05</v>
+        <v>0.0001262549882337805</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9964222633108666</v>
+        <v>0.9912588233840766</v>
       </c>
     </row>
     <row r="48">
@@ -2557,16 +2557,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.004300356456982055</v>
+        <v>0.004275903240217056</v>
       </c>
       <c r="D48" t="n">
-        <v>0.07367797727351966</v>
+        <v>0.06221197342442653</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0003974451363745182</v>
+        <v>7.122919150572444e-05</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9512482101275039</v>
+        <v>0.9936580170705306</v>
       </c>
     </row>
     <row r="49">
@@ -2577,16 +2577,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.005371390684840909</v>
+        <v>0.00551403599678935</v>
       </c>
       <c r="D49" t="n">
-        <v>0.09047999474745005</v>
+        <v>0.07826027581292472</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0001237686424554986</v>
+        <v>0.0001171310463654615</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9926216449751815</v>
+        <v>0.9919431709469207</v>
       </c>
     </row>
     <row r="50">
@@ -2597,16 +2597,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.005423275861708906</v>
+        <v>0.005524046522426835</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1684298218504683</v>
+        <v>0.1614487251982583</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002708987872688307</v>
+        <v>0.0002798064546090868</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9662474096746916</v>
+        <v>0.9653260850288305</v>
       </c>
     </row>
     <row r="51">
@@ -2617,16 +2617,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0007908746643062955</v>
+        <v>0.0009621308384246017</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0005402179470981039</v>
+        <v>-0.01138769339805996</v>
       </c>
       <c r="E51" t="n">
-        <v>4.105903163206155e-05</v>
+        <v>6.196973090674896e-05</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9636383009939862</v>
+        <v>0.9678780731419715</v>
       </c>
     </row>
     <row r="52">
@@ -2637,16 +2637,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002118910401073161</v>
+        <v>0.002090016258288111</v>
       </c>
       <c r="D52" t="n">
-        <v>0.008551280928761444</v>
+        <v>0.01268353915719857</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0003012703109368445</v>
+        <v>0.0001615358175177419</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9611398850203619</v>
+        <v>0.9823946134066297</v>
       </c>
     </row>
     <row r="53">
@@ -2657,16 +2657,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.004287067598712451</v>
+        <v>0.003678597107614001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.00881178310621239</v>
+        <v>-0.002532791536241447</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000516617963161244</v>
+        <v>0.0008675605980701494</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9717762561621692</v>
+        <v>0.8998947400198943</v>
       </c>
     </row>
     <row r="54">
@@ -2677,16 +2677,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.007445611277185945</v>
+        <v>0.006825451738651068</v>
       </c>
       <c r="D54" t="n">
-        <v>0.006263460448803576</v>
+        <v>0.01897597653677519</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0002573555074274554</v>
+        <v>0.0005566342512152093</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9976162553653904</v>
+        <v>0.9868729155975225</v>
       </c>
     </row>
     <row r="55">
@@ -2697,16 +2697,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.007727807473874301</v>
+        <v>0.007605155998573305</v>
       </c>
       <c r="D55" t="n">
-        <v>0.06069264537428681</v>
+        <v>0.07568104947000731</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0005633203090550361</v>
+        <v>0.0003410330407486728</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9691027858763316</v>
+        <v>0.9841679961686117</v>
       </c>
     </row>
     <row r="56">
@@ -2717,16 +2717,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01299371785357671</v>
+        <v>0.01143245536568657</v>
       </c>
       <c r="D56" t="n">
-        <v>0.08087505434038628</v>
+        <v>0.07380289198611356</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0008253247882385495</v>
+        <v>0.0003554448292402543</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9919957120389205</v>
+        <v>0.9866477171511565</v>
       </c>
     </row>
     <row r="57">
@@ -2737,16 +2737,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.01153291958460407</v>
+        <v>0.0140211073006486</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1339016053291051</v>
+        <v>0.05660014895781995</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001460631429758701</v>
+        <v>0.001301114182456645</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9689172497555619</v>
+        <v>0.9830690926269818</v>
       </c>
     </row>
     <row r="58">
@@ -2757,16 +2757,16 @@
         <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>0.001003266142374126</v>
+        <v>0.0007527514859529005</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.008190477567187623</v>
+        <v>-0.008012053459376826</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0003641300675207998</v>
+        <v>0.0005051000250432505</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7914788616690116</v>
+        <v>0.5261785757478664</v>
       </c>
     </row>
     <row r="59">
@@ -2777,16 +2777,16 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00153939718441269</v>
+        <v>0.002126034984225638</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0003441569472821815</v>
+        <v>-0.02003017181792856</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000157990513479088</v>
+        <v>0.0003599573116036422</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9405574768095059</v>
+        <v>0.9457774265454439</v>
       </c>
     </row>
     <row r="60">
@@ -2797,16 +2797,16 @@
         <v>20</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003368180013824296</v>
+        <v>0.00322290658017307</v>
       </c>
       <c r="D60" t="n">
-        <v>0.005090752026033429</v>
+        <v>0.009058173914654327</v>
       </c>
       <c r="E60" t="n">
-        <v>4.797998249801226e-05</v>
+        <v>7.801764588823817e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9995943202248345</v>
+        <v>0.9988293918097556</v>
       </c>
     </row>
     <row r="61">
@@ -2817,16 +2817,16 @@
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>0.004694795481427363</v>
+        <v>0.004746289823830715</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00504376305955212</v>
+        <v>0.001181687379300689</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0002105643739471675</v>
+        <v>0.0002796716640216505</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9880744789486345</v>
+        <v>0.9829358907835242</v>
       </c>
     </row>
     <row r="62">
@@ -2837,16 +2837,16 @@
         <v>80</v>
       </c>
       <c r="C62" t="n">
-        <v>0.01305434134753266</v>
+        <v>0.01513494231336207</v>
       </c>
       <c r="D62" t="n">
-        <v>0.002621238847854257</v>
+        <v>-0.0639798062371324</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0009522373477304717</v>
+        <v>0.0005714398269533462</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9894703658892012</v>
+        <v>0.9971570251343714</v>
       </c>
     </row>
     <row r="63">
@@ -2857,16 +2857,16 @@
         <v>160</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01889718533605814</v>
+        <v>0.01787112767769273</v>
       </c>
       <c r="D63" t="n">
-        <v>0.07078972384510701</v>
+        <v>0.07139505986625982</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004299909440382635</v>
+        <v>0.0004464823741827524</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9989655610013842</v>
+        <v>0.9950314289092821</v>
       </c>
     </row>
     <row r="64">
@@ -2877,16 +2877,16 @@
         <v>320</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02330734567724781</v>
+        <v>0.02764680748071382</v>
       </c>
       <c r="D64" t="n">
-        <v>0.007297867756104859</v>
+        <v>-0.2052811372649292</v>
       </c>
       <c r="E64" t="n">
-        <v>0.001469769573457913</v>
+        <v>0.002824173336857838</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9766963638057252</v>
+        <v>0.9696452371878808</v>
       </c>
     </row>
     <row r="65">
@@ -2897,16 +2897,16 @@
         <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>0.000387252404498048</v>
+        <v>0.0005637197688465659</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00433165072644312</v>
+        <v>-0.001031886090172476</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0002861329635453244</v>
+        <v>0.0002859533014543667</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4780373853901438</v>
+        <v>0.4927912834626165</v>
       </c>
     </row>
     <row r="66">
@@ -2917,16 +2917,16 @@
         <v>10</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0009821435780778178</v>
+        <v>0.0008978360107734975</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.009315946600906e-05</v>
+        <v>-0.0007700486957303021</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0009369574289914481</v>
+        <v>0.0005917662608704247</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3545844433970099</v>
+        <v>0.434169175813046</v>
       </c>
     </row>
     <row r="67">
@@ -2937,16 +2937,16 @@
         <v>20</v>
       </c>
       <c r="C67" t="n">
-        <v>0.002523916168410479</v>
+        <v>0.002178615788120938</v>
       </c>
       <c r="D67" t="n">
-        <v>0.007594400563426897</v>
+        <v>0.01823159514293464</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0001422256991158544</v>
+        <v>0.0001175770634265304</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9936891646028406</v>
+        <v>0.9942084955985089</v>
       </c>
     </row>
     <row r="68">
@@ -2957,16 +2957,16 @@
         <v>40</v>
       </c>
       <c r="C68" t="n">
-        <v>0.005809959355600041</v>
+        <v>0.005426697742977513</v>
       </c>
       <c r="D68" t="n">
-        <v>0.01737653831087016</v>
+        <v>0.0315753248257441</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0003597357063481165</v>
+        <v>0.0002457615064316883</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9923908933523224</v>
+        <v>0.9959148438993308</v>
       </c>
     </row>
     <row r="69">
@@ -2977,16 +2977,16 @@
         <v>80</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01157569379233286</v>
+        <v>0.01239225155307917</v>
       </c>
       <c r="D69" t="n">
-        <v>0.02974451666961153</v>
+        <v>0.01282673692620701</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0006668316553796719</v>
+        <v>0.0009258732744180148</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9934068116053195</v>
+        <v>0.9889589364397617</v>
       </c>
     </row>
     <row r="70">
@@ -2997,16 +2997,16 @@
         <v>160</v>
       </c>
       <c r="C70" t="n">
-        <v>0.02946246081953719</v>
+        <v>0.02067016100889742</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1767343371186675</v>
+        <v>0.4621826998076703</v>
       </c>
       <c r="E70" t="n">
-        <v>0.004527706112385978</v>
+        <v>0.001287346213401399</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9548970477885722</v>
+        <v>0.9847216491781178</v>
       </c>
     </row>
     <row r="71">
@@ -3017,16 +3017,16 @@
         <v>320</v>
       </c>
       <c r="C71" t="n">
-        <v>0.03305640257570239</v>
+        <v>0.03790092854516987</v>
       </c>
       <c r="D71" t="n">
-        <v>0.08296062366337886</v>
+        <v>-0.08720994348729749</v>
       </c>
       <c r="E71" t="n">
-        <v>0.003104751757282923</v>
+        <v>0.001272254596642153</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9826628730676739</v>
+        <v>0.9977514594464972</v>
       </c>
     </row>
     <row r="72">
@@ -3037,16 +3037,16 @@
         <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>0.001135912751817307</v>
+        <v>0.0008584242151243477</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0004695798110111518</v>
+        <v>-0.006037072804737052</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002234981412735392</v>
+        <v>0.0002294273229926866</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9281378262902603</v>
+        <v>0.6666593029726986</v>
       </c>
     </row>
     <row r="73">
@@ -3057,16 +3057,16 @@
         <v>10</v>
       </c>
       <c r="C73" t="n">
-        <v>0.001407866525127713</v>
+        <v>0.001676394625269263</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.01249697286699986</v>
+        <v>-0.02605638173439933</v>
       </c>
       <c r="E73" t="n">
-        <v>7.761379399383096e-05</v>
+        <v>0.0003513289687046589</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9591881121291276</v>
+        <v>0.8835764615344204</v>
       </c>
     </row>
     <row r="74">
@@ -3077,16 +3077,16 @@
         <v>20</v>
       </c>
       <c r="C74" t="n">
-        <v>0.002476006844546777</v>
+        <v>0.003095863290822843</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03464804509625913</v>
+        <v>-0.07222209143291283</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0001340353082516947</v>
+        <v>0.0004707125875367149</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9605904868200996</v>
+        <v>0.9153556573721072</v>
       </c>
     </row>
     <row r="75">
@@ -3097,16 +3097,16 @@
         <v>40</v>
       </c>
       <c r="C75" t="n">
-        <v>0.007467238900995353</v>
+        <v>0.005132557268998183</v>
       </c>
       <c r="D75" t="n">
-        <v>0.01605624732250516</v>
+        <v>0.06373114657094403</v>
       </c>
       <c r="E75" t="n">
-        <v>0.000297748132357331</v>
+        <v>0.0005419225591777818</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9968302194876132</v>
+        <v>0.9373041705430138</v>
       </c>
     </row>
     <row r="76">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0122268764975634</v>
+        <v>0.01196009499089357</v>
       </c>
       <c r="D76" t="n">
-        <v>0.09721665496145915</v>
+        <v>0.1321267101298278</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0009621640616472204</v>
+        <v>0.001623687378793117</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9641759441099554</v>
+        <v>0.9313399970844342</v>
       </c>
     </row>
     <row r="77">
@@ -3137,16 +3137,16 @@
         <v>160</v>
       </c>
       <c r="C77" t="n">
-        <v>0.01805331809704621</v>
+        <v>0.01611936559454548</v>
       </c>
       <c r="D77" t="n">
-        <v>0.03154016861642644</v>
+        <v>0.03375853296378639</v>
       </c>
       <c r="E77" t="n">
-        <v>0.001726493583298468</v>
+        <v>0.0008246738642194321</v>
       </c>
       <c r="F77" t="n">
-        <v>0.982037209386602</v>
+        <v>0.9820079107166423</v>
       </c>
     </row>
     <row r="78">
@@ -3157,16 +3157,16 @@
         <v>320</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03315246432704098</v>
+        <v>0.03356213944304377</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1362466422000176</v>
+        <v>0.1124713587437178</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0009139763843314667</v>
+        <v>0.0007222724083953382</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9984822206222843</v>
+        <v>0.9990745974609391</v>
       </c>
     </row>
     <row r="79">
@@ -3177,16 +3177,16 @@
         <v>5</v>
       </c>
       <c r="C79" t="n">
-        <v>0.000279880398109355</v>
+        <v>0.0004009496087340287</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00107333815562346</v>
+        <v>-0.005232962810444958</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0001723495464016834</v>
+        <v>0.0003837801705442652</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3053214495126091</v>
+        <v>0.2667684268824529</v>
       </c>
     </row>
     <row r="80">
@@ -3197,16 +3197,16 @@
         <v>10</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0005109504126800188</v>
+        <v>0.0009570944484226776</v>
       </c>
       <c r="D80" t="n">
-        <v>0.01037299725983249</v>
+        <v>-0.004700443734847196</v>
       </c>
       <c r="E80" t="n">
-        <v>0.000337509058446171</v>
+        <v>0.000467502178710605</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2763981168300562</v>
+        <v>0.5116733229703717</v>
       </c>
     </row>
     <row r="81">
@@ -3217,16 +3217,16 @@
         <v>20</v>
       </c>
       <c r="C81" t="n">
-        <v>0.002421474111853991</v>
+        <v>0.001051816246083653</v>
       </c>
       <c r="D81" t="n">
-        <v>0.01271429558830829</v>
+        <v>0.05142812019430012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0006997283739956431</v>
+        <v>0.0003192348130437325</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8568944054848067</v>
+        <v>0.7307437271986736</v>
       </c>
     </row>
     <row r="82">
@@ -3237,16 +3237,16 @@
         <v>40</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0009021772862781817</v>
+        <v>0.001264553751656187</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.02529149417312004</v>
+        <v>-0.05181048173942288</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0002585263071992269</v>
+        <v>0.000168441120477316</v>
       </c>
       <c r="F82" t="n">
-        <v>0.66992983133322</v>
+        <v>0.9037859510827202</v>
       </c>
     </row>
     <row r="83">
@@ -3257,16 +3257,16 @@
         <v>40</v>
       </c>
       <c r="C83" t="n">
-        <v>0.002296224938564639</v>
+        <v>0.001930064237791411</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.01111156895807989</v>
+        <v>-0.0163323767520718</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004027856392695229</v>
+        <v>0.004076667521451069</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1397842655982954</v>
+        <v>0.1007788625046391</v>
       </c>
     </row>
     <row r="84">
@@ -3277,16 +3277,16 @@
         <v>80</v>
       </c>
       <c r="C84" t="n">
-        <v>0.013794254697523</v>
+        <v>0.009773960567177109</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.004232540190900913</v>
+        <v>0.077119606102658</v>
       </c>
       <c r="E84" t="n">
-        <v>0.001218477547863089</v>
+        <v>0.003465003161321029</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9846346069999948</v>
+        <v>0.7991305706418145</v>
       </c>
     </row>
     <row r="85">
@@ -3297,16 +3297,16 @@
         <v>160</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02996496864412632</v>
+        <v>0.03757252222674497</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.08290977607339234</v>
+        <v>-0.3660034537039223</v>
       </c>
       <c r="E85" t="n">
-        <v>0.002122114045443191</v>
+        <v>0.006704172889795313</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9707864235164139</v>
+        <v>0.9401353964226261</v>
       </c>
     </row>
     <row r="86">
@@ -3317,16 +3317,16 @@
         <v>320</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0006751163377163224</v>
+        <v>8.33476960143616e-06</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1665484740560861</v>
+        <v>0.1898858289401071</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0003849665178418107</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6059477265030937</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3337,16 +3337,16 @@
         <v>5</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0003653162804208759</v>
+        <v>0.0005150329019100256</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.01478405936946857</v>
+        <v>-0.0260128059811548</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0002917939733785146</v>
+        <v>0.0003739113012065337</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2071274091619066</v>
+        <v>0.2750771654279539</v>
       </c>
     </row>
     <row r="88">
@@ -3357,16 +3357,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0001852148337714932</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.5966536199671595</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1.947002152725608e-05</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2626862253081088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3377,16 +3377,16 @@
         <v>20</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0006870908391310865</v>
+        <v>0.0007134529791442296</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1453861228854814</v>
+        <v>-0.1585876392360197</v>
       </c>
       <c r="E89" t="n">
-        <v>3.863116039053958e-05</v>
+        <v>4.40581179655976e-05</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8361258252090673</v>
+        <v>0.8214441552122356</v>
       </c>
     </row>
     <row r="90">
@@ -3397,16 +3397,16 @@
         <v>40</v>
       </c>
       <c r="C90" t="n">
-        <v>0.003286784479549671</v>
+        <v>0.002388618635204971</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1159607802821018</v>
+        <v>0.1803884656743361</v>
       </c>
       <c r="E90" t="n">
-        <v>0.001120985093462844</v>
+        <v>0.0007050628259957393</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5889543234530815</v>
+        <v>0.5892644851571086</v>
       </c>
     </row>
     <row r="91">
@@ -3417,16 +3417,16 @@
         <v>80</v>
       </c>
       <c r="C91" t="n">
-        <v>0.01599335971382894</v>
+        <v>0.005449699757250669</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1158191378105191</v>
+        <v>0.4255333059514934</v>
       </c>
       <c r="E91" t="n">
-        <v>0.004558187991029265</v>
+        <v>0.001891263276840214</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8602478089637235</v>
+        <v>0.6748791459314231</v>
       </c>
     </row>
     <row r="92">
@@ -3437,10 +3437,10 @@
         <v>160</v>
       </c>
       <c r="C92" t="n">
-        <v>1.070147608823855e-05</v>
+        <v>1.070147608823846e-05</v>
       </c>
       <c r="D92" t="n">
-        <v>0.05989367546435512</v>
+        <v>0.05989367546435513</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>320</v>
       </c>
       <c r="C93" t="n">
-        <v>8.334769601436124e-06</v>
+        <v>8.334769601436173e-06</v>
       </c>
       <c r="D93" t="n">
         <v>0.1565467505343628</v>
@@ -3523,16 +3523,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003025460098807991</v>
+        <v>0.0003816205072684881</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003980209301967303</v>
+        <v>-0.2541186855520316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00032307063866559</v>
+        <v>2.910875216952379e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3048257056604491</v>
+        <v>0.6076024630817439</v>
       </c>
     </row>
     <row r="3">
@@ -3543,16 +3543,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>7.928211577857877e-05</v>
+        <v>0.0001438313712653079</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2629654266481374</v>
+        <v>-0.2977256785257062</v>
       </c>
       <c r="E3" t="n">
-        <v>2.731571972712412e-05</v>
+        <v>4.415482350903891e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06266830176146131</v>
+        <v>0.105464436672254</v>
       </c>
     </row>
     <row r="4">
@@ -3563,16 +3563,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>3.881317573842804e-05</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01673338006579603</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008411638814219297</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001063420542775091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3583,16 +3583,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.0001268521211106938</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.07494826695552234</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.0004091183250062147</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.02347053357915767</v>
       </c>
     </row>
     <row r="6">
@@ -3623,16 +3623,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0006729679087543078</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07971843015711198</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003159012118663206</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02218766708158858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3643,16 +3643,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.0001068182457636831</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.08832407144644989</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.0002294981460497821</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.05137671240709708</v>
       </c>
     </row>
     <row r="9">
@@ -3903,16 +3903,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>5.841707073472536e-05</v>
+        <v>5.773190533628757e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02793964636550583</v>
+        <v>0.0278783649908234</v>
       </c>
       <c r="E21" t="n">
-        <v>8.455704873815684e-06</v>
+        <v>8.486476286761009e-06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2747313769421321</v>
+        <v>0.2686250520660254</v>
       </c>
     </row>
     <row r="22">
@@ -3923,16 +3923,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>3.840364797683741e-05</v>
+        <v>4.038422358278781e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08166980414628418</v>
+        <v>0.0792131683703977</v>
       </c>
       <c r="E22" t="n">
-        <v>1.444678408815227e-05</v>
+        <v>1.440644931136145e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05310482179807211</v>
+        <v>0.05870368673624444</v>
       </c>
     </row>
     <row r="23">
@@ -3943,16 +3943,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001061633013937221</v>
+        <v>0.0001181790251041508</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.050447435726363</v>
+        <v>-0.05615165232123705</v>
       </c>
       <c r="E23" t="n">
-        <v>1.063240205293211e-05</v>
+        <v>8.550575506893668e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6165689439346783</v>
+        <v>0.7346408571973584</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003083446262020191</v>
+        <v>0.0003117774276820419</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02436686219595716</v>
+        <v>-0.02632134484047918</v>
       </c>
       <c r="E24" t="n">
-        <v>1.121639840421884e-05</v>
+        <v>1.111499620402569e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9241802321544972</v>
+        <v>0.9269566922364543</v>
       </c>
     </row>
     <row r="25">
@@ -3983,16 +3983,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0005568843463976056</v>
+        <v>0.000556143054319711</v>
       </c>
       <c r="D25" t="n">
-        <v>0.008892111044252138</v>
+        <v>0.009269689321606767</v>
       </c>
       <c r="E25" t="n">
-        <v>1.605947635258048e-05</v>
+        <v>1.60583963862856e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9509668485978031</v>
+        <v>0.9508487634948516</v>
       </c>
     </row>
     <row r="26">
@@ -4003,16 +4003,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00119524503822301</v>
+        <v>0.001185080547867529</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03105000135364278</v>
+        <v>0.03500740777764189</v>
       </c>
       <c r="E26" t="n">
-        <v>2.182279768726024e-05</v>
+        <v>2.227955895049174e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9797505076236224</v>
+        <v>0.9785565307950059</v>
       </c>
     </row>
     <row r="27">
@@ -4023,16 +4023,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001602510586547736</v>
+        <v>0.001583439917352697</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1297331596039857</v>
+        <v>0.139271853738318</v>
       </c>
       <c r="E27" t="n">
-        <v>2.735607700717628e-05</v>
+        <v>2.706611476352178e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9822531635725102</v>
+        <v>0.9822072335727036</v>
       </c>
     </row>
     <row r="28">
@@ -4043,16 +4043,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001649730848031991</v>
+        <v>0.00163216413897797</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1762420858487194</v>
+        <v>0.1856448666209387</v>
       </c>
       <c r="E28" t="n">
-        <v>4.304015868357963e-05</v>
+        <v>4.261199360928302e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9595086621369823</v>
+        <v>0.9594536529315293</v>
       </c>
     </row>
     <row r="29">
@@ -4063,16 +4063,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00123356452966503</v>
+        <v>0.001201327258434666</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3712608610961426</v>
+        <v>0.3885542952162263</v>
       </c>
       <c r="E29" t="n">
-        <v>6.907854173152866e-05</v>
+        <v>6.81593761682471e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.837222254479743</v>
+        <v>0.833624073128851</v>
       </c>
     </row>
     <row r="30">
@@ -4083,16 +4083,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001952804002223989</v>
+        <v>0.0002241860788518645</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.01962067981260433</v>
+        <v>-0.02584009484056495</v>
       </c>
       <c r="E30" t="n">
-        <v>3.787179447859964e-05</v>
+        <v>2.89984697172058e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4698521939855165</v>
+        <v>0.6306761625748066</v>
       </c>
     </row>
     <row r="31">
@@ -4103,16 +4103,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005411625823445241</v>
+        <v>0.0005441688825017279</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01447657274410084</v>
+        <v>-0.01603923218609452</v>
       </c>
       <c r="E31" t="n">
-        <v>3.329720479089532e-05</v>
+        <v>3.312800922857091e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8980089731275368</v>
+        <v>0.8999405014973874</v>
       </c>
     </row>
     <row r="32">
@@ -4123,16 +4123,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001100701160793284</v>
+        <v>0.001126055313693867</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02479855446495194</v>
+        <v>0.02165428640812583</v>
       </c>
       <c r="E32" t="n">
-        <v>4.432764801233139e-05</v>
+        <v>3.412387113298319e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9536020330424777</v>
+        <v>0.9688594720216429</v>
       </c>
     </row>
     <row r="33">
@@ -4143,16 +4143,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002578695304826117</v>
+        <v>0.002595021740906298</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03000896246109297</v>
+        <v>-0.03541557423096076</v>
       </c>
       <c r="E33" t="n">
-        <v>5.319583197736964e-05</v>
+        <v>4.699138813516403e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9873942984107326</v>
+        <v>0.9896158449076077</v>
       </c>
     </row>
     <row r="34">
@@ -4163,16 +4163,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003640070164553211</v>
+        <v>0.003653960126991983</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.04876481875227168</v>
+        <v>-0.05578344249073353</v>
       </c>
       <c r="E34" t="n">
-        <v>7.074424032412329e-05</v>
+        <v>6.9117716968354e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9887955530686745</v>
+        <v>0.9893797332324222</v>
       </c>
     </row>
     <row r="35">
@@ -4183,16 +4183,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003936269330027829</v>
+        <v>0.003894530170857382</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1397340326780001</v>
+        <v>0.1517719847291011</v>
       </c>
       <c r="E35" t="n">
-        <v>7.723375233912523e-05</v>
+        <v>7.476780631677715e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9885822970097361</v>
+        <v>0.9890638435952981</v>
       </c>
     </row>
     <row r="36">
@@ -4203,16 +4203,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003966366430596541</v>
+        <v>0.003784141303998879</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4223668254115965</v>
+        <v>0.469583653550355</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001742125273988591</v>
+        <v>0.0001659196297573013</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9452908694491843</v>
+        <v>0.9454706695503851</v>
       </c>
     </row>
     <row r="37">
@@ -4223,16 +4223,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0002871154520127884</v>
+        <v>0.0003326164730829121</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.01908007298133023</v>
+        <v>-0.0258284904398546</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0001065131438037085</v>
+        <v>8.300979779588571e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3416780218068552</v>
+        <v>0.5008685421563729</v>
       </c>
     </row>
     <row r="38">
@@ -4243,16 +4243,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0007837501118251516</v>
+        <v>0.0008254240914288292</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01219743478585761</v>
+        <v>0.00942465354241627</v>
       </c>
       <c r="E38" t="n">
-        <v>3.676025657790608e-05</v>
+        <v>0.0001047199695042138</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9380890915126661</v>
+        <v>0.80552094706604</v>
       </c>
     </row>
     <row r="39">
@@ -4263,16 +4263,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002065360514877574</v>
+        <v>0.002113602456553173</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.05298736095187762</v>
+        <v>-0.06430186120848441</v>
       </c>
       <c r="E39" t="n">
-        <v>4.944797190357391e-05</v>
+        <v>5.612835500429166e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9830947399910827</v>
+        <v>0.981994693963183</v>
       </c>
     </row>
     <row r="40">
@@ -4283,16 +4283,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003832119075500241</v>
+        <v>0.003843256512152284</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.02001476817256204</v>
+        <v>-0.02628862822433298</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000139777023302188</v>
+        <v>9.109316127423411e-05</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9817145006150801</v>
+        <v>0.9894387500667222</v>
       </c>
     </row>
     <row r="41">
@@ -4303,16 +4303,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.007010183923754107</v>
+        <v>0.007174978077061659</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.105372339891018</v>
+        <v>-0.13669619094186</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002737843280597778</v>
+        <v>0.0002383962520486198</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9790921230003973</v>
+        <v>0.9847796447656758</v>
       </c>
     </row>
     <row r="42">
@@ -4323,16 +4323,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009140497616548705</v>
+        <v>0.009025375676811593</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09124461298845477</v>
+        <v>0.1052101028693226</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0002443552374749726</v>
+        <v>0.0002440165617944454</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9900937794618064</v>
+        <v>0.9898698895580664</v>
       </c>
     </row>
     <row r="43">
@@ -4343,16 +4343,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00852593470255722</v>
+        <v>0.008130233967624301</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2242968767163254</v>
+        <v>0.2669647893432185</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000498526847498899</v>
+        <v>0.0005164098692093357</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9543210976267368</v>
+        <v>0.9465375493183751</v>
       </c>
     </row>
     <row r="44">
@@ -4363,16 +4363,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001779544046283864</v>
+        <v>0.001917664636905432</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6040373573017679</v>
+        <v>-0.6932773395651705</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001899979174196614</v>
+        <v>0.0002185983798510912</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4104553718330192</v>
+        <v>0.4030087946085049</v>
       </c>
     </row>
     <row r="45">
@@ -4383,16 +4383,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.001886390771283367</v>
+        <v>0.00173932844311615</v>
       </c>
       <c r="D45" t="n">
-        <v>0.008428579774468786</v>
+        <v>0.01674719028861182</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0002286462016275311</v>
+        <v>0.0001823682966211965</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9189920467719535</v>
+        <v>0.9285444106611168</v>
       </c>
     </row>
     <row r="46">
@@ -4403,16 +4403,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.006764449774621974</v>
+        <v>0.0069180461531111</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.01918725563390034</v>
+        <v>-0.03239774194657796</v>
       </c>
       <c r="E46" t="n">
-        <v>9.739076891144439e-05</v>
+        <v>0.000209009879388154</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9971063888390801</v>
+        <v>0.9927506861551623</v>
       </c>
     </row>
     <row r="47">
@@ -4423,16 +4423,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003988364956224173</v>
+        <v>0.004247378458311378</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.007473852930137054</v>
+        <v>-0.03666855626697785</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0002262608844507256</v>
+        <v>0.0001363955355467638</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9810558912567907</v>
+        <v>0.9837680356313496</v>
       </c>
     </row>
     <row r="48">
@@ -4443,16 +4443,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01322430664523108</v>
+        <v>0.01314857466793648</v>
       </c>
       <c r="D48" t="n">
-        <v>0.08698020433260878</v>
+        <v>0.105839151171506</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0004051493478466904</v>
+        <v>0.0003237360122700553</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9943998870967204</v>
+        <v>0.995774445683436</v>
       </c>
     </row>
     <row r="49">
@@ -4463,16 +4463,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01434196314468077</v>
+        <v>0.01369003443743263</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1650798171161736</v>
+        <v>0.2085955500177412</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0009435105692509518</v>
+        <v>0.000241438370139</v>
       </c>
       <c r="F49" t="n">
-        <v>0.974689889213161</v>
+        <v>0.9956644466432263</v>
       </c>
     </row>
     <row r="50">
@@ -4483,16 +4483,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02242083742814161</v>
+        <v>0.02032884837792375</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2670648536675293</v>
+        <v>0.3927809618225233</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00128038967046422</v>
+        <v>0.001276812579547218</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9808081872722343</v>
+        <v>0.9768782634327834</v>
       </c>
     </row>
     <row r="51">
@@ -4503,16 +4503,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001258252129250831</v>
+        <v>0.001648682525433455</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.006088136943336118</v>
+        <v>-0.0240467937340505</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0002472858864263836</v>
+        <v>0.000380773748471562</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8118548764923719</v>
+        <v>0.8241554024054543</v>
       </c>
     </row>
     <row r="52">
@@ -4523,16 +4523,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003877890819384896</v>
+        <v>0.003400600292479618</v>
       </c>
       <c r="D52" t="n">
-        <v>0.004893994910489502</v>
+        <v>0.01537504834813463</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0003365650515482842</v>
+        <v>0.0002529940158978533</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9851583253393086</v>
+        <v>0.9783399672409434</v>
       </c>
     </row>
     <row r="53">
@@ -4543,16 +4543,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.007708804706595662</v>
+        <v>0.007592684785139749</v>
       </c>
       <c r="D53" t="n">
-        <v>0.01677996470789395</v>
+        <v>0.02548895881708751</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0003270208055525401</v>
+        <v>0.0004294256529135906</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9893177257908006</v>
+        <v>0.98425784735846</v>
       </c>
     </row>
     <row r="54">
@@ -4563,16 +4563,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01439059335998365</v>
+        <v>0.01369980274435692</v>
       </c>
       <c r="D54" t="n">
-        <v>0.02688263342709823</v>
+        <v>0.05091947393527485</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0008690972602726104</v>
+        <v>0.0003013016050445862</v>
       </c>
       <c r="F54" t="n">
-        <v>0.992758095524752</v>
+        <v>0.9980689443217509</v>
       </c>
     </row>
     <row r="55">
@@ -4583,16 +4583,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.02282163272797898</v>
+        <v>0.0267471601152821</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.05069968814268466</v>
+        <v>-0.2221384956940307</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000979624615810284</v>
+        <v>0.001133180578017999</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9890654170786762</v>
+        <v>0.9946441074136295</v>
       </c>
     </row>
     <row r="56">
@@ -4603,16 +4603,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02546810098245248</v>
+        <v>0.03243148987566799</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.04595004847234674</v>
+        <v>-0.3219004007342123</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001252572298834381</v>
+        <v>0.0021636296402738</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9856944019026791</v>
+        <v>0.9911770608839175</v>
       </c>
     </row>
     <row r="57">
@@ -4623,16 +4623,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03277010088543838</v>
+        <v>0.03075437374378786</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1266263403380211</v>
+        <v>0.1392807494767747</v>
       </c>
       <c r="E57" t="n">
-        <v>0.003925990665577704</v>
+        <v>0.0008241615422339491</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9720950220657318</v>
+        <v>0.9949981435314866</v>
       </c>
     </row>
   </sheetData>
@@ -4709,16 +4709,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007058680758317353</v>
+        <v>1.399188969111606e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02475970760064838</v>
+        <v>0.02165754535300702</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008757703305326392</v>
+        <v>0.000105857787862843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2451778640771581</v>
+        <v>0.001246342669901451</v>
       </c>
     </row>
     <row r="4">
@@ -4729,16 +4729,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008879341876269063</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01289312762669354</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008207127859081993</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3691888209947807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4749,16 +4749,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.000295681711622892</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.0539256417922117</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.0003562726464960944</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.1029761620219898</v>
       </c>
     </row>
     <row r="6">
@@ -4769,16 +4769,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000854909444743813</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03740306202130426</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000505095995211433</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5888823324875655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4789,16 +4789,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0005367673039949095</v>
+        <v>0.0001530275048712075</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07740518179056349</v>
+        <v>0.08007669025126371</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001810345657989377</v>
+        <v>0.0006820525814497987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04210530992968294</v>
+        <v>0.009967420086997135</v>
       </c>
     </row>
     <row r="8">
@@ -4809,16 +4809,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.813513207036181e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.08288682053092582</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3.074852964260057e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0114946496245095</v>
       </c>
     </row>
     <row r="9">
@@ -4829,16 +4829,16 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>2.403630670977865e-05</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08664690878558347</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7.747884774221464e-06</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0388665423059392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4849,16 +4849,16 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>5.894780377828478e-05</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07263048678769703</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>8.550251228237147e-06</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1664654650349521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4869,16 +4869,16 @@
         <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001005835417690604</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0003988057059280958</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.54249003802225e-06</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6732136086571048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4889,16 +4889,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001347378503144823</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04923801644702203</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.157426063982188e-05</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.36281290519397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4909,16 +4909,16 @@
         <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001455069137749235</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1088558536509066</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3.351103682627108e-06</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8879128630647228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4929,16 +4929,16 @@
         <v>160</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001002603865177246</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2183259213857184</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>5.968405746316781e-06</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5424751220558565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4949,16 +4949,16 @@
         <v>320</v>
       </c>
       <c r="C15" t="n">
-        <v>2.346393648982621e-05</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05695112878844712</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>5.917635301060756e-06</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06196513223906699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4969,16 +4969,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003463800868727549</v>
+        <v>0.0003296040140814354</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2363571896585102</v>
+        <v>-0.2292735262600052</v>
       </c>
       <c r="E16" t="n">
-        <v>9.1362433176318e-05</v>
+        <v>9.223473112270818e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1023963728112258</v>
+        <v>0.0920237555441196</v>
       </c>
     </row>
     <row r="17">
@@ -4989,16 +4989,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002628457095716966</v>
+        <v>0.0002647922579523449</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02550743242990919</v>
+        <v>-0.02719702650368974</v>
       </c>
       <c r="E17" t="n">
-        <v>5.757738593520059e-06</v>
+        <v>5.789685247285839e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9429864479890763</v>
+        <v>0.9431845358205895</v>
       </c>
     </row>
     <row r="18">
@@ -5009,16 +5009,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004773359709146446</v>
+        <v>0.00047683214278355</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01584170365218074</v>
+        <v>-0.01583845224947028</v>
       </c>
       <c r="E18" t="n">
-        <v>5.039373098037401e-06</v>
+        <v>5.064723069168582e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9861509921462154</v>
+        <v>0.9859841054757199</v>
       </c>
     </row>
     <row r="19">
@@ -5029,16 +5029,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0008785928718929624</v>
+        <v>0.0008730435938082817</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09563378199727868</v>
+        <v>0.100554532708124</v>
       </c>
       <c r="E19" t="n">
-        <v>8.540812178988862e-06</v>
+        <v>8.67945121581815e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9882333444459968</v>
+        <v>0.9876999115885081</v>
       </c>
     </row>
     <row r="20">
@@ -5049,16 +5049,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00106489050037243</v>
+        <v>0.001058295276653702</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1566216433853278</v>
+        <v>0.16295621422924</v>
       </c>
       <c r="E20" t="n">
-        <v>1.233150954890351e-05</v>
+        <v>1.23306164195152e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9833843844771901</v>
+        <v>0.98318253392891</v>
       </c>
     </row>
     <row r="21">
@@ -5069,16 +5069,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008352099904884476</v>
+        <v>0.0008261192910346995</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2274544506157005</v>
+        <v>0.2359567041279564</v>
       </c>
       <c r="E21" t="n">
-        <v>1.906092535762537e-05</v>
+        <v>1.911757245535773e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9384167111924993</v>
+        <v>0.936789050580468</v>
       </c>
     </row>
     <row r="22">
@@ -5089,16 +5089,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.000428431586544102</v>
+        <v>0.0004128969173520629</v>
       </c>
       <c r="D22" t="n">
-        <v>0.500632576576187</v>
+        <v>0.5160711126309077</v>
       </c>
       <c r="E22" t="n">
-        <v>2.637503362789632e-05</v>
+        <v>2.621083473908525e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6768087523205976</v>
+        <v>0.6632404225909762</v>
       </c>
     </row>
     <row r="23">
@@ -5109,16 +5109,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0002343270428245819</v>
+        <v>0.0001722025680334478</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04415551935441192</v>
+        <v>0.02939867698475011</v>
       </c>
       <c r="E23" t="n">
-        <v>8.647328451764371e-06</v>
+        <v>1.054096378739578e-05</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7552227260308154</v>
+        <v>0.8114822987142869</v>
       </c>
     </row>
     <row r="24">
@@ -5129,16 +5129,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003761888179718919</v>
+        <v>0.0003837187940931769</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.004978411210530942</v>
+        <v>-0.00631343165974052</v>
       </c>
       <c r="E24" t="n">
-        <v>4.724280187612345e-06</v>
+        <v>1.052028977014214e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9805157079816528</v>
+        <v>0.9513717728265446</v>
       </c>
     </row>
     <row r="25">
@@ -5149,16 +5149,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0009517296847824525</v>
+        <v>0.0009464036634520331</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03034205238054988</v>
+        <v>0.03289061818358796</v>
       </c>
       <c r="E25" t="n">
-        <v>1.24672210142826e-05</v>
+        <v>1.247086062759197e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9894729256239529</v>
+        <v>0.989349222015722</v>
       </c>
     </row>
     <row r="26">
@@ -5169,16 +5169,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001936979471988713</v>
+        <v>0.001922470088918773</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1140709143104868</v>
+        <v>0.1220759954049979</v>
       </c>
       <c r="E26" t="n">
-        <v>1.825440679206847e-05</v>
+        <v>1.734226810433011e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9945236372007654</v>
+        <v>0.9949800582816641</v>
       </c>
     </row>
     <row r="27">
@@ -5189,16 +5189,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002846568259417853</v>
+        <v>0.002834229081581685</v>
       </c>
       <c r="D27" t="n">
-        <v>0.054680835233202</v>
+        <v>0.05964918120381291</v>
       </c>
       <c r="E27" t="n">
-        <v>2.744343503787065e-05</v>
+        <v>2.790106688772344e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9942703261270693</v>
+        <v>0.9940274227487573</v>
       </c>
     </row>
     <row r="28">
@@ -5209,16 +5209,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002954356910193798</v>
+        <v>0.002898712527560802</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3168630779095616</v>
+        <v>0.3431052610730703</v>
       </c>
       <c r="E28" t="n">
-        <v>5.260475352421287e-05</v>
+        <v>5.313340028990311e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9807220134702338</v>
+        <v>0.9795937768583034</v>
       </c>
     </row>
     <row r="29">
@@ -5229,16 +5229,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001698768122745412</v>
+        <v>0.001672600903060682</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3152736491388041</v>
+        <v>0.3288169446983868</v>
       </c>
       <c r="E29" t="n">
-        <v>5.016018936394834e-05</v>
+        <v>4.96057049430844e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9487164310993256</v>
+        <v>0.9482858311949376</v>
       </c>
     </row>
     <row r="30">
@@ -5249,16 +5249,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003315392672301953</v>
+        <v>0.0003467753555619704</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.02710954162935972</v>
+        <v>-0.03243906652881531</v>
       </c>
       <c r="E30" t="n">
-        <v>8.430217761566958e-06</v>
+        <v>1.15564747246866e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9614583925433376</v>
+        <v>0.9483896074344957</v>
       </c>
     </row>
     <row r="31">
@@ -5269,16 +5269,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0008457985800794102</v>
+        <v>0.0008675308928499521</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.03808181450994511</v>
+        <v>-0.04466775274990287</v>
       </c>
       <c r="E31" t="n">
-        <v>3.740725081311306e-05</v>
+        <v>2.550736574913968e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9445714220917109</v>
+        <v>0.9690051782541096</v>
       </c>
     </row>
     <row r="32">
@@ -5289,16 +5289,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00170318290547758</v>
+        <v>0.001745596598856768</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0724684621704188</v>
+        <v>-0.08539313713068486</v>
       </c>
       <c r="E32" t="n">
-        <v>4.34720163958141e-05</v>
+        <v>2.108965070079562e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9808304384200394</v>
+        <v>0.9934744038140815</v>
       </c>
     </row>
     <row r="33">
@@ -5309,16 +5309,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003874476743890982</v>
+        <v>0.003882395702543811</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.05921568525371024</v>
+        <v>-0.0650228222729895</v>
       </c>
       <c r="E33" t="n">
-        <v>5.112393127973244e-05</v>
+        <v>4.691720025117606e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9948038571362766</v>
+        <v>0.9954932383585041</v>
       </c>
     </row>
     <row r="34">
@@ -5329,16 +5329,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006017738028470393</v>
+        <v>0.006022235463017628</v>
       </c>
       <c r="D34" t="n">
-        <v>0.07037134712241744</v>
+        <v>0.07258869473603879</v>
       </c>
       <c r="E34" t="n">
-        <v>8.119041343227554e-05</v>
+        <v>8.159522217645689e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9945687596909514</v>
+        <v>0.9945229079416756</v>
       </c>
     </row>
     <row r="35">
@@ -5349,16 +5349,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005502399823520278</v>
+        <v>0.005414733192349747</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1665030774040035</v>
+        <v>0.187846097478731</v>
       </c>
       <c r="E35" t="n">
-        <v>9.718465744255904e-05</v>
+        <v>9.657530104153475e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9907281396783136</v>
+        <v>0.9905468986386179</v>
       </c>
     </row>
     <row r="36">
@@ -5369,16 +5369,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005423152473174367</v>
+        <v>0.00526846354099629</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4709394932111828</v>
+        <v>0.5167055440000137</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001551754947973401</v>
+        <v>0.0001269496607863454</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9760268195632278</v>
+        <v>0.9823188981996667</v>
       </c>
     </row>
     <row r="37">
@@ -5389,16 +5389,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.000879646753834147</v>
+        <v>0.0009481272527492037</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.01223451880932896</v>
+        <v>-0.02121550765544289</v>
       </c>
       <c r="E37" t="n">
-        <v>9.187401882415047e-05</v>
+        <v>5.166300320718931e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8675131110309925</v>
+        <v>0.9439464174325526</v>
       </c>
     </row>
     <row r="38">
@@ -5409,16 +5409,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001311544954860391</v>
+        <v>0.001208238499149463</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05132829098462732</v>
+        <v>0.0666789737240395</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001081201987217719</v>
+        <v>9.372146435336483e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9131230346605573</v>
+        <v>0.9223079172922427</v>
       </c>
     </row>
     <row r="39">
@@ -5429,16 +5429,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003506310555601021</v>
+        <v>0.003407024358545448</v>
       </c>
       <c r="D39" t="n">
-        <v>0.05612625992168263</v>
+        <v>0.07118672276216598</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001730612195863432</v>
+        <v>0.0001493833608070349</v>
       </c>
       <c r="F39" t="n">
-        <v>0.967019147980731</v>
+        <v>0.9719715684830337</v>
       </c>
     </row>
     <row r="40">
@@ -5449,16 +5449,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.006856465632848347</v>
+        <v>0.006525808555291658</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07256592206157542</v>
+        <v>0.1089538073938503</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002263054854138223</v>
+        <v>0.0002481487393181031</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9849774424946618</v>
+        <v>0.9801582611718719</v>
       </c>
     </row>
     <row r="41">
@@ -5469,16 +5469,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0120431640066688</v>
+        <v>0.01185447483118439</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1338746188638102</v>
+        <v>0.164496445260929</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000257813658869609</v>
+        <v>0.0002283179300088704</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9936249854161406</v>
+        <v>0.9948335307457747</v>
       </c>
     </row>
     <row r="42">
@@ -5489,16 +5489,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01578054203905483</v>
+        <v>0.01543743351277951</v>
       </c>
       <c r="D42" t="n">
-        <v>0.08539790635557543</v>
+        <v>0.117962695207807</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0003690923810729367</v>
+        <v>0.0004054112913387799</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9923995219363606</v>
+        <v>0.9904369516658922</v>
       </c>
     </row>
     <row r="43">
@@ -5509,16 +5509,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01594905944815261</v>
+        <v>0.01546506666235702</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3178511338104111</v>
+        <v>0.3804977717065086</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0004952967360718256</v>
+        <v>0.0004735664198234177</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9866781564869426</v>
+        <v>0.9870424741717575</v>
       </c>
     </row>
     <row r="44">
@@ -5529,16 +5529,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001350854155382555</v>
+        <v>0.001361064642500137</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03850887869078777</v>
+        <v>0.04515095777122481</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0002588795330382715</v>
+        <v>0.0001487912348485626</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8194313562849765</v>
+        <v>0.9028878619097808</v>
       </c>
     </row>
     <row r="45">
@@ -5549,16 +5549,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00285453525304223</v>
+        <v>0.002812157786749078</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02430420575865727</v>
+        <v>0.03087271303409572</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001209837802395381</v>
+        <v>0.0001354916389787947</v>
       </c>
       <c r="F45" t="n">
-        <v>0.975468463641503</v>
+        <v>0.9707061301585734</v>
       </c>
     </row>
     <row r="46">
@@ -5569,16 +5569,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00617254182540551</v>
+        <v>0.00623047036929162</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.02598517829855385</v>
+        <v>-0.03732697741730789</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005471531215065217</v>
+        <v>0.0005378201535551229</v>
       </c>
       <c r="F46" t="n">
-        <v>0.95497705819388</v>
+        <v>0.9572054100170363</v>
       </c>
     </row>
     <row r="47">
@@ -5589,16 +5589,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01272761351063858</v>
+        <v>0.01274479825048714</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04156552663770596</v>
+        <v>0.04968217266617836</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0002180432475320557</v>
+        <v>0.0002259119773621837</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9982421634694439</v>
+        <v>0.9981183196013788</v>
       </c>
     </row>
     <row r="48">
@@ -5609,16 +5609,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02522975519413041</v>
+        <v>0.0228387584021772</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1187802651414562</v>
+        <v>0.2533122621749866</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001092006659187045</v>
+        <v>0.00129106244527952</v>
       </c>
       <c r="F48" t="n">
-        <v>0.988884694441608</v>
+        <v>0.9811872339169522</v>
       </c>
     </row>
     <row r="49">
@@ -5629,16 +5629,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03180259585119757</v>
+        <v>0.03030933071738421</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2671041590146486</v>
+        <v>0.3935040853363336</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001152745014829158</v>
+        <v>0.0003279156671265275</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9921786362014935</v>
+        <v>0.999298192519564</v>
       </c>
     </row>
     <row r="50">
@@ -5649,16 +5649,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02943374889666229</v>
+        <v>0.03187845768277089</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.136994887900395</v>
+        <v>-0.3308758228280708</v>
       </c>
       <c r="E50" t="n">
-        <v>0.005189767490779791</v>
+        <v>0.004936551957325687</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8427914954906641</v>
+        <v>0.8742166529297881</v>
       </c>
     </row>
     <row r="51">
@@ -5669,16 +5669,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.02534391897519787</v>
+        <v>0.09644322254222905</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.23693559057178</v>
+        <v>-2.172999364053341</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01228457644581162</v>
+        <v>0.03292841260715235</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6803196999517478</v>
+        <v>0.8109339180167362</v>
       </c>
     </row>
     <row r="52">
@@ -5689,16 +5689,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002987779703862834</v>
+        <v>0.00407104618485207</v>
       </c>
       <c r="D52" t="n">
-        <v>0.005286836509313664</v>
+        <v>-0.02905464381106707</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0002748267616338894</v>
+        <v>0.001065360935104604</v>
       </c>
       <c r="F52" t="n">
-        <v>0.951686758949257</v>
+        <v>0.8795340938565409</v>
       </c>
     </row>
     <row r="53">
@@ -5709,16 +5709,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.008261964477297594</v>
+        <v>0.009949199026401458</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.01929001587382212</v>
+        <v>-0.08870334040261507</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0004288156962820328</v>
+        <v>0.0004089492359797071</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9840939438800872</v>
+        <v>0.9949570096664733</v>
       </c>
     </row>
     <row r="54">
@@ -5729,16 +5729,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0165925872445787</v>
+        <v>0.01614767612621374</v>
       </c>
       <c r="D54" t="n">
-        <v>0.04716230300838475</v>
+        <v>0.06879495649774814</v>
       </c>
       <c r="E54" t="n">
-        <v>0.002731475217005766</v>
+        <v>0.001149958213314325</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9485869407889898</v>
+        <v>0.9801169973366607</v>
       </c>
     </row>
     <row r="55">
@@ -5749,16 +5749,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03982092787307945</v>
+        <v>0.03339576796216736</v>
       </c>
       <c r="D55" t="n">
-        <v>0.09123396912956527</v>
+        <v>0.2963520994842563</v>
       </c>
       <c r="E55" t="n">
-        <v>0.002893405540095763</v>
+        <v>0.001753863213203088</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9895512543854138</v>
+        <v>0.9945140796242438</v>
       </c>
     </row>
     <row r="56">
@@ -5769,16 +5769,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.05164586408042905</v>
+        <v>0.04167295313193533</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2242748339227816</v>
+        <v>0.5768614471007218</v>
       </c>
       <c r="E56" t="n">
-        <v>0.006465582645996871</v>
+        <v>0.001064243929351533</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9696072438215457</v>
+        <v>0.9980472521607722</v>
       </c>
     </row>
     <row r="57">
@@ -5789,16 +5789,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07447879482202589</v>
+        <v>0.07028880725628703</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01681928252113551</v>
+        <v>0.02841732632245542</v>
       </c>
       <c r="E57" t="n">
-        <v>0.005423048110431499</v>
+        <v>0.007828264928397929</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9895076974252245</v>
+        <v>0.9757927059688559</v>
       </c>
     </row>
   </sheetData>

--- a/kinetics/fit_velocities.xlsx
+++ b/kinetics/fit_velocities.xlsx
@@ -511,16 +511,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000478302634916474</v>
+        <v>0.0002066797928399725</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05652776651218976</v>
+        <v>-0.03343982493568712</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003364371204552723</v>
+        <v>0.0003041495537692709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2519772311255672</v>
+        <v>0.06188423975142914</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001099771855965461</v>
+        <v>0.0009918732454877407</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.008971080874085678</v>
+        <v>-0.0008786850882566213</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003657647952952742</v>
+        <v>0.0002796517194686669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6438920500322148</v>
+        <v>0.6770704705996078</v>
       </c>
     </row>
     <row r="6">
@@ -551,16 +551,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002011438509456745</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1296813323035764</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004567294155905606</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03131321635979728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -571,16 +571,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001508393386927035</v>
+        <v>0.00110015189170905</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00151189877664136</v>
+        <v>0.0260867396401473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005835356216511127</v>
+        <v>0.0003612762192180836</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6255318288762433</v>
+        <v>0.6071533264410046</v>
       </c>
     </row>
     <row r="8">
@@ -591,16 +591,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004744650518994195</v>
+        <v>0.0004942942175495736</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1229360042798103</v>
+        <v>0.1443977643356594</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003597557657813422</v>
+        <v>0.000979765648443344</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1365352687142509</v>
+        <v>0.05982404717506882</v>
       </c>
     </row>
     <row r="9">
@@ -751,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>1.785982204787331e-05</v>
+        <v>1.621585663973099e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.03561647620979188</v>
+        <v>-0.03400585023613803</v>
       </c>
       <c r="E16" t="n">
-        <v>4.453398800974768e-06</v>
+        <v>4.459726312051874e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.113195328940834</v>
+        <v>0.09496393821858118</v>
       </c>
     </row>
     <row r="17">
@@ -771,16 +771,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002087560199436228</v>
+        <v>0.0002064349907255227</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.01795821658051203</v>
+        <v>-0.01617406453809964</v>
       </c>
       <c r="E17" t="n">
-        <v>4.746240406804877e-06</v>
+        <v>4.629923784119111e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9388510915508703</v>
+        <v>0.9403976814296371</v>
       </c>
     </row>
     <row r="18">
@@ -791,16 +791,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004252064298049887</v>
+        <v>0.0004247609324866343</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.04524108253038911</v>
+        <v>-0.04418565753966186</v>
       </c>
       <c r="E18" t="n">
-        <v>4.830444861152769e-06</v>
+        <v>4.860980756298335e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9839992650574655</v>
+        <v>0.9837661660390636</v>
       </c>
     </row>
     <row r="19">
@@ -811,16 +811,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0007282179987246794</v>
+        <v>0.0007256801620756466</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0731321694487217</v>
+        <v>-0.07022478521595588</v>
       </c>
       <c r="E19" t="n">
-        <v>5.858315089204914e-06</v>
+        <v>5.965308847684862e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.991911534803762</v>
+        <v>0.991557639837634</v>
       </c>
     </row>
     <row r="20">
@@ -831,16 +831,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0008962771724840513</v>
+        <v>0.000897930436002321</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002995047908387782</v>
+        <v>0.002278639874260691</v>
       </c>
       <c r="E20" t="n">
-        <v>9.918642762637691e-06</v>
+        <v>9.841552410423922e-06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9848036247209059</v>
+        <v>0.9850896399431724</v>
       </c>
     </row>
     <row r="21">
@@ -851,16 +851,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008255629111637564</v>
+        <v>0.0008305976706377661</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2592153703934635</v>
+        <v>0.2529280392913571</v>
       </c>
       <c r="E21" t="n">
-        <v>1.349333154548062e-05</v>
+        <v>1.377738717042347e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9674365020607256</v>
+        <v>0.9664940423739194</v>
       </c>
     </row>
     <row r="22">
@@ -871,16 +871,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0002932697034450693</v>
+        <v>0.0003085698864542946</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4780884632808361</v>
+        <v>0.4633877042366994</v>
       </c>
       <c r="E22" t="n">
-        <v>2.067012642947798e-05</v>
+        <v>2.067505404011238e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6150344571569135</v>
+        <v>0.6387075849514779</v>
       </c>
     </row>
     <row r="23">
@@ -891,16 +891,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>6.029795801763322e-05</v>
+        <v>5.893715058888795e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05436702801731529</v>
+        <v>-0.05264560661995253</v>
       </c>
       <c r="E23" t="n">
-        <v>3.687667688445999e-06</v>
+        <v>3.713649578803446e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6831587757846261</v>
+        <v>0.6683206340327852</v>
       </c>
     </row>
     <row r="24">
@@ -911,16 +911,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002340085107049614</v>
+        <v>0.0002321808512417102</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03722282324636483</v>
+        <v>-0.03545328492594266</v>
       </c>
       <c r="E24" t="n">
-        <v>4.90505840341965e-06</v>
+        <v>4.90801180255446e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.947544020521632</v>
+        <v>0.946698360372256</v>
       </c>
     </row>
     <row r="25">
@@ -931,16 +931,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0006342249354125421</v>
+        <v>0.0006318300396228363</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08881462964274656</v>
+        <v>-0.08584148722027629</v>
       </c>
       <c r="E25" t="n">
-        <v>5.783247634426094e-06</v>
+        <v>6.098774160438206e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9896318526124485</v>
+        <v>0.988578649098534</v>
       </c>
     </row>
     <row r="26">
@@ -951,16 +951,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001296220162453696</v>
+        <v>0.001293972008266505</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0645252731309145</v>
+        <v>-0.06195113658658036</v>
       </c>
       <c r="E26" t="n">
-        <v>7.302735100593686e-06</v>
+        <v>7.292167642024154e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9964576585444301</v>
+        <v>0.9964240932186318</v>
       </c>
     </row>
     <row r="27">
@@ -971,16 +971,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0020328831988604</v>
+        <v>0.002027081668054414</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.07905705463012147</v>
+        <v>-0.07421277640712276</v>
       </c>
       <c r="E27" t="n">
-        <v>1.580037380195139e-05</v>
+        <v>1.578362268094247e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9951306053751406</v>
+        <v>0.9950531241832966</v>
       </c>
     </row>
     <row r="28">
@@ -991,16 +991,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002335400531598719</v>
+        <v>0.002326861761781762</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.09457011908927027</v>
+        <v>-0.08712767445681724</v>
       </c>
       <c r="E28" t="n">
-        <v>2.649180922918144e-05</v>
+        <v>2.762641162832023e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9920851782360345</v>
+        <v>0.9913359621279403</v>
       </c>
     </row>
     <row r="29">
@@ -1011,16 +1011,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001571090486478261</v>
+        <v>0.001608720148898064</v>
       </c>
       <c r="D29" t="n">
-        <v>0.374349996204941</v>
+        <v>0.3557950142143778</v>
       </c>
       <c r="E29" t="n">
-        <v>4.775135426978585e-05</v>
+        <v>4.816707023444801e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9458282389316479</v>
+        <v>0.9473450345343329</v>
       </c>
     </row>
     <row r="30">
@@ -1031,16 +1031,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001704272153634825</v>
+        <v>0.0001667188646155453</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.06683392403166011</v>
+        <v>-0.06370036764965314</v>
       </c>
       <c r="E30" t="n">
-        <v>8.653868558899004e-06</v>
+        <v>8.717233867979127e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8254740633360486</v>
+        <v>0.815051417740515</v>
       </c>
     </row>
     <row r="31">
@@ -1051,16 +1051,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005863258384838786</v>
+        <v>0.0005811561670510231</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1085232359940234</v>
+        <v>-0.1037929866329606</v>
       </c>
       <c r="E31" t="n">
-        <v>7.640414537697913e-06</v>
+        <v>8.048207399309667e-06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9851121677088666</v>
+        <v>0.9830323023898313</v>
       </c>
     </row>
     <row r="32">
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001487240994550972</v>
+        <v>0.001482264166965039</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.05209869324874161</v>
+        <v>-0.04878910290409655</v>
       </c>
       <c r="E32" t="n">
-        <v>1.260834493596635e-05</v>
+        <v>1.256484919122508e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9954213190807712</v>
+        <v>0.995351070230918</v>
       </c>
     </row>
     <row r="33">
@@ -1091,16 +1091,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003136557019145229</v>
+        <v>0.00312087062405688</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1338278000200972</v>
+        <v>-0.1244964155406056</v>
       </c>
       <c r="E33" t="n">
-        <v>2.866600340313802e-05</v>
+        <v>2.765255338090741e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9953442541689717</v>
+        <v>0.9953893310435695</v>
       </c>
     </row>
     <row r="34">
@@ -1111,16 +1111,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005164683274213436</v>
+        <v>0.005152630721264479</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0857805892262089</v>
+        <v>-0.07860932022157918</v>
       </c>
       <c r="E34" t="n">
-        <v>2.957688416213837e-05</v>
+        <v>2.942532932812065e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9981341307134131</v>
+        <v>0.998112043790193</v>
       </c>
     </row>
     <row r="35">
@@ -1131,16 +1131,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005891830832750924</v>
+        <v>0.005901955093417277</v>
       </c>
       <c r="D35" t="n">
-        <v>0.002727339536637174</v>
+        <v>0.005121083777652524</v>
       </c>
       <c r="E35" t="n">
-        <v>7.751994605327562e-05</v>
+        <v>9.70071398375188e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9938065768474211</v>
+        <v>0.9919604597379778</v>
       </c>
     </row>
     <row r="36">
@@ -1151,16 +1151,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0057652215976994</v>
+        <v>0.005705253774844659</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1048495559973901</v>
+        <v>-0.0797123430590414</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000120017009781955</v>
+        <v>0.0001314072377368927</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9871659123909748</v>
+        <v>0.9843342039021774</v>
       </c>
     </row>
     <row r="37">
@@ -1171,16 +1171,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001098100552301054</v>
+        <v>0.00109267330202125</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.003704113102340589</v>
+        <v>-0.002754344303374817</v>
       </c>
       <c r="E37" t="n">
-        <v>8.215878731992411e-05</v>
+        <v>7.306721621772189e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9225362495304232</v>
+        <v>0.9332311826565748</v>
       </c>
     </row>
     <row r="38">
@@ -1191,16 +1191,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.002111442394386372</v>
+        <v>0.002210197033083216</v>
       </c>
       <c r="D38" t="n">
-        <v>0.07200756820683007</v>
+        <v>0.05637137827491062</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001072672848888687</v>
+        <v>0.000122746631818973</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9651270547951992</v>
+        <v>0.9586070993360108</v>
       </c>
     </row>
     <row r="39">
@@ -1211,16 +1211,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.005309864779760402</v>
+        <v>0.005379404078927708</v>
       </c>
       <c r="D39" t="n">
-        <v>0.05778493681801278</v>
+        <v>0.04631095245540728</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001363062167551276</v>
+        <v>0.0001267380656089606</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9908587791390311</v>
+        <v>0.9917427373232157</v>
       </c>
     </row>
     <row r="40">
@@ -1231,16 +1231,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.009886122940502593</v>
+        <v>0.009972988471972389</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.01755458898130091</v>
+        <v>-0.02077476760704089</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002416494101240257</v>
+        <v>0.0002289866702139264</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9917047421436169</v>
+        <v>0.9926733713913378</v>
       </c>
     </row>
     <row r="41">
@@ -1251,16 +1251,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01672856515487804</v>
+        <v>0.01701544414391577</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1665822309957221</v>
+        <v>0.1285216483659899</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0001798853970874118</v>
+        <v>0.0002205238809878187</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9982685375530441</v>
+        <v>0.997653974936683</v>
       </c>
     </row>
     <row r="42">
@@ -1271,16 +1271,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02178229184401826</v>
+        <v>0.02266560342250378</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4667254223592683</v>
+        <v>0.3526144955146293</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0004169971657031811</v>
+        <v>0.0004920789556532591</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9948953672152042</v>
+        <v>0.9934444874501255</v>
       </c>
     </row>
     <row r="43">
@@ -1291,16 +1291,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.02415986008531077</v>
+        <v>0.02561597951300466</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5561283192825321</v>
+        <v>0.3999097658821769</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0008232636006541199</v>
+        <v>0.0006488372489791191</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9840039092956276</v>
+        <v>0.9910978647101609</v>
       </c>
     </row>
     <row r="44">
@@ -1311,16 +1311,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00189415084345195</v>
+        <v>0.001785748972083108</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.02345423517109729</v>
+        <v>-0.01424007610474572</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001943309573332065</v>
+        <v>0.0001630205544062265</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9405968304334549</v>
+        <v>0.9448788725307488</v>
       </c>
     </row>
     <row r="45">
@@ -1331,16 +1331,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003959776405379444</v>
+        <v>0.004018346887248028</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005651660402169134</v>
+        <v>-0.005988805854920315</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001743428716327566</v>
+        <v>0.0001620501534752195</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9885026918953527</v>
+        <v>0.9903364200358433</v>
       </c>
     </row>
     <row r="46">
@@ -1351,16 +1351,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00911553263511417</v>
+        <v>0.008891393804213213</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.05705080554274033</v>
+        <v>-0.03575761660714938</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0002882535352447337</v>
+        <v>0.000263859035075208</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9930488948746661</v>
+        <v>0.9930040730649258</v>
       </c>
     </row>
     <row r="47">
@@ -1371,16 +1371,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01723067399952703</v>
+        <v>0.01768304580982624</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09323560845379464</v>
+        <v>0.05900594188401331</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0005183320118346973</v>
+        <v>0.0005830224752495374</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9945997838639774</v>
+        <v>0.9935198620098215</v>
       </c>
     </row>
     <row r="48">
@@ -1391,16 +1391,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02295695362902065</v>
+        <v>0.02544544042696292</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3172324373760587</v>
+        <v>0.1650838067548952</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001257044723888447</v>
+        <v>0.001318021503089539</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9823281992253925</v>
+        <v>0.9841568829342399</v>
       </c>
     </row>
     <row r="49">
@@ -1411,16 +1411,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03391835505664999</v>
+        <v>0.03825256439971473</v>
       </c>
       <c r="D49" t="n">
-        <v>0.860354049405057</v>
+        <v>0.5307766392998574</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00144665246362715</v>
+        <v>0.002964648763695965</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9892031861240218</v>
+        <v>0.9652143281163967</v>
       </c>
     </row>
     <row r="50">
@@ -1431,16 +1431,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03258927876527163</v>
+        <v>0.03743799790642453</v>
       </c>
       <c r="D50" t="n">
-        <v>1.045753653182488</v>
+        <v>0.6784469493203307</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0005564460082692587</v>
+        <v>0.002922312076682579</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9982538208601266</v>
+        <v>0.9647316038290692</v>
       </c>
     </row>
     <row r="51">
@@ -1451,16 +1451,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002602955416039446</v>
+        <v>0.002429107965784368</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.032667021084142</v>
+        <v>-0.02246244008618048</v>
       </c>
       <c r="E51" t="n">
-        <v>0.002517134442321767</v>
+        <v>0.0003412543227808501</v>
       </c>
       <c r="F51" t="n">
-        <v>0.348396637926584</v>
+        <v>0.8636404258181274</v>
       </c>
     </row>
     <row r="52">
@@ -1471,16 +1471,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.006796595050849956</v>
+        <v>0.006258293212662747</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.03831660190928815</v>
+        <v>-0.01409301919086378</v>
       </c>
       <c r="E52" t="n">
-        <v>0.001551658832806882</v>
+        <v>0.0009482288757508825</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9055991926690973</v>
+        <v>0.9355666757370785</v>
       </c>
     </row>
     <row r="53">
@@ -1491,16 +1491,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01059476060694278</v>
+        <v>0.01034792823791227</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.02133002579317989</v>
+        <v>-0.00775424549650211</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0005397331825440457</v>
+        <v>0.00038099435715485</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9922744570958819</v>
+        <v>0.994606859780006</v>
       </c>
     </row>
     <row r="54">
@@ -1511,16 +1511,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01743958534911457</v>
+        <v>0.02676310308295157</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3747755366013105</v>
+        <v>0.08919282355799296</v>
       </c>
       <c r="E54" t="n">
-        <v>0.002560991338361036</v>
+        <v>0.00319558185696926</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9586537906506466</v>
+        <v>0.9722765815049113</v>
       </c>
     </row>
     <row r="55">
@@ -1531,16 +1531,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03832872015289975</v>
+        <v>0.04732323654130814</v>
       </c>
       <c r="D55" t="n">
-        <v>0.372433468607366</v>
+        <v>0.09857414539042542</v>
       </c>
       <c r="E55" t="n">
-        <v>0.001488061831749408</v>
+        <v>0.003011737924075016</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9954985213670325</v>
+        <v>0.9919645239153858</v>
       </c>
     </row>
     <row r="56">
@@ -1551,16 +1551,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.05080560003201921</v>
+        <v>0.04419940743382526</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4823684941987576</v>
+        <v>-0.1694905856805076</v>
       </c>
       <c r="E56" t="n">
-        <v>0.006419894881066486</v>
+        <v>0.003672265791131092</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9690535775972782</v>
+        <v>0.9731300899279662</v>
       </c>
     </row>
     <row r="57">
@@ -1571,16 +1571,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07841921019065964</v>
+        <v>0.07112134243455477</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3907933311735032</v>
+        <v>-0.06238928214878392</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0007111157905048245</v>
+        <v>0.004233381605489921</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9998355649883426</v>
+        <v>0.989482696550156</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,16 +1637,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>6.209594303830201e-05</v>
+        <v>5.628656830937105e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.006412673145205544</v>
+        <v>-0.005163657578485387</v>
       </c>
       <c r="E2" t="n">
-        <v>2.884766245330071e-05</v>
+        <v>2.643310343664179e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.196055004913752</v>
+        <v>0.1848157629210962</v>
       </c>
     </row>
     <row r="3">
@@ -1657,16 +1657,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001257183073095175</v>
+        <v>7.205419769015503e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01861712949268713</v>
+        <v>-0.01273595573324893</v>
       </c>
       <c r="E3" t="n">
-        <v>7.180165638959597e-05</v>
+        <v>4.661692172466613e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2770445784243408</v>
+        <v>0.1660344647037607</v>
       </c>
     </row>
     <row r="4">
@@ -1677,16 +1677,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009984601995747884</v>
+        <v>0.0008161805919785038</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1047803916027477</v>
+        <v>-0.07834984850128637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003035024839455897</v>
+        <v>0.0002831264795740749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4742084980621581</v>
+        <v>0.3899635316753821</v>
       </c>
     </row>
     <row r="5">
@@ -1697,16 +1697,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000326458562780244</v>
+        <v>0.000199917643695579</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01200685199019024</v>
+        <v>-0.004558089425062846</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002780082963968378</v>
+        <v>0.0001061860756082395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2563569728014092</v>
+        <v>0.2616983331835226</v>
       </c>
     </row>
     <row r="6">
@@ -1717,16 +1717,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001520676920305501</v>
+        <v>0.0003468664934470913</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06240977496141587</v>
+        <v>0.04991926274700873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001872671434176062</v>
+        <v>0.000531747739814807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07614875367753955</v>
+        <v>0.096150095479599</v>
       </c>
     </row>
     <row r="7">
@@ -1737,16 +1737,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001421196642303034</v>
+        <v>0.0002046560787841618</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07107077271207084</v>
+        <v>0.07049220324967641</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001954056569086212</v>
+        <v>0.0005186153909323345</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05551213782667042</v>
+        <v>0.03747241545762591</v>
       </c>
     </row>
     <row r="8">
@@ -1757,16 +1757,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004649420157516727</v>
+        <v>0.000680025019008728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2156945764300531</v>
+        <v>0.1952616911206328</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0005267056494834522</v>
+        <v>0.0004381318241622798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1001671752355073</v>
+        <v>0.231435721242002</v>
       </c>
     </row>
     <row r="9">
@@ -1917,16 +1917,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>2.411881232082187e-06</v>
+        <v>1.748872353998049e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.05425479219142621</v>
+        <v>-0.05297810747510917</v>
       </c>
       <c r="E16" t="n">
-        <v>3.614776919342887e-06</v>
+        <v>3.67638024569158e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.003520841783216418</v>
+        <v>0.001792773985524489</v>
       </c>
     </row>
     <row r="17">
@@ -1937,16 +1937,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>4.672664280418188e-05</v>
+        <v>4.580987992056485e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02576524357955568</v>
+        <v>-0.02475176148126029</v>
       </c>
       <c r="E17" t="n">
-        <v>4.163952341648628e-06</v>
+        <v>4.179462055758129e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.499854426448087</v>
+        <v>0.4880903979440749</v>
       </c>
     </row>
     <row r="18">
@@ -1957,16 +1957,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>6.188118152200374e-05</v>
+        <v>5.938380911222198e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07831265593113737</v>
+        <v>-0.07544155268524905</v>
       </c>
       <c r="E18" t="n">
-        <v>4.08064104168906e-06</v>
+        <v>4.231228251251504e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6460319128190359</v>
+        <v>0.6098725900112486</v>
       </c>
     </row>
     <row r="19">
@@ -1977,16 +1977,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>8.158483334156716e-05</v>
+        <v>8.489547614818244e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06812193358724206</v>
+        <v>0.06512554727209036</v>
       </c>
       <c r="E19" t="n">
-        <v>5.494806372388042e-06</v>
+        <v>5.436532408102335e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6363132724301142</v>
+        <v>0.6593225745605525</v>
       </c>
     </row>
     <row r="20">
@@ -1997,16 +1997,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>1.033180810614429e-06</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0627236862814774</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6.510975997369133e-06</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001998035253734738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2057,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001178679120737686</v>
+        <v>0.0001155003975527648</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05713984124309128</v>
+        <v>-0.05503022626042029</v>
       </c>
       <c r="E23" t="n">
-        <v>5.917179917407381e-06</v>
+        <v>4.639926820762821e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8167935792586754</v>
+        <v>0.8527484079560501</v>
       </c>
     </row>
     <row r="24">
@@ -2077,16 +2077,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002217476949400288</v>
+        <v>0.0002220332215753877</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008841576444053312</v>
+        <v>0.008566043240932047</v>
       </c>
       <c r="E24" t="n">
-        <v>6.610358084213259e-06</v>
+        <v>6.476145837589664e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9229065754859566</v>
+        <v>0.9252231102969609</v>
       </c>
     </row>
     <row r="25">
@@ -2097,16 +2097,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007797272755529897</v>
+        <v>0.007732086049437432</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.245331787826456</v>
+        <v>-2.169389275228733</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0009973904245682631</v>
+        <v>0.0009810619139538747</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3490030208179414</v>
+        <v>0.3507064604164092</v>
       </c>
     </row>
     <row r="26">
@@ -2117,16 +2117,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0007721726105941707</v>
+        <v>0.0007842167826253947</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1152010516155826</v>
+        <v>0.1081840487302492</v>
       </c>
       <c r="E26" t="n">
-        <v>2.162514060167383e-05</v>
+        <v>2.235298011661702e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9536275977592287</v>
+        <v>0.9520435418973305</v>
       </c>
     </row>
     <row r="27">
@@ -2137,16 +2137,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005222595554624347</v>
+        <v>0.0005459299151155997</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1627023554206921</v>
+        <v>0.1509938202787462</v>
       </c>
       <c r="E27" t="n">
-        <v>2.51306199864678e-05</v>
+        <v>2.547939676237555e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8744642642204643</v>
+        <v>0.8810180714839072</v>
       </c>
     </row>
     <row r="28">
@@ -2157,16 +2157,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003233247855342739</v>
+        <v>0.0003641574810850646</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2551053734529309</v>
+        <v>0.236236560570168</v>
       </c>
       <c r="E28" t="n">
-        <v>3.756820165193303e-05</v>
+        <v>3.670407978660341e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5443492241177484</v>
+        <v>0.6135507937046042</v>
       </c>
     </row>
     <row r="29">
@@ -2197,16 +2197,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0002867274857200216</v>
+        <v>0.0002850703145352181</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0045821941585035</v>
+        <v>-0.003993898387898279</v>
       </c>
       <c r="E30" t="n">
-        <v>1.818077211860912e-05</v>
+        <v>1.719656288003925e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8828632017335215</v>
+        <v>0.8898972658624508</v>
       </c>
     </row>
     <row r="31">
@@ -2217,16 +2217,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0007496363205057472</v>
+        <v>0.0007499003703418351</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00284158421711378</v>
+        <v>0.002753127522024362</v>
       </c>
       <c r="E31" t="n">
-        <v>2.944434728437061e-05</v>
+        <v>2.771119970806042e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9543568999435621</v>
+        <v>0.9581323114461171</v>
       </c>
     </row>
     <row r="32">
@@ -2237,16 +2237,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0008655556727159334</v>
+        <v>0.0008645819153415167</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03017576531164468</v>
+        <v>-0.02902186282296104</v>
       </c>
       <c r="E32" t="n">
-        <v>2.566099939298885e-05</v>
+        <v>2.523595440359163e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9074768011424375</v>
+        <v>0.9093544986460201</v>
       </c>
     </row>
     <row r="33">
@@ -2257,16 +2257,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002437030902672767</v>
+        <v>0.002459567829627863</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07366674912094495</v>
+        <v>0.06634224786053888</v>
       </c>
       <c r="E33" t="n">
-        <v>4.85314512615775e-05</v>
+        <v>4.740792966926108e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9882426530682312</v>
+        <v>0.9886139574303013</v>
       </c>
     </row>
     <row r="34">
@@ -2277,16 +2277,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002495975548750779</v>
+        <v>0.002554696137585798</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1172384620212398</v>
+        <v>0.1025162742812357</v>
       </c>
       <c r="E34" t="n">
-        <v>8.148349526454975e-05</v>
+        <v>8.24850348824289e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9690178412634881</v>
+        <v>0.969673749668542</v>
       </c>
     </row>
     <row r="35">
@@ -2297,16 +2297,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001587505497167043</v>
+        <v>0.001693242234872524</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3267654403083639</v>
+        <v>0.2942021996098321</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001227535583571808</v>
+        <v>0.0001358146958590824</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8479076075967945</v>
+        <v>0.838216943657637</v>
       </c>
     </row>
     <row r="36">
@@ -2317,16 +2317,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0008719794750613077</v>
+        <v>0.001009956733979327</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2471417998592124</v>
+        <v>0.2202647156769284</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001243275685572527</v>
+        <v>0.0001078532978239687</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6211647336653245</v>
+        <v>0.7450880599703606</v>
       </c>
     </row>
     <row r="37">
@@ -2337,16 +2337,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0001521637414711799</v>
+        <v>0.0001473176772068823</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.005751382797838562</v>
+        <v>-0.004661018338371598</v>
       </c>
       <c r="E37" t="n">
-        <v>1.882703615585702e-05</v>
+        <v>1.741290292559487e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7655934423725234</v>
+        <v>0.7731593271735433</v>
       </c>
     </row>
     <row r="38">
@@ -2357,16 +2357,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0004051157036444823</v>
+        <v>0.0003964976802027301</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0108709992078756</v>
+        <v>-0.008845763699063862</v>
       </c>
       <c r="E38" t="n">
-        <v>1.991426035954873e-05</v>
+        <v>1.891777204575704e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9517060921314737</v>
+        <v>0.952306614030468</v>
       </c>
     </row>
     <row r="39">
@@ -2377,16 +2377,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0005965366668375799</v>
+        <v>0.000593926264534353</v>
       </c>
       <c r="D39" t="n">
-        <v>0.002590415193054474</v>
+        <v>0.003021131573086921</v>
       </c>
       <c r="E39" t="n">
-        <v>5.804087190416274e-05</v>
+        <v>5.120942001051714e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8829770550589137</v>
+        <v>0.8996745021616125</v>
       </c>
     </row>
     <row r="40">
@@ -2397,16 +2397,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001158969921057227</v>
+        <v>0.001182439295320993</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02840474032368476</v>
+        <v>0.0245322935701634</v>
       </c>
       <c r="E40" t="n">
-        <v>7.164900948817428e-05</v>
+        <v>6.462498528644017e-05</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9492113121152258</v>
+        <v>0.9571156451523041</v>
       </c>
     </row>
     <row r="41">
@@ -2417,16 +2417,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.002169824324658339</v>
+        <v>0.002156404977928663</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007524796643692211</v>
+        <v>0.01040995619057256</v>
       </c>
       <c r="E41" t="n">
-        <v>8.289679172795167e-05</v>
+        <v>7.57416341029007e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9730163897535241</v>
+        <v>0.9759201936469593</v>
       </c>
     </row>
     <row r="42">
@@ -2437,16 +2437,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.002905365855796949</v>
+        <v>0.002898463651132493</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04053299138055666</v>
+        <v>0.04277620789650471</v>
       </c>
       <c r="E42" t="n">
-        <v>5.147047277240375e-05</v>
+        <v>4.851203970848812e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9906724837713394</v>
+        <v>0.9913906597831205</v>
       </c>
     </row>
     <row r="43">
@@ -2457,16 +2457,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003033476652225692</v>
+        <v>0.002969718789253187</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09877549581390038</v>
+        <v>0.1049284071023305</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0002112133026626807</v>
+        <v>5.907837821483914e-05</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9364420111609991</v>
+        <v>0.9867229792033405</v>
       </c>
     </row>
     <row r="44">
@@ -2477,16 +2477,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000473446184572259</v>
+        <v>0.0004712840599903716</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.003766435078712882</v>
+        <v>-0.003150229572874988</v>
       </c>
       <c r="E44" t="n">
-        <v>2.249394257714965e-05</v>
+        <v>2.097789439413365e-05</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9445636655951232</v>
+        <v>0.9492204178435816</v>
       </c>
     </row>
     <row r="45">
@@ -2497,16 +2497,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0008647858611495035</v>
+        <v>0.0009218005177409231</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01773506651739286</v>
+        <v>0.01231867414120799</v>
       </c>
       <c r="E45" t="n">
-        <v>4.900236615642623e-05</v>
+        <v>5.110394973649267e-05</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9780182660449773</v>
+        <v>0.9760019630682881</v>
       </c>
     </row>
     <row r="46">
@@ -2517,16 +2517,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.001465986781903427</v>
+        <v>0.00144666281006591</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.01193462296605419</v>
+        <v>-0.008552927894488666</v>
       </c>
       <c r="E46" t="n">
-        <v>5.374331485776544e-05</v>
+        <v>4.903818365449162e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9802388613186047</v>
+        <v>0.9819472952891001</v>
       </c>
     </row>
     <row r="47">
@@ -2537,16 +2537,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003293311088063584</v>
+        <v>0.003410969672741011</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00823581351713662</v>
+        <v>0.004609953163375008</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001262549882337805</v>
+        <v>8.344200074700834e-05</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9912588233840766</v>
+        <v>0.9964222633108666</v>
       </c>
     </row>
     <row r="48">
@@ -2557,16 +2557,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.004275903240217056</v>
+        <v>0.004300356456982055</v>
       </c>
       <c r="D48" t="n">
-        <v>0.06221197342442653</v>
+        <v>0.07367797727351966</v>
       </c>
       <c r="E48" t="n">
-        <v>7.122919150572444e-05</v>
+        <v>0.0003974451363745182</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9936580170705306</v>
+        <v>0.9512482101275039</v>
       </c>
     </row>
     <row r="49">
@@ -2577,16 +2577,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00551403599678935</v>
+        <v>0.005529937815272958</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07826027581292472</v>
+        <v>0.07500040302378497</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0001171310463654615</v>
+        <v>0.0001063460561526024</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9919431709469207</v>
+        <v>0.9930222586598397</v>
       </c>
     </row>
     <row r="50">
@@ -2597,16 +2597,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.005524046522426835</v>
+        <v>0.005530454332444998</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1614487251982583</v>
+        <v>0.1603914365452611</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002798064546090868</v>
+        <v>0.0002467938285681735</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9653260850288305</v>
+        <v>0.9709961444062045</v>
       </c>
     </row>
     <row r="51">
@@ -2617,16 +2617,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0009621308384246017</v>
+        <v>0.0009247857496823227</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01138769339805996</v>
+        <v>-0.007466459080120662</v>
       </c>
       <c r="E51" t="n">
-        <v>6.196973090674896e-05</v>
+        <v>5.500045681773457e-05</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9678780731419715</v>
+        <v>0.9691480257505163</v>
       </c>
     </row>
     <row r="52">
@@ -2637,16 +2637,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002090016258288111</v>
+        <v>0.002191230574501884</v>
       </c>
       <c r="D52" t="n">
-        <v>0.01268353915719857</v>
+        <v>0.007116751765441104</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0001615358175177419</v>
+        <v>0.000120821542488728</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9823946134066297</v>
+        <v>0.9879850229344083</v>
       </c>
     </row>
     <row r="53">
@@ -2657,16 +2657,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003678597107614001</v>
+        <v>0.004287067598712451</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.002532791536241447</v>
+        <v>-0.00881178310621239</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0008675605980701494</v>
+        <v>0.000516617963161244</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8998947400198943</v>
+        <v>0.9717762561621692</v>
       </c>
     </row>
     <row r="54">
@@ -2677,16 +2677,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.006825451738651068</v>
+        <v>0.007445611277185945</v>
       </c>
       <c r="D54" t="n">
-        <v>0.01897597653677519</v>
+        <v>0.006263460448803576</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0005566342512152093</v>
+        <v>0.0002573555074274554</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9868729155975225</v>
+        <v>0.9976162553653904</v>
       </c>
     </row>
     <row r="55">
@@ -2697,16 +2697,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.007605155998573305</v>
+        <v>0.007810094934652962</v>
       </c>
       <c r="D55" t="n">
-        <v>0.07568104947000731</v>
+        <v>0.060617474894507</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0003410330407486728</v>
+        <v>0.00152334488833706</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9841679961686117</v>
+        <v>0.8975602057449142</v>
       </c>
     </row>
     <row r="56">
@@ -2717,16 +2717,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01143245536568657</v>
+        <v>0.01299371785357671</v>
       </c>
       <c r="D56" t="n">
-        <v>0.07380289198611356</v>
+        <v>0.08087505434038628</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0003554448292402543</v>
+        <v>0.0008253247882385495</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9866477171511565</v>
+        <v>0.9919957120389205</v>
       </c>
     </row>
     <row r="57">
@@ -2737,16 +2737,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0140211073006486</v>
+        <v>0.0126884859462947</v>
       </c>
       <c r="D57" t="n">
-        <v>0.05660014895781995</v>
+        <v>0.1165681099037457</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001301114182456645</v>
+        <v>0.001075294965714032</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9830690926269818</v>
+        <v>0.9789089038027073</v>
       </c>
     </row>
     <row r="58">
@@ -2757,16 +2757,16 @@
         <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0007527514859529005</v>
+        <v>0.001003266142374126</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.008012053459376826</v>
+        <v>-0.008190477567187623</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0005051000250432505</v>
+        <v>0.0003641300675207998</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5261785757478664</v>
+        <v>0.7914788616690116</v>
       </c>
     </row>
     <row r="59">
@@ -2777,16 +2777,16 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>0.002126034984225638</v>
+        <v>0.001831552213923223</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.02003017181792856</v>
+        <v>-0.00677844715431989</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0003599573116036422</v>
+        <v>0.000268507832400911</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9457774265454439</v>
+        <v>0.9394295525437246</v>
       </c>
     </row>
     <row r="60">
@@ -2797,16 +2797,16 @@
         <v>20</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00322290658017307</v>
+        <v>0.003368180013824296</v>
       </c>
       <c r="D60" t="n">
-        <v>0.009058173914654327</v>
+        <v>0.005090752026033429</v>
       </c>
       <c r="E60" t="n">
-        <v>7.801764588823817e-05</v>
+        <v>4.797998249801226e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9988293918097556</v>
+        <v>0.9995943202248345</v>
       </c>
     </row>
     <row r="61">
@@ -2817,16 +2817,16 @@
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>0.004746289823830715</v>
+        <v>0.004694795481427363</v>
       </c>
       <c r="D61" t="n">
-        <v>0.001181687379300689</v>
+        <v>0.00504376305955212</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0002796716640216505</v>
+        <v>0.0002105643739471675</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9829358907835242</v>
+        <v>0.9880744789486345</v>
       </c>
     </row>
     <row r="62">
@@ -2837,16 +2837,16 @@
         <v>80</v>
       </c>
       <c r="C62" t="n">
-        <v>0.01513494231336207</v>
+        <v>0.01396969459598969</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0639798062371324</v>
+        <v>-0.011181493058397</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0005714398269533462</v>
+        <v>0.0004955237199908368</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9971570251343714</v>
+        <v>0.9949923403720207</v>
       </c>
     </row>
     <row r="63">
@@ -2857,16 +2857,16 @@
         <v>160</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01787112767769273</v>
+        <v>0.01889718533605814</v>
       </c>
       <c r="D63" t="n">
-        <v>0.07139505986625982</v>
+        <v>0.07078972384510701</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004464823741827524</v>
+        <v>0.0004299909440382635</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9950314289092821</v>
+        <v>0.9989655610013842</v>
       </c>
     </row>
     <row r="64">
@@ -2877,16 +2877,16 @@
         <v>320</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02764680748071382</v>
+        <v>0.02420082759691104</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.2052811372649292</v>
+        <v>-0.01575224365577621</v>
       </c>
       <c r="E64" t="n">
-        <v>0.002824173336857838</v>
+        <v>0.002715975987398086</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9696452371878808</v>
+        <v>0.952037116176167</v>
       </c>
     </row>
     <row r="65">
@@ -2897,16 +2897,16 @@
         <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0005637197688465659</v>
+        <v>0.0005496621118675329</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.001031886090172476</v>
+        <v>-0.0001181383865353318</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0002859533014543667</v>
+        <v>0.0002023623430373663</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4927912834626165</v>
+        <v>0.5960539482746412</v>
       </c>
     </row>
     <row r="66">
@@ -2914,19 +2914,19 @@
         <v>32</v>
       </c>
       <c r="B66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0008978360107734975</v>
+        <v>0.000819435243417543</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0007700486957303021</v>
+        <v>-0.00683877978074216</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0005917662608704247</v>
+        <v>0.0007628825410641393</v>
       </c>
       <c r="F66" t="n">
-        <v>0.434169175813046</v>
+        <v>0.3658355056271101</v>
       </c>
     </row>
     <row r="67">
@@ -2934,19 +2934,19 @@
         <v>32</v>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>0.002178615788120938</v>
+        <v>0.0009821435780778178</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01823159514293464</v>
+        <v>-1.009315946600906e-05</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0001175770634265304</v>
+        <v>0.0009369574289914481</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9942084955985089</v>
+        <v>0.3545844433970099</v>
       </c>
     </row>
     <row r="68">
@@ -2954,19 +2954,19 @@
         <v>32</v>
       </c>
       <c r="B68" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>0.005426697742977513</v>
+        <v>0.001053389409602596</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0315753248257441</v>
+        <v>0.002097596023141999</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0002457615064316883</v>
+        <v>0.001102714858712065</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9959148438993308</v>
+        <v>0.3133139201404768</v>
       </c>
     </row>
     <row r="69">
@@ -2974,19 +2974,19 @@
         <v>32</v>
       </c>
       <c r="B69" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01239225155307917</v>
+        <v>0.002523916168410479</v>
       </c>
       <c r="D69" t="n">
-        <v>0.01282673692620701</v>
+        <v>0.007594400563426897</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0009258732744180148</v>
+        <v>0.0001422256991158544</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9889589364397617</v>
+        <v>0.9936891646028406</v>
       </c>
     </row>
     <row r="70">
@@ -2994,19 +2994,19 @@
         <v>32</v>
       </c>
       <c r="B70" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="C70" t="n">
-        <v>0.02067016100889742</v>
+        <v>0.002607623439993274</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4621826998076703</v>
+        <v>-0.0296430346745202</v>
       </c>
       <c r="E70" t="n">
-        <v>0.001287346213401399</v>
+        <v>0.0004907065923779716</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9847216491781178</v>
+        <v>0.8759258353652499</v>
       </c>
     </row>
     <row r="71">
@@ -3014,299 +3014,299 @@
         <v>32</v>
       </c>
       <c r="B71" t="n">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="C71" t="n">
-        <v>0.03790092854516987</v>
+        <v>0.005809959355600041</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.08720994348729749</v>
+        <v>0.01737653831087016</v>
       </c>
       <c r="E71" t="n">
-        <v>0.001272254596642153</v>
+        <v>0.0003597357063481165</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9977514594464972</v>
+        <v>0.9923908933523224</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0008584242151243477</v>
+        <v>0.003780483493484689</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.006037072804737052</v>
+        <v>-0.056499400878102</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002294273229926866</v>
+        <v>0.001346646721732433</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6666593029726986</v>
+        <v>0.7242928096262273</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B73" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C73" t="n">
-        <v>0.001676394625269263</v>
+        <v>0.0122366044420055</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.02605638173439933</v>
+        <v>0.01983085692452186</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0003513289687046589</v>
+        <v>0.0005420539159736259</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8835764615344204</v>
+        <v>0.9941475832366091</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B74" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003095863290822843</v>
+        <v>0.007723427793259673</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.07222209143291283</v>
+        <v>-0.007124392765962745</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0004707125875367149</v>
+        <v>0.0006250090251931952</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9153556573721072</v>
+        <v>0.9807325500176823</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B75" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="C75" t="n">
-        <v>0.005132557268998183</v>
+        <v>0.02946246081953719</v>
       </c>
       <c r="D75" t="n">
-        <v>0.06373114657094403</v>
+        <v>0.1767343371186675</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0005419225591777818</v>
+        <v>0.004527706112385978</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9373041705430138</v>
+        <v>0.9548970477885722</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B76" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C76" t="n">
-        <v>0.01196009499089357</v>
+        <v>0.02194054126078456</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1321267101298278</v>
+        <v>-2.888723639059728</v>
       </c>
       <c r="E76" t="n">
-        <v>0.001623687378793117</v>
+        <v>0.002255551975568189</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9313399970844342</v>
+        <v>0.7299826882576329</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B77" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="C77" t="n">
-        <v>0.01611936559454548</v>
+        <v>0.03465083929154774</v>
       </c>
       <c r="D77" t="n">
-        <v>0.03375853296378639</v>
+        <v>0.05904407292569869</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0008246738642194321</v>
+        <v>0.002015085764526063</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9820079107166423</v>
+        <v>0.9899562290322302</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B78" t="n">
         <v>320</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03356213944304377</v>
+        <v>0.02250938734785125</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1124713587437178</v>
+        <v>0.1604598542285963</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0007222724083953382</v>
+        <v>0.005576638574385628</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9990745974609391</v>
+        <v>0.890664367590961</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B79" t="n">
         <v>5</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0004009496087340287</v>
+        <v>0.001135912751817307</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.005232962810444958</v>
+        <v>-0.0004695798110111518</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0003837801705442652</v>
+        <v>0.0002234981412735392</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2667684268824529</v>
+        <v>0.9281378262902603</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B80" t="n">
         <v>10</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0009570944484226776</v>
+        <v>0.001468339833923692</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.004700443734847196</v>
+        <v>-0.01282289261100238</v>
       </c>
       <c r="E80" t="n">
-        <v>0.000467502178710605</v>
+        <v>0.0001989579590711142</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5116733229703717</v>
+        <v>0.9159192345404438</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B81" t="n">
         <v>20</v>
       </c>
       <c r="C81" t="n">
-        <v>0.001051816246083653</v>
+        <v>0.002602557624009712</v>
       </c>
       <c r="D81" t="n">
-        <v>0.05142812019430012</v>
+        <v>-0.04299519607311125</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0003192348130437325</v>
+        <v>0.0001622731220728725</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7307437271986736</v>
+        <v>0.9554270621394217</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B82" t="n">
         <v>40</v>
       </c>
       <c r="C82" t="n">
-        <v>0.001264553751656187</v>
+        <v>0.007467238900995353</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.05181048173942288</v>
+        <v>0.01605624732250516</v>
       </c>
       <c r="E82" t="n">
-        <v>0.000168441120477316</v>
+        <v>0.000297748132357331</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9037859510827202</v>
+        <v>0.9968302194876132</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B83" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C83" t="n">
-        <v>0.001930064237791411</v>
+        <v>0.0127288552757014</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0163323767520718</v>
+        <v>0.08215729161731899</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004076667521451069</v>
+        <v>0.001230925590978314</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1007788625046391</v>
+        <v>0.9553307495298988</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B84" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C84" t="n">
-        <v>0.009773960567177109</v>
+        <v>0.01805331809704621</v>
       </c>
       <c r="D84" t="n">
-        <v>0.077119606102658</v>
+        <v>0.03154016861642644</v>
       </c>
       <c r="E84" t="n">
-        <v>0.003465003161321029</v>
+        <v>0.001726493583298468</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7991305706418145</v>
+        <v>0.982037209386602</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B85" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="C85" t="n">
-        <v>0.03757252222674497</v>
+        <v>0.03315246432704098</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.3660034537039223</v>
+        <v>0.1362466422000176</v>
       </c>
       <c r="E85" t="n">
-        <v>0.006704172889795313</v>
+        <v>0.0009139763843314667</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9401353964226261</v>
+        <v>0.9984822206222843</v>
       </c>
     </row>
     <row r="86">
@@ -3314,139 +3314,139 @@
         <v>128</v>
       </c>
       <c r="B86" t="n">
-        <v>320</v>
+        <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>8.33476960143616e-06</v>
+        <v>0.0003421958116165327</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1898858289401071</v>
+        <v>-0.002001503968982675</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.000253522708145776</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.3129346749643677</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0005150329019100256</v>
+        <v>0.0009088338792112508</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0260128059811548</v>
+        <v>-0.001563506736104454</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0003739113012065337</v>
+        <v>0.0003317461445087969</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2750771654279539</v>
+        <v>0.6001635558521589</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.002421474111853991</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.01271429558830829</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>0.0006997283739956431</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>0.8568944054848067</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B89" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0007134529791442296</v>
+        <v>0.0009878375260947341</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1585876392360197</v>
+        <v>-0.02828960256669937</v>
       </c>
       <c r="E89" t="n">
-        <v>4.40581179655976e-05</v>
+        <v>0.0002062702187348377</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8214441552122356</v>
+        <v>0.7661596988624588</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B90" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C90" t="n">
-        <v>0.002388618635204971</v>
+        <v>0.013794254697523</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1803884656743361</v>
+        <v>-0.004232540190900913</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0007050628259957393</v>
+        <v>0.001218477547863089</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5892644851571086</v>
+        <v>0.9846346069999948</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B91" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C91" t="n">
-        <v>0.005449699757250669</v>
+        <v>0.03189389383783461</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4255333059514934</v>
+        <v>-0.1104651762029562</v>
       </c>
       <c r="E91" t="n">
-        <v>0.001891263276840214</v>
+        <v>0.005072565245698507</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6748791459314231</v>
+        <v>0.929466536770731</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B92" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="C92" t="n">
-        <v>1.070147608823846e-05</v>
+        <v>0.0006751163377163224</v>
       </c>
       <c r="D92" t="n">
-        <v>0.05989367546435513</v>
+        <v>0.1665484740560861</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.0003849665178418107</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0.6059477265030937</v>
       </c>
     </row>
     <row r="93">
@@ -3454,18 +3454,138 @@
         <v>256</v>
       </c>
       <c r="B93" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.0003653162804208759</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.01478405936946857</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0002917939733785146</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.2071274091619066</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>256</v>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>256</v>
+      </c>
+      <c r="B95" t="n">
+        <v>20</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.0006956196444785418</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.1479768051099354</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4.381598593396443e-05</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.812930525599893</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>256</v>
+      </c>
+      <c r="B96" t="n">
+        <v>40</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.003352529581827439</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.1139884272137688</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.001503096867302475</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.4987343255693353</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>256</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.01599335971382894</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.1158191378105191</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.004558187991029265</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.8602478089637235</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>256</v>
+      </c>
+      <c r="B98" t="n">
+        <v>160</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1.070147608823855e-05</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.05989367546435512</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>256</v>
+      </c>
+      <c r="B99" t="n">
         <v>320</v>
       </c>
-      <c r="C93" t="n">
-        <v>8.334769601436173e-06</v>
-      </c>
-      <c r="D93" t="n">
+      <c r="C99" t="n">
+        <v>8.33476960143617e-06</v>
+      </c>
+      <c r="D99" t="n">
         <v>0.1565467505343628</v>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3523,16 +3643,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003816205072684881</v>
+        <v>0.0003738385127165759</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2541186855520316</v>
+        <v>-0.2452861217356112</v>
       </c>
       <c r="E2" t="n">
-        <v>2.910875216952379e-05</v>
+        <v>2.894881606616765e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6076024630817439</v>
+        <v>0.5982287607833533</v>
       </c>
     </row>
     <row r="3">
@@ -3543,16 +3663,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001438313712653079</v>
+        <v>0.0001301145231993981</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2977256785257062</v>
+        <v>-0.2850375940647397</v>
       </c>
       <c r="E3" t="n">
-        <v>4.415482350903891e-05</v>
+        <v>4.392495853956181e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.105464436672254</v>
+        <v>0.08794450349583403</v>
       </c>
     </row>
     <row r="4">
@@ -3563,16 +3683,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.056049406762446e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.01865448402665061</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.0004687578173191595</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.871721832022097e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3583,16 +3703,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001268521211106938</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07494826695552234</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004091183250062147</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02347053357915767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3643,16 +3763,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001068182457636831</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08832407144644989</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002294981460497821</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05137671240709708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3903,16 +4023,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>5.773190533628757e-05</v>
+        <v>5.841707073472536e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0278783649908234</v>
+        <v>0.02793964636550583</v>
       </c>
       <c r="E21" t="n">
-        <v>8.486476286761009e-06</v>
+        <v>8.455704873815684e-06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2686250520660254</v>
+        <v>0.2747313769421321</v>
       </c>
     </row>
     <row r="22">
@@ -3923,16 +4043,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>4.038422358278781e-05</v>
+        <v>3.840364797683741e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0792131683703977</v>
+        <v>0.08166980414628418</v>
       </c>
       <c r="E22" t="n">
-        <v>1.440644931136145e-05</v>
+        <v>1.444678408815227e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05870368673624444</v>
+        <v>0.05310482179807211</v>
       </c>
     </row>
     <row r="23">
@@ -3943,16 +4063,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001181790251041508</v>
+        <v>0.0001138344407656326</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05615165232123705</v>
+        <v>-0.05304527451919653</v>
       </c>
       <c r="E23" t="n">
-        <v>8.550575506893668e-06</v>
+        <v>8.683201607625822e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7346408571973584</v>
+        <v>0.7105824183107697</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +4083,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003117774276820419</v>
+        <v>0.0003091315180507849</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02632134484047918</v>
+        <v>-0.02461473312831837</v>
       </c>
       <c r="E24" t="n">
-        <v>1.111499620402569e-05</v>
+        <v>1.088068426801181e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9269566922364543</v>
+        <v>0.9276017680126061</v>
       </c>
     </row>
     <row r="25">
@@ -3983,16 +4103,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000556143054319711</v>
+        <v>0.0005568843463976056</v>
       </c>
       <c r="D25" t="n">
-        <v>0.009269689321606767</v>
+        <v>0.008892111044252138</v>
       </c>
       <c r="E25" t="n">
-        <v>1.60583963862856e-05</v>
+        <v>1.605947635258048e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9508487634948516</v>
+        <v>0.9509668485978031</v>
       </c>
     </row>
     <row r="26">
@@ -4003,16 +4123,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001185080547867529</v>
+        <v>0.00119524503822301</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03500740777764189</v>
+        <v>0.03105000135364278</v>
       </c>
       <c r="E26" t="n">
-        <v>2.227955895049174e-05</v>
+        <v>2.182279768726024e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9785565307950059</v>
+        <v>0.9797505076236224</v>
       </c>
     </row>
     <row r="27">
@@ -4023,16 +4143,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001583439917352697</v>
+        <v>0.001602510586547736</v>
       </c>
       <c r="D27" t="n">
-        <v>0.139271853738318</v>
+        <v>0.1297331596039857</v>
       </c>
       <c r="E27" t="n">
-        <v>2.706611476352178e-05</v>
+        <v>2.735607700717628e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9822072335727036</v>
+        <v>0.9822531635725102</v>
       </c>
     </row>
     <row r="28">
@@ -4043,16 +4163,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00163216413897797</v>
+        <v>0.001649730848031991</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1856448666209387</v>
+        <v>0.1762420858487194</v>
       </c>
       <c r="E28" t="n">
-        <v>4.261199360928302e-05</v>
+        <v>4.304015868357963e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9594536529315293</v>
+        <v>0.9595086621369823</v>
       </c>
     </row>
     <row r="29">
@@ -4063,16 +4183,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001201327258434666</v>
+        <v>0.00123356452966503</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3885542952162263</v>
+        <v>0.3712608610961426</v>
       </c>
       <c r="E29" t="n">
-        <v>6.81593761682471e-05</v>
+        <v>6.907854173152866e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.833624073128851</v>
+        <v>0.837222254479743</v>
       </c>
     </row>
     <row r="30">
@@ -4083,16 +4203,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0002241860788518645</v>
+        <v>0.0002169590125286642</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.02584009484056495</v>
+        <v>-0.02312994496936484</v>
       </c>
       <c r="E30" t="n">
-        <v>2.89984697172058e-05</v>
+        <v>2.778622142736362e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6306761625748066</v>
+        <v>0.6287405242407832</v>
       </c>
     </row>
     <row r="31">
@@ -4103,16 +4223,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005441688825017279</v>
+        <v>0.0005411625823445241</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01603923218609452</v>
+        <v>-0.01447657274410084</v>
       </c>
       <c r="E31" t="n">
-        <v>3.312800922857091e-05</v>
+        <v>3.329720479089532e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8999405014973874</v>
+        <v>0.8980089731275368</v>
       </c>
     </row>
     <row r="32">
@@ -4123,16 +4243,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001126055313693867</v>
+        <v>0.001130661768067174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02165428640812583</v>
+        <v>0.0199268660181357</v>
       </c>
       <c r="E32" t="n">
-        <v>3.412387113298319e-05</v>
+        <v>3.243581544635475e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9688594720216429</v>
+        <v>0.9712255631754347</v>
       </c>
     </row>
     <row r="33">
@@ -4143,16 +4263,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002595021740906298</v>
+        <v>0.002580461028765706</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03541557423096076</v>
+        <v>-0.03039212854245654</v>
       </c>
       <c r="E33" t="n">
-        <v>4.699138813516403e-05</v>
+        <v>4.509442868406623e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9896158449076077</v>
+        <v>0.9900227629883557</v>
       </c>
     </row>
     <row r="34">
@@ -4163,16 +4283,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003653960126991983</v>
+        <v>0.003640070164553211</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.05578344249073353</v>
+        <v>-0.04876481875227168</v>
       </c>
       <c r="E34" t="n">
-        <v>6.9117716968354e-05</v>
+        <v>7.074424032412329e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9893797332324222</v>
+        <v>0.9887955530686745</v>
       </c>
     </row>
     <row r="35">
@@ -4183,16 +4303,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003894530170857382</v>
+        <v>0.003936269330027829</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1517719847291011</v>
+        <v>0.1397340326780001</v>
       </c>
       <c r="E35" t="n">
-        <v>7.476780631677715e-05</v>
+        <v>7.723375233912523e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9890638435952981</v>
+        <v>0.9885822970097361</v>
       </c>
     </row>
     <row r="36">
@@ -4203,16 +4323,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003784141303998879</v>
+        <v>0.003966366430596541</v>
       </c>
       <c r="D36" t="n">
-        <v>0.469583653550355</v>
+        <v>0.4223668254115965</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001659196297573013</v>
+        <v>0.0001742125273988591</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9454706695503851</v>
+        <v>0.9452908694491843</v>
       </c>
     </row>
     <row r="37">
@@ -4223,16 +4343,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0003326164730829121</v>
+        <v>0.0003044431295810735</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0258284904398546</v>
+        <v>-0.02061642189201445</v>
       </c>
       <c r="E37" t="n">
-        <v>8.300979779588571e-05</v>
+        <v>7.600710702810579e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5008685421563729</v>
+        <v>0.485529432998119</v>
       </c>
     </row>
     <row r="38">
@@ -4243,16 +4363,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0008254240914288292</v>
+        <v>0.0008340423576132309</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00942465354241627</v>
+        <v>0.007916456960145951</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001047199695042138</v>
+        <v>9.317908208822485e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.80552094706604</v>
+        <v>0.8335409011876733</v>
       </c>
     </row>
     <row r="39">
@@ -4263,16 +4383,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002113602456553173</v>
+        <v>0.002081929245443514</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.06430186120848441</v>
+        <v>-0.05527499604223168</v>
       </c>
       <c r="E39" t="n">
-        <v>5.612835500429166e-05</v>
+        <v>5.536007018981986e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.981994693963183</v>
+        <v>0.9812667901790803</v>
       </c>
     </row>
     <row r="40">
@@ -4283,16 +4403,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003843256512152284</v>
+        <v>0.003832119075500241</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.02628862822433298</v>
+        <v>-0.02001476817256204</v>
       </c>
       <c r="E40" t="n">
-        <v>9.109316127423411e-05</v>
+        <v>0.000139777023302188</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9894387500667222</v>
+        <v>0.9817145006150801</v>
       </c>
     </row>
     <row r="41">
@@ -4303,16 +4423,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.007174978077061659</v>
+        <v>0.007010183923754107</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.13669619094186</v>
+        <v>-0.105372339891018</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002383962520486198</v>
+        <v>0.0002737843280597778</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9847796447656758</v>
+        <v>0.9790921230003973</v>
       </c>
     </row>
     <row r="42">
@@ -4323,16 +4443,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009025375676811593</v>
+        <v>0.009140497616548705</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1052101028693226</v>
+        <v>0.09124461298845477</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0002440165617944454</v>
+        <v>0.0002443552374749726</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9898698895580664</v>
+        <v>0.9900937794618064</v>
       </c>
     </row>
     <row r="43">
@@ -4343,16 +4463,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.008130233967624301</v>
+        <v>0.00852593470255722</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2669647893432185</v>
+        <v>0.2242968767163254</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0005164098692093357</v>
+        <v>0.000498526847498899</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9465375493183751</v>
+        <v>0.9543210976267368</v>
       </c>
     </row>
     <row r="44">
@@ -4363,16 +4483,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001917664636905432</v>
+        <v>0.00189755125068344</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6932773395651705</v>
+        <v>-0.6698452446165497</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0002185983798510912</v>
+        <v>0.0002151749568812471</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4030087946085049</v>
+        <v>0.4034294232388093</v>
       </c>
     </row>
     <row r="45">
@@ -4383,16 +4503,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00173932844311615</v>
+        <v>0.001886390771283367</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01674719028861182</v>
+        <v>0.008428579774468786</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001823682966211965</v>
+        <v>0.0002286462016275311</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9285444106611168</v>
+        <v>0.9189920467719535</v>
       </c>
     </row>
     <row r="46">
@@ -4403,16 +4523,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0069180461531111</v>
+        <v>0.006811664017456285</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.03239774194657796</v>
+        <v>-0.02091444934690367</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000209009879388154</v>
+        <v>0.0001518943030330381</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9927506861551623</v>
+        <v>0.9950520836641094</v>
       </c>
     </row>
     <row r="47">
@@ -4423,16 +4543,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.004247378458311378</v>
+        <v>0.004200140324072199</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.03666855626697785</v>
+        <v>-0.02770520165756352</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001363955355467638</v>
+        <v>0.0001127556065449841</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9837680356313496</v>
+        <v>0.9871937029230418</v>
       </c>
     </row>
     <row r="48">
@@ -4443,16 +4563,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01314857466793648</v>
+        <v>0.01344435241671748</v>
       </c>
       <c r="D48" t="n">
-        <v>0.105839151171506</v>
+        <v>0.07774026503731113</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0003237360122700553</v>
+        <v>0.000309605534064179</v>
       </c>
       <c r="F48" t="n">
-        <v>0.995774445683436</v>
+        <v>0.9957753666883911</v>
       </c>
     </row>
     <row r="49">
@@ -4463,16 +4583,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01369003443743263</v>
+        <v>0.01434196314468077</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2085955500177412</v>
+        <v>0.1650798171161736</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000241438370139</v>
+        <v>0.0009435105692509518</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9956644466432263</v>
+        <v>0.974689889213161</v>
       </c>
     </row>
     <row r="50">
@@ -4483,16 +4603,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02032884837792375</v>
+        <v>0.02242083742814161</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3927809618225233</v>
+        <v>0.2670648536675293</v>
       </c>
       <c r="E50" t="n">
-        <v>0.001276812579547218</v>
+        <v>0.00128038967046422</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9768782634327834</v>
+        <v>0.9808081872722343</v>
       </c>
     </row>
     <row r="51">
@@ -4503,16 +4623,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001648682525433455</v>
+        <v>0.001470232670998151</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0240467937340505</v>
+        <v>-0.01244755319575571</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000380773748471562</v>
+        <v>0.0002882865020748212</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8241554024054543</v>
+        <v>0.8387564484856354</v>
       </c>
     </row>
     <row r="52">
@@ -4523,16 +4643,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003400600292479618</v>
+        <v>0.003877890819384896</v>
       </c>
       <c r="D52" t="n">
-        <v>0.01537504834813463</v>
+        <v>0.004893994910489502</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0002529940158978533</v>
+        <v>0.0003365650515482842</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9783399672409434</v>
+        <v>0.9851583253393086</v>
       </c>
     </row>
     <row r="53">
@@ -4543,16 +4663,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.007592684785139749</v>
+        <v>0.007708804706595662</v>
       </c>
       <c r="D53" t="n">
-        <v>0.02548895881708751</v>
+        <v>0.01677996470789395</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0004294256529135906</v>
+        <v>0.0003270208055525401</v>
       </c>
       <c r="F53" t="n">
-        <v>0.98425784735846</v>
+        <v>0.9893177257908006</v>
       </c>
     </row>
     <row r="54">
@@ -4563,16 +4683,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01369980274435692</v>
+        <v>0.01439059335998365</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05091947393527485</v>
+        <v>0.02688263342709823</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0003013016050445862</v>
+        <v>0.0008690972602726104</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9980689443217509</v>
+        <v>0.992758095524752</v>
       </c>
     </row>
     <row r="55">
@@ -4583,16 +4703,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0267471601152821</v>
+        <v>0.0243982194871796</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2221384956940307</v>
+        <v>-0.09294676114839329</v>
       </c>
       <c r="E55" t="n">
-        <v>0.001133180578017999</v>
+        <v>0.001545801356702187</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9946441074136295</v>
+        <v>0.984197229609965</v>
       </c>
     </row>
     <row r="56">
@@ -4603,16 +4723,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.03243148987566799</v>
+        <v>0.02734090219302043</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3219004007342123</v>
+        <v>-0.0928239550150719</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0021636296402738</v>
+        <v>0.003193502579456932</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9911770608839175</v>
+        <v>0.9606804040134669</v>
       </c>
     </row>
     <row r="57">
@@ -4623,16 +4743,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03075437374378786</v>
+        <v>0.03277010088543838</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1392807494767747</v>
+        <v>0.1266263403380211</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0008241615422339491</v>
+        <v>0.003925990665577704</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9949981435314866</v>
+        <v>0.9720950220657318</v>
       </c>
     </row>
   </sheetData>
@@ -4709,16 +4829,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>1.399188969111606e-05</v>
+        <v>3.96147777934095e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02165754535300702</v>
+        <v>0.01742976881612861</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000105857787862843</v>
+        <v>9.452259926282807e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001246342669901451</v>
+        <v>0.01157433087423384</v>
       </c>
     </row>
     <row r="4">
@@ -4729,16 +4849,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.630229239460409e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.02005965597976166</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.0002651227009577521</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.001404058259057197</v>
       </c>
     </row>
     <row r="5">
@@ -4749,16 +4869,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000295681711622892</v>
+        <v>9.564774715710905e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0539256417922117</v>
+        <v>-0.02960570215510131</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003562726464960944</v>
+        <v>0.0003216298385512677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1029761620219898</v>
+        <v>0.0001263234331311562</v>
       </c>
     </row>
     <row r="6">
@@ -4769,16 +4889,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.187125251007729e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.03303995834466802</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.0003468475441218737</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.001818336504716771</v>
       </c>
     </row>
     <row r="7">
@@ -4789,16 +4909,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001530275048712075</v>
+        <v>0.0002651553647984774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08007669025126371</v>
+        <v>0.07166710075671846</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0006820525814497987</v>
+        <v>0.0005124772721494074</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009967420086997135</v>
+        <v>0.04271134797218319</v>
       </c>
     </row>
     <row r="8">
@@ -4809,16 +4929,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>2.813513207036181e-05</v>
+        <v>0.00156631107282387</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08288682053092582</v>
+        <v>0.1294368865361486</v>
       </c>
       <c r="E8" t="n">
-        <v>3.074852964260057e-05</v>
+        <v>0.001630208462167612</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0114946496245095</v>
+        <v>0.1875111749100075</v>
       </c>
     </row>
     <row r="9">
@@ -4969,16 +5089,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003296040140814354</v>
+        <v>0.0003463800868727549</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2292735262600052</v>
+        <v>-0.2363571896585102</v>
       </c>
       <c r="E16" t="n">
-        <v>9.223473112270818e-05</v>
+        <v>9.1362433176318e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0920237555441196</v>
+        <v>0.1023963728112258</v>
       </c>
     </row>
     <row r="17">
@@ -4989,16 +5109,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002647922579523449</v>
+        <v>0.0002628457095716966</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02719702650368974</v>
+        <v>-0.02550743242990919</v>
       </c>
       <c r="E17" t="n">
-        <v>5.789685247285839e-06</v>
+        <v>5.757738593520059e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9431845358205895</v>
+        <v>0.9429864479890763</v>
       </c>
     </row>
     <row r="18">
@@ -5009,16 +5129,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00047683214278355</v>
+        <v>0.0004773359709146446</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01583845224947028</v>
+        <v>-0.01584170365218074</v>
       </c>
       <c r="E18" t="n">
-        <v>5.064723069168582e-06</v>
+        <v>5.039373098037401e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9859841054757199</v>
+        <v>0.9861509921462154</v>
       </c>
     </row>
     <row r="19">
@@ -5029,16 +5149,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0008730435938082817</v>
+        <v>0.0008785928718929624</v>
       </c>
       <c r="D19" t="n">
-        <v>0.100554532708124</v>
+        <v>0.09563378199727868</v>
       </c>
       <c r="E19" t="n">
-        <v>8.67945121581815e-06</v>
+        <v>8.540812178988862e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9876999115885081</v>
+        <v>0.9882333444459968</v>
       </c>
     </row>
     <row r="20">
@@ -5049,16 +5169,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001058295276653702</v>
+        <v>0.00106489050037243</v>
       </c>
       <c r="D20" t="n">
-        <v>0.16295621422924</v>
+        <v>0.1566216433853278</v>
       </c>
       <c r="E20" t="n">
-        <v>1.23306164195152e-05</v>
+        <v>1.233150954890351e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.98318253392891</v>
+        <v>0.9833843844771901</v>
       </c>
     </row>
     <row r="21">
@@ -5069,16 +5189,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008261192910346995</v>
+        <v>0.0008352099904884476</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2359567041279564</v>
+        <v>0.2274544506157005</v>
       </c>
       <c r="E21" t="n">
-        <v>1.911757245535773e-05</v>
+        <v>1.906092535762537e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.936789050580468</v>
+        <v>0.9384167111924993</v>
       </c>
     </row>
     <row r="22">
@@ -5089,16 +5209,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0004128969173520629</v>
+        <v>0.000428431586544102</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5160711126309077</v>
+        <v>0.500632576576187</v>
       </c>
       <c r="E22" t="n">
-        <v>2.621083473908525e-05</v>
+        <v>2.637503362789632e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6632404225909762</v>
+        <v>0.6768087523205976</v>
       </c>
     </row>
     <row r="23">
@@ -5109,16 +5229,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001722025680334478</v>
+        <v>0.0001767969376464119</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02939867698475011</v>
+        <v>0.02707568159980925</v>
       </c>
       <c r="E23" t="n">
-        <v>1.054096378739578e-05</v>
+        <v>1.059598114613674e-05</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8114822987142869</v>
+        <v>0.8178606164523486</v>
       </c>
     </row>
     <row r="24">
@@ -5129,16 +5249,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003837187940931769</v>
+        <v>0.0003830639061734199</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.00631343165974052</v>
+        <v>-0.005851735676311892</v>
       </c>
       <c r="E24" t="n">
-        <v>1.052028977014214e-05</v>
+        <v>1.023087298202126e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9513717728265446</v>
+        <v>0.9530899495023613</v>
       </c>
     </row>
     <row r="25">
@@ -5149,16 +5269,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0009464036634520331</v>
+        <v>0.0009517296847824525</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03289061818358796</v>
+        <v>0.03034205238054988</v>
       </c>
       <c r="E25" t="n">
-        <v>1.247086062759197e-05</v>
+        <v>1.24672210142826e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.989349222015722</v>
+        <v>0.9894729256239529</v>
       </c>
     </row>
     <row r="26">
@@ -5169,16 +5289,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001922470088918773</v>
+        <v>0.001936979471988713</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1220759954049979</v>
+        <v>0.1140709143104868</v>
       </c>
       <c r="E26" t="n">
-        <v>1.734226810433011e-05</v>
+        <v>1.825440679206847e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9949800582816641</v>
+        <v>0.9945236372007654</v>
       </c>
     </row>
     <row r="27">
@@ -5189,16 +5309,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002834229081581685</v>
+        <v>0.002846568259417853</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05964918120381291</v>
+        <v>0.054680835233202</v>
       </c>
       <c r="E27" t="n">
-        <v>2.790106688772344e-05</v>
+        <v>2.744343503787065e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9940274227487573</v>
+        <v>0.9942703261270693</v>
       </c>
     </row>
     <row r="28">
@@ -5209,16 +5329,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002898712527560802</v>
+        <v>0.002954356910193798</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3431052610730703</v>
+        <v>0.3168630779095616</v>
       </c>
       <c r="E28" t="n">
-        <v>5.313340028990311e-05</v>
+        <v>5.260475352421287e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9795937768583034</v>
+        <v>0.9807220134702338</v>
       </c>
     </row>
     <row r="29">
@@ -5229,16 +5349,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001672600903060682</v>
+        <v>0.001698768122745412</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3288169446983868</v>
+        <v>0.3152736491388041</v>
       </c>
       <c r="E29" t="n">
-        <v>4.96057049430844e-05</v>
+        <v>5.016018936394834e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9482858311949376</v>
+        <v>0.9487164310993256</v>
       </c>
     </row>
     <row r="30">
@@ -5249,16 +5369,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003467753555619704</v>
+        <v>0.0003419313421489506</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.03243906652881531</v>
+        <v>-0.02994439962111009</v>
       </c>
       <c r="E30" t="n">
-        <v>1.15564747246866e-05</v>
+        <v>1.145836778641541e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9483896074344957</v>
+        <v>0.946836601433323</v>
       </c>
     </row>
     <row r="31">
@@ -5269,16 +5389,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0008675308928499521</v>
+        <v>0.0008561348468244264</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.04466775274990287</v>
+        <v>-0.04016631456982014</v>
       </c>
       <c r="E31" t="n">
-        <v>2.550736574913968e-05</v>
+        <v>2.510856395115142e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9690051782541096</v>
+        <v>0.9683498842841248</v>
       </c>
     </row>
     <row r="32">
@@ -5289,16 +5409,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001745596598856768</v>
+        <v>0.001730293791019063</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.08539313713068486</v>
+        <v>-0.07812430340777476</v>
       </c>
       <c r="E32" t="n">
-        <v>2.108965070079562e-05</v>
+        <v>2.205728857591041e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9934744038140815</v>
+        <v>0.9925802713631882</v>
       </c>
     </row>
     <row r="33">
@@ -5309,16 +5429,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003882395702543811</v>
+        <v>0.003874476743890982</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0650228222729895</v>
+        <v>-0.05921568525371024</v>
       </c>
       <c r="E33" t="n">
-        <v>4.691720025117606e-05</v>
+        <v>5.112393127973244e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9954932383585041</v>
+        <v>0.9948038571362766</v>
       </c>
     </row>
     <row r="34">
@@ -5329,16 +5449,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006022235463017628</v>
+        <v>0.006039379286361409</v>
       </c>
       <c r="D34" t="n">
-        <v>0.07258869473603879</v>
+        <v>0.06701695214931003</v>
       </c>
       <c r="E34" t="n">
-        <v>8.159522217645689e-05</v>
+        <v>7.728183641602217e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9945229079416756</v>
+        <v>0.9949495160454805</v>
       </c>
     </row>
     <row r="35">
@@ -5349,16 +5469,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005414733192349747</v>
+        <v>0.005502399823520278</v>
       </c>
       <c r="D35" t="n">
-        <v>0.187846097478731</v>
+        <v>0.1665030774040035</v>
       </c>
       <c r="E35" t="n">
-        <v>9.657530104153475e-05</v>
+        <v>9.718465744255904e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9905468986386179</v>
+        <v>0.9907281396783136</v>
       </c>
     </row>
     <row r="36">
@@ -5369,16 +5489,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00526846354099629</v>
+        <v>0.005423152473174367</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5167055440000137</v>
+        <v>0.4709394932111828</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001269496607863454</v>
+        <v>0.0001551754947973401</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9823188981996667</v>
+        <v>0.9760268195632278</v>
       </c>
     </row>
     <row r="37">
@@ -5389,16 +5509,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0009481272527492037</v>
+        <v>0.0009320753009069319</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.02121550765544289</v>
+        <v>-0.01760381849093173</v>
       </c>
       <c r="E37" t="n">
-        <v>5.166300320718931e-05</v>
+        <v>4.806360337757931e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9439464174325526</v>
+        <v>0.9471126753402288</v>
       </c>
     </row>
     <row r="38">
@@ -5409,16 +5529,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001208238499149463</v>
+        <v>0.001311544954860391</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0666789737240395</v>
+        <v>0.05132829098462732</v>
       </c>
       <c r="E38" t="n">
-        <v>9.372146435336483e-05</v>
+        <v>0.0001081201987217719</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9223079172922427</v>
+        <v>0.9131230346605573</v>
       </c>
     </row>
     <row r="39">
@@ -5429,16 +5549,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003407024358545448</v>
+        <v>0.003506310555601021</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07118672276216598</v>
+        <v>0.05612625992168263</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001493833608070349</v>
+        <v>0.0001730612195863432</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9719715684830337</v>
+        <v>0.967019147980731</v>
       </c>
     </row>
     <row r="40">
@@ -5449,16 +5569,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.006525808555291658</v>
+        <v>0.006856465632848347</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1089538073938503</v>
+        <v>0.07256592206157542</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002481487393181031</v>
+        <v>0.0002263054854138223</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9801582611718719</v>
+        <v>0.9849774424946618</v>
       </c>
     </row>
     <row r="41">
@@ -5469,16 +5589,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01185447483118439</v>
+        <v>0.0120431640066688</v>
       </c>
       <c r="D41" t="n">
-        <v>0.164496445260929</v>
+        <v>0.1338746188638102</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002283179300088704</v>
+        <v>0.000257813658869609</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9948335307457747</v>
+        <v>0.9936249854161406</v>
       </c>
     </row>
     <row r="42">
@@ -5489,16 +5609,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01543743351277951</v>
+        <v>0.01578054203905483</v>
       </c>
       <c r="D42" t="n">
-        <v>0.117962695207807</v>
+        <v>0.08539790635557543</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0004054112913387799</v>
+        <v>0.0003690923810729367</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9904369516658922</v>
+        <v>0.9923995219363606</v>
       </c>
     </row>
     <row r="43">
@@ -5509,16 +5629,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01546506666235702</v>
+        <v>0.01594905944815261</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3804977717065086</v>
+        <v>0.3178511338104111</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0004735664198234177</v>
+        <v>0.0004952967360718256</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9870424741717575</v>
+        <v>0.9866781564869426</v>
       </c>
     </row>
     <row r="44">
@@ -5529,16 +5649,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001361064642500137</v>
+        <v>0.001474435852459965</v>
       </c>
       <c r="D44" t="n">
-        <v>0.04515095777122481</v>
+        <v>0.03211326862584467</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001487912348485626</v>
+        <v>0.0001400400911964733</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9028878619097808</v>
+        <v>0.9172547672182512</v>
       </c>
     </row>
     <row r="45">
@@ -5549,16 +5669,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.002812157786749078</v>
+        <v>0.002887897605879234</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03087271303409572</v>
+        <v>0.023904757622351</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001354916389787947</v>
+        <v>0.0002211063298614175</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9707061301585734</v>
+        <v>0.94988669077291</v>
       </c>
     </row>
     <row r="46">
@@ -5569,16 +5689,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00623047036929162</v>
+        <v>0.00617254182540551</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.03732697741730789</v>
+        <v>-0.02598517829855385</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005378201535551229</v>
+        <v>0.0005471531215065217</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9572054100170363</v>
+        <v>0.95497705819388</v>
       </c>
     </row>
     <row r="47">
@@ -5589,16 +5709,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01274479825048714</v>
+        <v>0.01291916048895058</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04968217266617836</v>
+        <v>0.03486138239678593</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0002259119773621837</v>
+        <v>0.0002018806486765827</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9981183196013788</v>
+        <v>0.9982936145879031</v>
       </c>
     </row>
     <row r="48">
@@ -5609,16 +5729,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0228387584021772</v>
+        <v>0.02522975519413041</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2533122621749866</v>
+        <v>0.1187802651414562</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00129106244527952</v>
+        <v>0.001092006659187045</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9811872339169522</v>
+        <v>0.988884694441608</v>
       </c>
     </row>
     <row r="49">
@@ -5629,16 +5749,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03030933071738421</v>
+        <v>0.03180259585119757</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3935040853363336</v>
+        <v>0.2671041590146486</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0003279156671265275</v>
+        <v>0.001152745014829158</v>
       </c>
       <c r="F49" t="n">
-        <v>0.999298192519564</v>
+        <v>0.9921786362014935</v>
       </c>
     </row>
     <row r="50">
@@ -5649,16 +5769,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03187845768277089</v>
+        <v>0.02971213513449341</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3308758228280708</v>
+        <v>-0.1467384062244845</v>
       </c>
       <c r="E50" t="n">
-        <v>0.004936551957325687</v>
+        <v>0.004023188403594524</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8742166529297881</v>
+        <v>0.8862555938229987</v>
       </c>
     </row>
     <row r="51">
@@ -5669,16 +5789,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09644322254222905</v>
+        <v>0.06745741520969262</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.172999364053341</v>
+        <v>-0.8686380340892015</v>
       </c>
       <c r="E51" t="n">
-        <v>0.03292841260715235</v>
+        <v>0.02532756985017048</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8109339180167362</v>
+        <v>0.7027846798826166</v>
       </c>
     </row>
     <row r="52">
@@ -5689,16 +5809,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00407104618485207</v>
+        <v>0.003656237121307809</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.02905464381106707</v>
+        <v>-0.01038823595157529</v>
       </c>
       <c r="E52" t="n">
-        <v>0.001065360935104604</v>
+        <v>0.0006600657748147589</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8795340938565409</v>
+        <v>0.910933637492361</v>
       </c>
     </row>
     <row r="53">
@@ -5709,16 +5829,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.009949199026401458</v>
+        <v>0.009060716042042997</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.08870334040261507</v>
+        <v>-0.03983677626289989</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0004089492359797071</v>
+        <v>0.0005786260159466892</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9949570096664733</v>
+        <v>0.9839489506233197</v>
       </c>
     </row>
     <row r="54">
@@ -5729,16 +5849,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01614767612621374</v>
+        <v>0.0165925872445787</v>
       </c>
       <c r="D54" t="n">
-        <v>0.06879495649774814</v>
+        <v>0.04716230300838475</v>
       </c>
       <c r="E54" t="n">
-        <v>0.001149958213314325</v>
+        <v>0.002731475217005766</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9801169973366607</v>
+        <v>0.9485869407889898</v>
       </c>
     </row>
     <row r="55">
@@ -5749,16 +5869,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03339576796216736</v>
+        <v>0.03982092787307945</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2963520994842563</v>
+        <v>0.09123396912956527</v>
       </c>
       <c r="E55" t="n">
-        <v>0.001753863213203088</v>
+        <v>0.002893405540095763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9945140796242438</v>
+        <v>0.9895512543854138</v>
       </c>
     </row>
     <row r="56">
@@ -5769,16 +5889,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.04167295313193533</v>
+        <v>0.05164586408042905</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5768614471007218</v>
+        <v>0.2242748339227816</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001064243929351533</v>
+        <v>0.006465582645996871</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9980472521607722</v>
+        <v>0.9696072438215457</v>
       </c>
     </row>
     <row r="57">
@@ -5789,16 +5909,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07028880725628703</v>
+        <v>0.07447879482202589</v>
       </c>
       <c r="D57" t="n">
-        <v>0.02841732632245542</v>
+        <v>0.01681928252113551</v>
       </c>
       <c r="E57" t="n">
-        <v>0.007828264928397929</v>
+        <v>0.005423048110431499</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9757927059688559</v>
+        <v>0.9895076974252245</v>
       </c>
     </row>
   </sheetData>

--- a/kinetics/fit_velocities.xlsx
+++ b/kinetics/fit_velocities.xlsx
@@ -511,7 +511,7 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002066797928399725</v>
+        <v>0.0002036330247785941</v>
       </c>
       <c r="D4" t="n">
         <v>-0.03343982493568712</v>
@@ -520,7 +520,7 @@
         <v>0.0003041495537692709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06188423975142914</v>
+        <v>0.06018215103766274</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009918732454877407</v>
+        <v>0.0009851586227469131</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0008786850882566213</v>
+        <v>-0.0008786850882566352</v>
       </c>
       <c r="E5" t="n">
         <v>0.0002796517194686669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6770704705996078</v>
+        <v>0.674092979139321</v>
       </c>
     </row>
     <row r="6">
@@ -571,16 +571,16 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00110015189170905</v>
+        <v>0.001089450415620811</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0260867396401473</v>
+        <v>0.02608673964014731</v>
       </c>
       <c r="E7" t="n">
         <v>0.0003612762192180836</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6071533264410046</v>
+        <v>0.6024807091095006</v>
       </c>
     </row>
     <row r="8">
@@ -591,16 +591,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004942942175495736</v>
+        <v>0.0004859594479481378</v>
       </c>
       <c r="D8" t="n">
         <v>0.1443977643356594</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000979765648443344</v>
+        <v>0.0009797656484433442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05982404717506882</v>
+        <v>0.0579394626696411</v>
       </c>
     </row>
     <row r="9">
@@ -751,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>1.621585663973099e-05</v>
+        <v>1.572924543661062e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.03400585023613803</v>
+        <v>-0.03400585023613802</v>
       </c>
       <c r="E16" t="n">
         <v>4.459726312051874e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09496393821858118</v>
+        <v>0.08985446471998564</v>
       </c>
     </row>
     <row r="17">
@@ -771,16 +771,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002064349907255227</v>
+        <v>0.0002047132164636739</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.01617406453809964</v>
+        <v>-0.01617406453809966</v>
       </c>
       <c r="E17" t="n">
-        <v>4.629923784119111e-06</v>
+        <v>4.629923784119093e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9403976814296371</v>
+        <v>0.9394518352329292</v>
       </c>
     </row>
     <row r="18">
@@ -791,16 +791,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004247609324866343</v>
+        <v>0.0004217141644252561</v>
       </c>
       <c r="D18" t="n">
         <v>-0.04418565753966186</v>
       </c>
       <c r="E18" t="n">
-        <v>4.860980756298335e-06</v>
+        <v>4.860980756298202e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9837661660390636</v>
+        <v>0.9835346250110955</v>
       </c>
     </row>
     <row r="19">
@@ -811,16 +811,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0007256801620756466</v>
+        <v>0.0007189655393348189</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07022478521595588</v>
+        <v>-0.07022478521595599</v>
       </c>
       <c r="E19" t="n">
-        <v>5.965308847684862e-06</v>
+        <v>5.96530884768479e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.991557639837634</v>
+        <v>0.9914005746782927</v>
       </c>
     </row>
     <row r="20">
@@ -831,16 +831,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.000897930436002321</v>
+        <v>0.0008884677991359104</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002278639874260691</v>
+        <v>0.002278639874260802</v>
       </c>
       <c r="E20" t="n">
-        <v>9.841552410423922e-06</v>
+        <v>9.841552410423754e-06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9850896399431724</v>
+        <v>0.9847752039116656</v>
       </c>
     </row>
     <row r="21">
@@ -851,16 +851,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008305976706377661</v>
+        <v>0.0008198961945495278</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2529280392913571</v>
+        <v>0.252928039291357</v>
       </c>
       <c r="E21" t="n">
-        <v>1.377738717042347e-05</v>
+        <v>1.377738717042337e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9664940423739194</v>
+        <v>0.9656439249725713</v>
       </c>
     </row>
     <row r="22">
@@ -871,16 +871,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0003085698864542946</v>
+        <v>0.0003002351168528586</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4633877042366994</v>
+        <v>0.4633877042366991</v>
       </c>
       <c r="E22" t="n">
-        <v>2.067505404011238e-05</v>
+        <v>2.067505404011239e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6387075849514779</v>
+        <v>0.6259764915616287</v>
       </c>
     </row>
     <row r="23">
@@ -891,16 +891,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>5.893715058888795e-05</v>
+        <v>5.84505393857676e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05264560661995253</v>
+        <v>-0.05264560661995255</v>
       </c>
       <c r="E23" t="n">
-        <v>3.713649578803446e-06</v>
+        <v>3.713649578803443e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6683206340327852</v>
+        <v>0.6646348559648121</v>
       </c>
     </row>
     <row r="24">
@@ -911,16 +911,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002321808512417102</v>
+        <v>0.0002304590769798614</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03545328492594266</v>
+        <v>-0.03545328492594263</v>
       </c>
       <c r="E24" t="n">
-        <v>4.90801180255446e-06</v>
+        <v>4.908011802554495e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.946698360372256</v>
+        <v>0.9459421600851785</v>
       </c>
     </row>
     <row r="25">
@@ -931,16 +931,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0006318300396228363</v>
+        <v>0.0006287832715614581</v>
       </c>
       <c r="D25" t="n">
         <v>-0.08584148722027629</v>
       </c>
       <c r="E25" t="n">
-        <v>6.098774160438206e-06</v>
+        <v>6.098774160437908e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.988578649098534</v>
+        <v>0.988468976068365</v>
       </c>
     </row>
     <row r="26">
@@ -951,16 +951,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001293972008266505</v>
+        <v>0.001287257385525677</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.06195113658658036</v>
+        <v>-0.06195113658658014</v>
       </c>
       <c r="E26" t="n">
-        <v>7.292167642024154e-06</v>
+        <v>7.292167642024558e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9964240932186318</v>
+        <v>0.9963868256036597</v>
       </c>
     </row>
     <row r="27">
@@ -971,16 +971,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002027081668054414</v>
+        <v>0.002017619031188004</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.07421277640712276</v>
+        <v>-0.07421277640712343</v>
       </c>
       <c r="E27" t="n">
-        <v>1.578362268094247e-05</v>
+        <v>1.578362268094246e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9950531241832966</v>
+        <v>0.9950068458925934</v>
       </c>
     </row>
     <row r="28">
@@ -991,16 +991,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002326861761781762</v>
+        <v>0.002316160285693525</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08712767445681724</v>
+        <v>-0.08712767445681791</v>
       </c>
       <c r="E28" t="n">
-        <v>2.762641162832023e-05</v>
+        <v>2.762641162831835e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9913359621279403</v>
+        <v>0.9912564170038262</v>
       </c>
     </row>
     <row r="29">
@@ -1011,16 +1011,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001608720148898064</v>
+        <v>0.001600385379296627</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3557950142143778</v>
+        <v>0.3557950142143779</v>
       </c>
       <c r="E29" t="n">
-        <v>4.816707023444801e-05</v>
+        <v>4.816707023444817e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9473450345343329</v>
+        <v>0.9468243949089428</v>
       </c>
     </row>
     <row r="30">
@@ -1031,16 +1031,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001667188646155453</v>
+        <v>0.0001662322534124249</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.06370036764965314</v>
+        <v>-0.06370036764965316</v>
       </c>
       <c r="E30" t="n">
-        <v>8.717233867979127e-06</v>
+        <v>8.717233867979132e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>0.815051417740515</v>
+        <v>0.8141685465940599</v>
       </c>
     </row>
     <row r="31">
@@ -1051,16 +1051,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005811561670510231</v>
+        <v>0.0005794343927891739</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1037929866329606</v>
+        <v>-0.1037929866329603</v>
       </c>
       <c r="E31" t="n">
-        <v>8.048207399309667e-06</v>
+        <v>8.048207399310042e-06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9830323023898313</v>
+        <v>0.9829330379823557</v>
       </c>
     </row>
     <row r="32">
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001482264166965039</v>
+        <v>0.001479217398903661</v>
       </c>
       <c r="D32" t="n">
         <v>-0.04878910290409655</v>
       </c>
       <c r="E32" t="n">
-        <v>1.256484919122508e-05</v>
+        <v>1.256484919122468e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.995351070230918</v>
+        <v>0.9953319890450236</v>
       </c>
     </row>
     <row r="33">
@@ -1091,16 +1091,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00312087062405688</v>
+        <v>0.003114156001316051</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1244964155406056</v>
       </c>
       <c r="E33" t="n">
-        <v>2.765255338090741e-05</v>
+        <v>2.765255338090659e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9953893310435695</v>
+        <v>0.9953695190819013</v>
       </c>
     </row>
     <row r="34">
@@ -1111,16 +1111,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005152630721264479</v>
+        <v>0.00514316808439807</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07860932022157918</v>
+        <v>-0.07860932022158051</v>
       </c>
       <c r="E34" t="n">
-        <v>2.942532932812065e-05</v>
+        <v>2.942532932811507e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.998112043790193</v>
+        <v>0.9981051034784431</v>
       </c>
     </row>
     <row r="35">
@@ -1131,16 +1131,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005901955093417277</v>
+        <v>0.005891253617329039</v>
       </c>
       <c r="D35" t="n">
-        <v>0.005121083777652524</v>
+        <v>0.00512108377765208</v>
       </c>
       <c r="E35" t="n">
-        <v>9.70071398375188e-05</v>
+        <v>9.700713983751669e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9919604597379778</v>
+        <v>0.9919314613997698</v>
       </c>
     </row>
     <row r="36">
@@ -1151,16 +1151,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005705253774844659</v>
+        <v>0.005696919005243221</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0797123430590414</v>
+        <v>-0.07971234305904096</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001314072377368927</v>
+        <v>0.0001314072377368961</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9843342039021774</v>
+        <v>0.9842890519792312</v>
       </c>
     </row>
     <row r="37">
@@ -1171,16 +1171,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00109267330202125</v>
+        <v>0.00109218669081813</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.002754344303374817</v>
+        <v>-0.002754344303374873</v>
       </c>
       <c r="E37" t="n">
-        <v>7.306721621772189e-05</v>
+        <v>7.306721621772177e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9332311826565748</v>
+        <v>0.9331756499248673</v>
       </c>
     </row>
     <row r="38">
@@ -1191,16 +1191,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.002210197033083216</v>
+        <v>0.002208475258821368</v>
       </c>
       <c r="D38" t="n">
         <v>0.05637137827491062</v>
       </c>
       <c r="E38" t="n">
-        <v>0.000122746631818973</v>
+        <v>0.0001227466318189737</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9586070993360108</v>
+        <v>0.9585452092066278</v>
       </c>
     </row>
     <row r="39">
@@ -1211,16 +1211,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.005379404078927708</v>
+        <v>0.005376357310866329</v>
       </c>
       <c r="D39" t="n">
         <v>0.04631095245540728</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001267380656089606</v>
+        <v>0.0001267380656089652</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9917427373232157</v>
+        <v>0.9917334533181467</v>
       </c>
     </row>
     <row r="40">
@@ -1231,16 +1231,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.009972988471972389</v>
+        <v>0.009966273849231561</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.02077476760704089</v>
+        <v>-0.02077476760704111</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002289866702139264</v>
+        <v>0.0002289866702139234</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9926733713913378</v>
+        <v>0.9926635681130386</v>
       </c>
     </row>
     <row r="41">
@@ -1251,16 +1251,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01701544414391577</v>
+        <v>0.01700598150704937</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1285216483659899</v>
+        <v>0.1285216483659892</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002205238809878187</v>
+        <v>0.0002205238809878151</v>
       </c>
       <c r="F41" t="n">
-        <v>0.997653974936683</v>
+        <v>0.9976513695467645</v>
       </c>
     </row>
     <row r="42">
@@ -1271,16 +1271,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02266560342250378</v>
+        <v>0.02265490194641553</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3526144955146293</v>
+        <v>0.3526144955146306</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0004920789556532591</v>
+        <v>0.0004920789556532723</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9934444874501255</v>
+        <v>0.9934383333915889</v>
       </c>
     </row>
     <row r="43">
@@ -1291,16 +1291,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.02561597951300466</v>
+        <v>0.02560764474340323</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3999097658821769</v>
+        <v>0.399909765882176</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0006488372489791191</v>
+        <v>0.0006488372489791067</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9910978647101609</v>
+        <v>0.9910921204666361</v>
       </c>
     </row>
     <row r="44">
@@ -1311,16 +1311,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001785748972083108</v>
+        <v>0.001785262360879988</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01424007610474572</v>
+        <v>-0.01424007610474574</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001630205544062265</v>
+        <v>0.0001630205544062261</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9448788725307488</v>
+        <v>0.9448504769723701</v>
       </c>
     </row>
     <row r="45">
@@ -1331,16 +1331,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.004018346887248028</v>
+        <v>0.00401662511298618</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005988805854920315</v>
+        <v>-0.005988805854920259</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001620501534752195</v>
+        <v>0.0001620501534752174</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9903364200358433</v>
+        <v>0.9903282135886887</v>
       </c>
     </row>
     <row r="46">
@@ -1351,16 +1351,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.008891393804213213</v>
+        <v>0.008888347036151835</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.03575761660714938</v>
+        <v>-0.03575761660714916</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000263859035075208</v>
+        <v>0.0002638590350752062</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9930040730649258</v>
+        <v>0.9929993096652072</v>
       </c>
     </row>
     <row r="47">
@@ -1371,16 +1371,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01768304580982624</v>
+        <v>0.01767633118708541</v>
       </c>
       <c r="D47" t="n">
         <v>0.05900594188401331</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0005830224752495374</v>
+        <v>0.0005830224752495346</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9935198620098215</v>
+        <v>0.9935149698500653</v>
       </c>
     </row>
     <row r="48">
@@ -1391,16 +1391,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02544544042696292</v>
+        <v>0.02543597779009651</v>
       </c>
       <c r="D48" t="n">
         <v>0.1650838067548952</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001318021503089539</v>
+        <v>0.001318021503089541</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9841568829342399</v>
+        <v>0.9841452798257505</v>
       </c>
     </row>
     <row r="49">
@@ -1411,16 +1411,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03825256439971473</v>
+        <v>0.0382418629236265</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5307766392998574</v>
+        <v>0.530776639299857</v>
       </c>
       <c r="E49" t="n">
-        <v>0.002964648763695965</v>
+        <v>0.002964648763695972</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9652143281163967</v>
+        <v>0.965195534467796</v>
       </c>
     </row>
     <row r="50">
@@ -1431,16 +1431,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03743799790642453</v>
+        <v>0.03742966313682308</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6784469493203307</v>
+        <v>0.6784469493203313</v>
       </c>
       <c r="E50" t="n">
-        <v>0.002922312076682579</v>
+        <v>0.002922312076682583</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9647316038290692</v>
+        <v>0.9647164493357071</v>
       </c>
     </row>
     <row r="51">
@@ -1451,16 +1451,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002429107965784368</v>
+        <v>0.002428621354581247</v>
       </c>
       <c r="D51" t="n">
         <v>-0.02246244008618048</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0003412543227808501</v>
+        <v>0.0003412543227808499</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8636404258181274</v>
+        <v>0.8635932313971284</v>
       </c>
     </row>
     <row r="52">
@@ -1471,16 +1471,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.006258293212662747</v>
+        <v>0.006256571438400898</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.01409301919086378</v>
+        <v>-0.01409301919086373</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0009482288757508825</v>
+        <v>0.000948228875750884</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9355666757370785</v>
+        <v>0.9355334939760045</v>
       </c>
     </row>
     <row r="53">
@@ -1491,16 +1491,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01034792823791227</v>
+        <v>0.01034488146985089</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.00775424549650211</v>
+        <v>-0.007754245496502055</v>
       </c>
       <c r="E53" t="n">
-        <v>0.00038099435715485</v>
+        <v>0.0003809943571548494</v>
       </c>
       <c r="F53" t="n">
-        <v>0.994606859780006</v>
+        <v>0.9946036996889062</v>
       </c>
     </row>
     <row r="54">
@@ -1511,16 +1511,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02676310308295157</v>
+        <v>0.02675638846021074</v>
       </c>
       <c r="D54" t="n">
         <v>0.08919282355799296</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00319558185696926</v>
+        <v>0.00319558185696928</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9722765815049113</v>
+        <v>0.9722630511504846</v>
       </c>
     </row>
     <row r="55">
@@ -1531,16 +1531,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.04732323654130814</v>
+        <v>0.04731377390444173</v>
       </c>
       <c r="D55" t="n">
         <v>0.09857414539042542</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003011737924075016</v>
+        <v>0.003011737924075001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9919645239153858</v>
+        <v>0.9919613352836537</v>
       </c>
     </row>
     <row r="56">
@@ -1551,16 +1551,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.04419940743382526</v>
+        <v>0.04418870595773702</v>
       </c>
       <c r="D56" t="n">
         <v>-0.1694905856805076</v>
       </c>
       <c r="E56" t="n">
-        <v>0.003672265791131092</v>
+        <v>0.003672265791131101</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9731300899279662</v>
+        <v>0.9731174237249739</v>
       </c>
     </row>
     <row r="57">
@@ -1571,16 +1571,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07112134243455477</v>
+        <v>0.07111300766495333</v>
       </c>
       <c r="D57" t="n">
         <v>-0.06238928214878392</v>
       </c>
       <c r="E57" t="n">
-        <v>0.004233381605489921</v>
+        <v>0.004233381605489879</v>
       </c>
       <c r="F57" t="n">
-        <v>0.989482696550156</v>
+        <v>0.9894802569899799</v>
       </c>
     </row>
   </sheetData>
@@ -1637,16 +1637,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>5.628656830937105e-05</v>
+        <v>5.579995710625068e-05</v>
       </c>
       <c r="D2" t="n">
         <v>-0.005163657578485387</v>
       </c>
       <c r="E2" t="n">
-        <v>2.643310343664179e-05</v>
+        <v>2.64331034366418e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1848157629210962</v>
+        <v>0.1822137780562366</v>
       </c>
     </row>
     <row r="3">
@@ -1657,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>7.205419769015503e-05</v>
+        <v>7.033242342830622e-05</v>
       </c>
       <c r="D3" t="n">
         <v>-0.01273595573324893</v>
@@ -1666,7 +1666,7 @@
         <v>4.661692172466613e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1660344647037607</v>
+        <v>0.1594443719253838</v>
       </c>
     </row>
     <row r="4">
@@ -1677,16 +1677,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008161805919785038</v>
+        <v>0.0008131338239171255</v>
       </c>
       <c r="D4" t="n">
         <v>-0.07834984850128637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002831264795740749</v>
+        <v>0.0002831264795740748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3899635316753821</v>
+        <v>0.3881855984001254</v>
       </c>
     </row>
     <row r="5">
@@ -1697,7 +1697,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000199917643695579</v>
+        <v>0.0001932030209547512</v>
       </c>
       <c r="D5" t="n">
         <v>-0.004558089425062846</v>
@@ -1706,7 +1706,7 @@
         <v>0.0001061860756082395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2616983331835226</v>
+        <v>0.2487130311947823</v>
       </c>
     </row>
     <row r="6">
@@ -1717,16 +1717,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003468664934470913</v>
+        <v>0.000337403856580681</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04991926274700873</v>
+        <v>0.04991926274700872</v>
       </c>
       <c r="E6" t="n">
         <v>0.000531747739814807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.096150095479599</v>
+        <v>0.09144883509557718</v>
       </c>
     </row>
     <row r="7">
@@ -1737,7 +1737,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002046560787841618</v>
+        <v>0.0001939546026959233</v>
       </c>
       <c r="D7" t="n">
         <v>0.07049220324967641</v>
@@ -1746,7 +1746,7 @@
         <v>0.0005186153909323345</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03747241545762591</v>
+        <v>0.03378494279221504</v>
       </c>
     </row>
     <row r="8">
@@ -1757,7 +1757,7 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000680025019008728</v>
+        <v>0.0006716902494072919</v>
       </c>
       <c r="D8" t="n">
         <v>0.1952616911206328</v>
@@ -1766,7 +1766,7 @@
         <v>0.0004381318241622798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.231435721242002</v>
+        <v>0.2270776402338947</v>
       </c>
     </row>
     <row r="9">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>1.748872353998049e-06</v>
+        <v>1.262261150877684e-06</v>
       </c>
       <c r="D16" t="n">
         <v>-0.05297810747510917</v>
@@ -1926,7 +1926,7 @@
         <v>3.67638024569158e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001792773985524489</v>
+        <v>0.0009347186458834545</v>
       </c>
     </row>
     <row r="17">
@@ -1937,16 +1937,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>4.580987992056485e-05</v>
+        <v>4.408810565871607e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02475176148126029</v>
+        <v>-0.0247517614812603</v>
       </c>
       <c r="E17" t="n">
-        <v>4.179462055758129e-06</v>
+        <v>4.179462055758128e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4880903979440749</v>
+        <v>0.4689731848557779</v>
       </c>
     </row>
     <row r="18">
@@ -1957,16 +1957,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>5.938380911222198e-05</v>
+        <v>5.633704105084367e-05</v>
       </c>
       <c r="D18" t="n">
         <v>-0.07544155268524905</v>
       </c>
       <c r="E18" t="n">
-        <v>4.231228251251504e-06</v>
+        <v>4.231228251251505e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6098725900112486</v>
+        <v>0.5845397736299829</v>
       </c>
     </row>
     <row r="19">
@@ -1977,16 +1977,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>8.489547614818244e-05</v>
+        <v>7.81808534073547e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06512554727209036</v>
+        <v>0.06512554727209037</v>
       </c>
       <c r="E19" t="n">
-        <v>5.436532408102335e-06</v>
+        <v>5.436532408102329e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6593225745605525</v>
+        <v>0.6213976525628583</v>
       </c>
     </row>
     <row r="20">
@@ -2057,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001155003975527648</v>
+        <v>0.0001150137863496445</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05503022626042029</v>
+        <v>-0.05503022626042033</v>
       </c>
       <c r="E23" t="n">
-        <v>4.639926820762821e-06</v>
+        <v>4.639926820762811e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8527484079560501</v>
+        <v>0.8516849534192144</v>
       </c>
     </row>
     <row r="24">
@@ -2077,16 +2077,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002220332215753877</v>
+        <v>0.0002203114473135389</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008566043240932047</v>
+        <v>0.008566043240931964</v>
       </c>
       <c r="E24" t="n">
-        <v>6.476145837589664e-06</v>
+        <v>6.476145837589652e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9252231102969609</v>
+        <v>0.9241387653322993</v>
       </c>
     </row>
     <row r="25">
@@ -2097,16 +2097,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007732086049437432</v>
+        <v>0.007729039281376056</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.169389275228733</v>
+        <v>-2.169389275228736</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0009810619139538747</v>
+        <v>0.0009810619139538743</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3507064604164092</v>
+        <v>0.3505269903549129</v>
       </c>
     </row>
     <row r="26">
@@ -2117,16 +2117,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0007842167826253947</v>
+        <v>0.0007775021598845671</v>
       </c>
       <c r="D26" t="n">
         <v>0.1081840487302492</v>
       </c>
       <c r="E26" t="n">
-        <v>2.235298011661702e-05</v>
+        <v>2.235298011661691e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9520435418973305</v>
+        <v>0.9512522001801157</v>
       </c>
     </row>
     <row r="27">
@@ -2137,16 +2137,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005459299151155997</v>
+        <v>0.0005364672782491894</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1509938202787462</v>
+        <v>0.1509938202787463</v>
       </c>
       <c r="E27" t="n">
-        <v>2.547939676237555e-05</v>
+        <v>2.547939676237561e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8810180714839072</v>
+        <v>0.8773032061302061</v>
       </c>
     </row>
     <row r="28">
@@ -2157,16 +2157,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003641574810850646</v>
+        <v>0.0003534560049968263</v>
       </c>
       <c r="D28" t="n">
-        <v>0.236236560570168</v>
+        <v>0.2362365605701679</v>
       </c>
       <c r="E28" t="n">
-        <v>3.670407978660341e-05</v>
+        <v>3.67040797866034e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6135507937046042</v>
+        <v>0.5993140576725877</v>
       </c>
     </row>
     <row r="29">
@@ -2197,16 +2197,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0002850703145352181</v>
+        <v>0.0002845837033320976</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003993898387898279</v>
+        <v>-0.003993898387898237</v>
       </c>
       <c r="E30" t="n">
-        <v>1.719656288003925e-05</v>
+        <v>1.719656288003929e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8898972658624508</v>
+        <v>0.8895620322499147</v>
       </c>
     </row>
     <row r="31">
@@ -2217,16 +2217,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0007499003703418351</v>
+        <v>0.0007481785960799862</v>
       </c>
       <c r="D31" t="n">
         <v>0.002753127522024362</v>
       </c>
       <c r="E31" t="n">
-        <v>2.771119970806042e-05</v>
+        <v>2.771119970806065e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9581323114461171</v>
+        <v>0.9579475033244074</v>
       </c>
     </row>
     <row r="32">
@@ -2237,16 +2237,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0008645819153415167</v>
+        <v>0.0008615351472801388</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02902186282296104</v>
+        <v>-0.02902186282296149</v>
       </c>
       <c r="E32" t="n">
-        <v>2.523595440359163e-05</v>
+        <v>2.523595440359153e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9093544986460201</v>
+        <v>0.9087708328067223</v>
       </c>
     </row>
     <row r="33">
@@ -2257,16 +2257,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002459567829627863</v>
+        <v>0.002452853206887034</v>
       </c>
       <c r="D33" t="n">
-        <v>0.06634224786053888</v>
+        <v>0.06634224786053899</v>
       </c>
       <c r="E33" t="n">
-        <v>4.740792966926108e-05</v>
+        <v>4.740792966926294e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9886139574303013</v>
+        <v>0.9885522487136539</v>
       </c>
     </row>
     <row r="34">
@@ -2277,16 +2277,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002554696137585798</v>
+        <v>0.002545233500719388</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1025162742812357</v>
+        <v>0.1025162742812356</v>
       </c>
       <c r="E34" t="n">
-        <v>8.24850348824289e-05</v>
+        <v>8.248503488242869e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.969673749668542</v>
+        <v>0.9694547379515946</v>
       </c>
     </row>
     <row r="35">
@@ -2297,16 +2297,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001693242234872524</v>
+        <v>0.001682540758784286</v>
       </c>
       <c r="D35" t="n">
         <v>0.2942021996098321</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001358146958590824</v>
+        <v>0.0001358146958590821</v>
       </c>
       <c r="F35" t="n">
-        <v>0.838216943657637</v>
+        <v>0.836489989525419</v>
       </c>
     </row>
     <row r="36">
@@ -2317,16 +2317,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001009956733979327</v>
+        <v>0.001001621964377891</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2202647156769284</v>
+        <v>0.2202647156769285</v>
       </c>
       <c r="E36" t="n">
         <v>0.0001078532978239687</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7450880599703606</v>
+        <v>0.7419274234770703</v>
       </c>
     </row>
     <row r="37">
@@ -2337,16 +2337,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0001473176772068823</v>
+        <v>0.0001468310660037619</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.004661018338371598</v>
+        <v>-0.004661018338371594</v>
       </c>
       <c r="E37" t="n">
-        <v>1.741290292559487e-05</v>
+        <v>1.741290292559486e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7731593271735433</v>
+        <v>0.7719966756799519</v>
       </c>
     </row>
     <row r="38">
@@ -2357,16 +2357,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0003964976802027301</v>
+        <v>0.0003947759059408813</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.008845763699063862</v>
+        <v>-0.008845763699063848</v>
       </c>
       <c r="E38" t="n">
-        <v>1.891777204575704e-05</v>
+        <v>1.891777204575707e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.952306614030468</v>
+        <v>0.9519097373991275</v>
       </c>
     </row>
     <row r="39">
@@ -2377,16 +2377,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.000593926264534353</v>
+        <v>0.0005908794964729746</v>
       </c>
       <c r="D39" t="n">
-        <v>0.003021131573086921</v>
+        <v>0.003021131573086935</v>
       </c>
       <c r="E39" t="n">
-        <v>5.120942001051714e-05</v>
+        <v>5.120942001051732e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8996745021616125</v>
+        <v>0.898742246153012</v>
       </c>
     </row>
     <row r="40">
@@ -2397,16 +2397,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001182439295320993</v>
+        <v>0.001175724672580165</v>
       </c>
       <c r="D40" t="n">
         <v>0.0245322935701634</v>
       </c>
       <c r="E40" t="n">
-        <v>6.462498528644017e-05</v>
+        <v>6.462498528644015e-05</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9571156451523041</v>
+        <v>0.9566457138622231</v>
       </c>
     </row>
     <row r="41">
@@ -2417,16 +2417,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.002156404977928663</v>
+        <v>0.002146942341062254</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01040995619057256</v>
+        <v>0.01040995619057244</v>
       </c>
       <c r="E41" t="n">
-        <v>7.57416341029007e-05</v>
+        <v>7.574163410290059e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9759201936469593</v>
+        <v>0.9757126293143122</v>
       </c>
     </row>
     <row r="42">
@@ -2437,16 +2437,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.002898463651132493</v>
+        <v>0.002887762175044255</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04277620789650471</v>
+        <v>0.04277620789650483</v>
       </c>
       <c r="E42" t="n">
-        <v>4.851203970848812e-05</v>
+        <v>4.851203970848846e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9913906597831205</v>
+        <v>0.9913272869462654</v>
       </c>
     </row>
     <row r="43">
@@ -2457,16 +2457,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.002969718789253187</v>
+        <v>0.00296138401965175</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1049284071023305</v>
+        <v>0.1049284071023306</v>
       </c>
       <c r="E43" t="n">
-        <v>5.907837821483914e-05</v>
+        <v>5.907837821483897e-05</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9867229792033405</v>
+        <v>0.9866491372850861</v>
       </c>
     </row>
     <row r="44">
@@ -2477,16 +2477,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0004712840599903716</v>
+        <v>0.0004707974487872514</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.003150229572874988</v>
+        <v>-0.003150229572874974</v>
       </c>
       <c r="E44" t="n">
         <v>2.097789439413365e-05</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9492204178435816</v>
+        <v>0.9491207367104121</v>
       </c>
     </row>
     <row r="45">
@@ -2497,16 +2497,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0009218005177409231</v>
+        <v>0.0009200787434790743</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01231867414120799</v>
+        <v>0.01231867414120801</v>
       </c>
       <c r="E45" t="n">
-        <v>5.110394973649267e-05</v>
+        <v>5.110394973649275e-05</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9760019630682881</v>
+        <v>0.9759142276922969</v>
       </c>
     </row>
     <row r="46">
@@ -2517,16 +2517,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00144666281006591</v>
+        <v>0.001443616042004532</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.008552927894488666</v>
+        <v>-0.00855292789448861</v>
       </c>
       <c r="E46" t="n">
-        <v>4.903818365449162e-05</v>
+        <v>4.903818365449207e-05</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9819472952891001</v>
+        <v>0.9818723967977437</v>
       </c>
     </row>
     <row r="47">
@@ -2537,16 +2537,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003410969672741011</v>
+        <v>0.003404255050000183</v>
       </c>
       <c r="D47" t="n">
-        <v>0.004609953163375008</v>
+        <v>0.004609953163375036</v>
       </c>
       <c r="E47" t="n">
-        <v>8.344200074700834e-05</v>
+        <v>8.34420007470132e-05</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9964222633108666</v>
+        <v>0.996408186532315</v>
       </c>
     </row>
     <row r="48">
@@ -2557,16 +2557,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.004300356456982055</v>
+        <v>0.004290893820115645</v>
       </c>
       <c r="D48" t="n">
-        <v>0.07367797727351966</v>
+        <v>0.07367797727351968</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0003974451363745182</v>
+        <v>0.0003974451363745206</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9512482101275039</v>
+        <v>0.9510434883938225</v>
       </c>
     </row>
     <row r="49">
@@ -2577,16 +2577,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.005529937815272958</v>
+        <v>0.005519236339184721</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07500040302378497</v>
+        <v>0.07500040302378508</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0001063460561526024</v>
+        <v>0.000106346056152603</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9930222586598397</v>
+        <v>0.9929953632845575</v>
       </c>
     </row>
     <row r="50">
@@ -2597,16 +2597,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.005530454332444998</v>
+        <v>0.005522119562843562</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1603914365452611</v>
+        <v>0.1603914365452612</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002467938285681735</v>
+        <v>0.0002467938285681765</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9709961444062045</v>
+        <v>0.9709110735892027</v>
       </c>
     </row>
     <row r="51">
@@ -2617,16 +2617,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0009247857496823227</v>
+        <v>0.0009242991384792021</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.007466459080120662</v>
+        <v>-0.007466459080120641</v>
       </c>
       <c r="E51" t="n">
-        <v>5.500045681773457e-05</v>
+        <v>5.500045681773441e-05</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9691480257505163</v>
+        <v>0.9691165357389433</v>
       </c>
     </row>
     <row r="52">
@@ -2637,16 +2637,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002191230574501884</v>
+        <v>0.002189508800240034</v>
       </c>
       <c r="D52" t="n">
-        <v>0.007116751765441104</v>
+        <v>0.007116751765441132</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000120821542488728</v>
+        <v>0.0001208215424887314</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9879850229344083</v>
+        <v>0.9879663464411689</v>
       </c>
     </row>
     <row r="53">
@@ -2657,16 +2657,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.004287067598712451</v>
+        <v>0.004284020830651073</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.00881178310621239</v>
+        <v>-0.008811783106212417</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000516617963161244</v>
+        <v>0.0005166179631612431</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9717762561621692</v>
+        <v>0.9717372318113626</v>
       </c>
     </row>
     <row r="54">
@@ -2677,16 +2677,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.007445611277185945</v>
+        <v>0.007438896654445118</v>
       </c>
       <c r="D54" t="n">
-        <v>0.006263460448803576</v>
+        <v>0.006263460448803548</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0002573555074274554</v>
+        <v>0.0002573555074274304</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9976162553653904</v>
+        <v>0.9976119603925289</v>
       </c>
     </row>
     <row r="55">
@@ -2697,16 +2697,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.007810094934652962</v>
+        <v>0.007800632297786552</v>
       </c>
       <c r="D55" t="n">
         <v>0.060617474894507</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00152334488833706</v>
+        <v>0.001523344888337057</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8975602057449142</v>
+        <v>0.8973370541501066</v>
       </c>
     </row>
     <row r="56">
@@ -2717,16 +2717,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01299371785357671</v>
+        <v>0.01298301637748847</v>
       </c>
       <c r="D56" t="n">
         <v>0.08087505434038628</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0008253247882385495</v>
+        <v>0.000825324788238565</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9919957120389205</v>
+        <v>0.9919826170904761</v>
       </c>
     </row>
     <row r="57">
@@ -2737,16 +2737,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0126884859462947</v>
+        <v>0.01268015117669326</v>
       </c>
       <c r="D57" t="n">
         <v>0.1165681099037457</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001075294965714032</v>
+        <v>0.001075294965714038</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9789089038027073</v>
+        <v>0.9788817537136472</v>
       </c>
     </row>
     <row r="58">
@@ -2757,16 +2757,16 @@
         <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>0.001003266142374126</v>
+        <v>0.001002779531171005</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.008190477567187623</v>
+        <v>-0.008190477567187618</v>
       </c>
       <c r="E58" t="n">
         <v>0.0003641300675207998</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7914788616690116</v>
+        <v>0.7913186797456992</v>
       </c>
     </row>
     <row r="59">
@@ -2777,16 +2777,16 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>0.001831552213923223</v>
+        <v>0.001829830439661375</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.00677844715431989</v>
+        <v>-0.006778447154319904</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000268507832400911</v>
+        <v>0.0002685078324009096</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9394295525437246</v>
+        <v>0.9393224314222294</v>
       </c>
     </row>
     <row r="60">
@@ -2797,16 +2797,16 @@
         <v>20</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003368180013824296</v>
+        <v>0.003365133245762918</v>
       </c>
       <c r="D60" t="n">
-        <v>0.005090752026033429</v>
+        <v>0.005090752026033415</v>
       </c>
       <c r="E60" t="n">
-        <v>4.797998249801226e-05</v>
+        <v>4.797998249799236e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9995943202248345</v>
+        <v>0.9995935855917195</v>
       </c>
     </row>
     <row r="61">
@@ -2817,16 +2817,16 @@
         <v>40</v>
       </c>
       <c r="C61" t="n">
-        <v>0.004694795481427363</v>
+        <v>0.004688080858686536</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00504376305955212</v>
+        <v>0.005043763059552064</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0002105643739471675</v>
+        <v>0.0002105643739471671</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9880744789486345</v>
+        <v>0.988040702061607</v>
       </c>
     </row>
     <row r="62">
@@ -2837,16 +2837,16 @@
         <v>80</v>
       </c>
       <c r="C62" t="n">
-        <v>0.01396969459598969</v>
+        <v>0.01396023195912328</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.011181493058397</v>
+        <v>-0.01118149305839689</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0004955237199908368</v>
+        <v>0.0004955237199908384</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9949923403720207</v>
+        <v>0.9949855834596105</v>
       </c>
     </row>
     <row r="63">
@@ -2857,16 +2857,16 @@
         <v>160</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01889718533605814</v>
+        <v>0.01888648385996991</v>
       </c>
       <c r="D63" t="n">
-        <v>0.07078972384510701</v>
+        <v>0.07078972384510707</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004299909440382635</v>
+        <v>0.000429990944038298</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9989655610013842</v>
+        <v>0.9989643896141567</v>
       </c>
     </row>
     <row r="64">
@@ -2877,16 +2877,16 @@
         <v>320</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02420082759691104</v>
+        <v>0.0241924928273096</v>
       </c>
       <c r="D64" t="n">
         <v>-0.01575224365577621</v>
       </c>
       <c r="E64" t="n">
-        <v>0.002715975987398086</v>
+        <v>0.002715975987398078</v>
       </c>
       <c r="F64" t="n">
-        <v>0.952037116176167</v>
+        <v>0.9520056486507552</v>
       </c>
     </row>
     <row r="65">
@@ -2897,16 +2897,16 @@
         <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0005496621118675329</v>
+        <v>0.0005491755006644127</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0001181383865353318</v>
+        <v>-0.0001181383865353353</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0002023623430373663</v>
+        <v>0.0002023623430373662</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5960539482746412</v>
+        <v>0.595627377272081</v>
       </c>
     </row>
     <row r="66">
@@ -2917,7 +2917,7 @@
         <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.000819435243417543</v>
+        <v>0.0008189486322144227</v>
       </c>
       <c r="D66" t="n">
         <v>-0.00683877978074216</v>
@@ -2926,7 +2926,7 @@
         <v>0.0007628825410641393</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3658355056271101</v>
+        <v>0.3655599273693483</v>
       </c>
     </row>
     <row r="67">
@@ -2937,16 +2937,16 @@
         <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0009821435780778178</v>
+        <v>0.0009804218038159693</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.009315946600906e-05</v>
+        <v>-1.009315946601252e-05</v>
       </c>
       <c r="E67" t="n">
         <v>0.0009369574289914481</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3545844433970099</v>
+        <v>0.3537817507601905</v>
       </c>
     </row>
     <row r="68">
@@ -2957,16 +2957,16 @@
         <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>0.001053389409602596</v>
+        <v>0.001051667635340747</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002097596023141999</v>
+        <v>0.002097596023142002</v>
       </c>
       <c r="E68" t="n">
         <v>0.001102714858712065</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3133139201404768</v>
+        <v>0.3126104514058096</v>
       </c>
     </row>
     <row r="69">
@@ -2977,16 +2977,16 @@
         <v>20</v>
       </c>
       <c r="C69" t="n">
-        <v>0.002523916168410479</v>
+        <v>0.002520869400349101</v>
       </c>
       <c r="D69" t="n">
-        <v>0.007594400563426897</v>
+        <v>0.00759440056342691</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0001422256991158544</v>
+        <v>0.000142225699115857</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9936891646028406</v>
+        <v>0.9936739971661737</v>
       </c>
     </row>
     <row r="70">
@@ -2997,16 +2997,16 @@
         <v>20</v>
       </c>
       <c r="C70" t="n">
-        <v>0.002607623439993274</v>
+        <v>0.002604576671931896</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.0296430346745202</v>
+        <v>-0.02964303467452023</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0004907065923779716</v>
+        <v>0.0004907065923779707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8759258353652499</v>
+        <v>0.8756714988262549</v>
       </c>
     </row>
     <row r="71">
@@ -3017,16 +3017,16 @@
         <v>40</v>
       </c>
       <c r="C71" t="n">
-        <v>0.005809959355600041</v>
+        <v>0.005803244732859212</v>
       </c>
       <c r="D71" t="n">
-        <v>0.01737653831087016</v>
+        <v>0.01737653831087019</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0003597357063481165</v>
+        <v>0.0003597357063481179</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9923908933523224</v>
+        <v>0.9923734093565235</v>
       </c>
     </row>
     <row r="72">
@@ -3037,16 +3037,16 @@
         <v>40</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003780483493484689</v>
+        <v>0.003773768870743861</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.056499400878102</v>
+        <v>-0.05649940087810202</v>
       </c>
       <c r="E72" t="n">
-        <v>0.001346646721732433</v>
+        <v>0.001346646721732431</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7242928096262273</v>
+        <v>0.7235822533007146</v>
       </c>
     </row>
     <row r="73">
@@ -3057,16 +3057,16 @@
         <v>80</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0122366044420055</v>
+        <v>0.01222714180513909</v>
       </c>
       <c r="D73" t="n">
-        <v>0.01983085692452186</v>
+        <v>0.0198308569245218</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0005420539159736259</v>
+        <v>0.000542053915973641</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9941475832366091</v>
+        <v>0.9941385744269594</v>
       </c>
     </row>
     <row r="74">
@@ -3077,16 +3077,16 @@
         <v>80</v>
       </c>
       <c r="C74" t="n">
-        <v>0.007723427793259673</v>
+        <v>0.007713965156393263</v>
       </c>
       <c r="D74" t="n">
         <v>-0.007124392765962745</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0006250090251931952</v>
+        <v>0.0006250090251931925</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9807325500176823</v>
+        <v>0.9806861642150374</v>
       </c>
     </row>
     <row r="75">
@@ -3097,16 +3097,16 @@
         <v>160</v>
       </c>
       <c r="C75" t="n">
-        <v>0.02946246081953719</v>
+        <v>0.02945175934344895</v>
       </c>
       <c r="D75" t="n">
         <v>0.1767343371186675</v>
       </c>
       <c r="E75" t="n">
-        <v>0.004527706112385978</v>
+        <v>0.004527706112385955</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9548970477885722</v>
+        <v>0.9548657445972499</v>
       </c>
     </row>
     <row r="76">
@@ -3117,16 +3117,16 @@
         <v>160</v>
       </c>
       <c r="C76" t="n">
-        <v>0.02194054126078456</v>
+        <v>0.02192983978469632</v>
       </c>
       <c r="D76" t="n">
-        <v>-2.888723639059728</v>
+        <v>-2.888723639059727</v>
       </c>
       <c r="E76" t="n">
-        <v>0.002255551975568189</v>
+        <v>0.002255551975568191</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7299826882576329</v>
+        <v>0.7297903197915668</v>
       </c>
     </row>
     <row r="77">
@@ -3137,16 +3137,16 @@
         <v>320</v>
       </c>
       <c r="C77" t="n">
-        <v>0.03465083929154774</v>
+        <v>0.0346425045219463</v>
       </c>
       <c r="D77" t="n">
-        <v>0.05904407292569869</v>
+        <v>0.05904407292569847</v>
       </c>
       <c r="E77" t="n">
-        <v>0.002015085764526063</v>
+        <v>0.002015085764526093</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9899562290322302</v>
+        <v>0.9899514440839507</v>
       </c>
     </row>
     <row r="78">
@@ -3157,16 +3157,16 @@
         <v>320</v>
       </c>
       <c r="C78" t="n">
-        <v>0.02250938734785125</v>
+        <v>0.02250105257824981</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1604598542285963</v>
+        <v>0.1604598542285964</v>
       </c>
       <c r="E78" t="n">
-        <v>0.005576638574385628</v>
+        <v>0.005576638574385627</v>
       </c>
       <c r="F78" t="n">
-        <v>0.890664367590961</v>
+        <v>0.8905922166823802</v>
       </c>
     </row>
     <row r="79">
@@ -3177,16 +3177,16 @@
         <v>5</v>
       </c>
       <c r="C79" t="n">
-        <v>0.001135912751817307</v>
+        <v>0.001135426140614187</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.0004695798110111518</v>
+        <v>-0.0004695798110111588</v>
       </c>
       <c r="E79" t="n">
         <v>0.0002234981412735392</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9281378262902603</v>
+        <v>0.9280806478465912</v>
       </c>
     </row>
     <row r="80">
@@ -3197,7 +3197,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="n">
-        <v>0.001468339833923692</v>
+        <v>0.001466618059661843</v>
       </c>
       <c r="D80" t="n">
         <v>-0.01282289261100238</v>
@@ -3206,7 +3206,7 @@
         <v>0.0001989579590711142</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9159192345404438</v>
+        <v>0.9157383455702169</v>
       </c>
     </row>
     <row r="81">
@@ -3217,16 +3217,16 @@
         <v>20</v>
       </c>
       <c r="C81" t="n">
-        <v>0.002602557624009712</v>
+        <v>0.002599510855948333</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.04299519607311125</v>
+        <v>-0.04299519607311122</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0001622731220728725</v>
+        <v>0.0001622731220728721</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9554270621394217</v>
+        <v>0.9553271874169061</v>
       </c>
     </row>
     <row r="82">
@@ -3237,16 +3237,16 @@
         <v>40</v>
       </c>
       <c r="C82" t="n">
-        <v>0.007467238900995353</v>
+        <v>0.007460524278254525</v>
       </c>
       <c r="D82" t="n">
-        <v>0.01605624732250516</v>
+        <v>0.01605624732250513</v>
       </c>
       <c r="E82" t="n">
-        <v>0.000297748132357331</v>
+        <v>0.0002977481323573289</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9968302194876132</v>
+        <v>0.9968245293133764</v>
       </c>
     </row>
     <row r="83">
@@ -3257,16 +3257,16 @@
         <v>80</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0127288552757014</v>
+        <v>0.01271939263883499</v>
       </c>
       <c r="D83" t="n">
         <v>0.08215729161731899</v>
       </c>
       <c r="E83" t="n">
-        <v>0.001230925590978314</v>
+        <v>0.001230925590978313</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9553307495298988</v>
+        <v>0.9552672353257341</v>
       </c>
     </row>
     <row r="84">
@@ -3277,16 +3277,16 @@
         <v>160</v>
       </c>
       <c r="C84" t="n">
-        <v>0.01805331809704621</v>
+        <v>0.01804261662095797</v>
       </c>
       <c r="D84" t="n">
-        <v>0.03154016861642644</v>
+        <v>0.03154016861642639</v>
       </c>
       <c r="E84" t="n">
-        <v>0.001726493583298468</v>
+        <v>0.001726493583298451</v>
       </c>
       <c r="F84" t="n">
-        <v>0.982037209386602</v>
+        <v>0.9820162781238232</v>
       </c>
     </row>
     <row r="85">
@@ -3297,16 +3297,16 @@
         <v>320</v>
       </c>
       <c r="C85" t="n">
-        <v>0.03315246432704098</v>
+        <v>0.03314412955743953</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1362466422000176</v>
+        <v>0.1362466422000178</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0009139763843314667</v>
+        <v>0.0009139763843316744</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9984822206222843</v>
+        <v>0.9984814583322675</v>
       </c>
     </row>
     <row r="86">
@@ -3317,16 +3317,16 @@
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0003421958116165327</v>
+        <v>0.0003417092004134123</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.002001503968982675</v>
+        <v>-0.002001503968982672</v>
       </c>
       <c r="E86" t="n">
         <v>0.000253522708145776</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3129346749643677</v>
+        <v>0.3123230761287316</v>
       </c>
     </row>
     <row r="87">
@@ -3337,16 +3337,16 @@
         <v>10</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0009088338792112508</v>
+        <v>0.0009071121049494023</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.001563506736104454</v>
+        <v>-0.001563506736104468</v>
       </c>
       <c r="E87" t="n">
         <v>0.0003317461445087969</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6001635558521589</v>
+        <v>0.5992531188663633</v>
       </c>
     </row>
     <row r="88">
@@ -3357,16 +3357,16 @@
         <v>20</v>
       </c>
       <c r="C88" t="n">
-        <v>0.002421474111853991</v>
+        <v>0.002418427343792613</v>
       </c>
       <c r="D88" t="n">
         <v>0.01271429558830829</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0006997283739956431</v>
+        <v>0.0006997283739956421</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8568944054848067</v>
+        <v>0.8565853495563025</v>
       </c>
     </row>
     <row r="89">
@@ -3377,16 +3377,16 @@
         <v>40</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0009878375260947341</v>
+        <v>0.0009811229033539063</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.02828960256669937</v>
+        <v>-0.02828960256669938</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0002062702187348377</v>
+        <v>0.0002062702187348378</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7661596988624588</v>
+        <v>0.763706922985719</v>
       </c>
     </row>
     <row r="90">
@@ -3397,16 +3397,16 @@
         <v>80</v>
       </c>
       <c r="C90" t="n">
-        <v>0.013794254697523</v>
+        <v>0.01378479206065659</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.004232540190900913</v>
+        <v>-0.004232540190900969</v>
       </c>
       <c r="E90" t="n">
-        <v>0.001218477547863089</v>
+        <v>0.001218477547863091</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9846346069999948</v>
+        <v>0.9846138291507628</v>
       </c>
     </row>
     <row r="91">
@@ -3417,16 +3417,16 @@
         <v>160</v>
       </c>
       <c r="C91" t="n">
-        <v>0.03189389383783461</v>
+        <v>0.03188319236174637</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.1104651762029562</v>
+        <v>-0.1104651762029559</v>
       </c>
       <c r="E91" t="n">
-        <v>0.005072565245698507</v>
+        <v>0.005072565245698502</v>
       </c>
       <c r="F91" t="n">
-        <v>0.929466536770731</v>
+        <v>0.9294225225354036</v>
       </c>
     </row>
     <row r="92">
@@ -3437,16 +3437,16 @@
         <v>320</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0006751163377163224</v>
+        <v>0.0006667815681148864</v>
       </c>
       <c r="D92" t="n">
         <v>0.1665484740560861</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0003849665178418107</v>
+        <v>0.0003849665178418104</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6059477265030937</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3457,7 +3457,7 @@
         <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0003653162804208759</v>
+        <v>0.0003648296692177556</v>
       </c>
       <c r="D93" t="n">
         <v>-0.01478405936946857</v>
@@ -3466,7 +3466,7 @@
         <v>0.0002917939733785146</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2071274091619066</v>
+        <v>0.2066899532835667</v>
       </c>
     </row>
     <row r="94">
@@ -3497,16 +3497,16 @@
         <v>20</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0006956196444785418</v>
+        <v>0.0006925728764171634</v>
       </c>
       <c r="D95" t="n">
         <v>-0.1479768051099354</v>
       </c>
       <c r="E95" t="n">
-        <v>4.381598593396443e-05</v>
+        <v>4.381598593396447e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>0.812930525599893</v>
+        <v>0.8115917780125143</v>
       </c>
     </row>
     <row r="96">
@@ -3517,16 +3517,16 @@
         <v>40</v>
       </c>
       <c r="C96" t="n">
-        <v>0.003352529581827439</v>
+        <v>0.003345814959086611</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1139884272137688</v>
+        <v>0.1139884272137687</v>
       </c>
       <c r="E96" t="n">
-        <v>0.001503096867302475</v>
+        <v>0.001503096867302474</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4987343255693353</v>
+        <v>0.4977319079046663</v>
       </c>
     </row>
     <row r="97">
@@ -3537,16 +3537,16 @@
         <v>80</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01599335971382894</v>
+        <v>0.01598389707696253</v>
       </c>
       <c r="D97" t="n">
         <v>0.1158191378105191</v>
       </c>
       <c r="E97" t="n">
-        <v>0.004558187991029265</v>
+        <v>0.004558187991029257</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8602478089637235</v>
+        <v>0.8601054455633501</v>
       </c>
     </row>
     <row r="98">
@@ -3557,16 +3557,16 @@
         <v>160</v>
       </c>
       <c r="C98" t="n">
-        <v>1.070147608823855e-05</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.05989367546435512</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3577,16 +3577,16 @@
         <v>320</v>
       </c>
       <c r="C99" t="n">
-        <v>8.33476960143617e-06</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1565467505343628</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3643,16 +3643,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003738385127165759</v>
+        <v>0.0003733519015134554</v>
       </c>
       <c r="D2" t="n">
         <v>-0.2452861217356112</v>
       </c>
       <c r="E2" t="n">
-        <v>2.894881606616765e-05</v>
+        <v>2.894881606616768e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5982287607833533</v>
+        <v>0.5976024817150968</v>
       </c>
     </row>
     <row r="3">
@@ -3663,7 +3663,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001301145231993981</v>
+        <v>0.0001283927489375493</v>
       </c>
       <c r="D3" t="n">
         <v>-0.2850375940647397</v>
@@ -3672,7 +3672,7 @@
         <v>4.392495853956181e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08794450349583403</v>
+        <v>0.08583085537824685</v>
       </c>
     </row>
     <row r="4">
@@ -3683,16 +3683,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>4.056049406762446e-06</v>
+        <v>1.009281345384113e-06</v>
       </c>
       <c r="D4" t="n">
         <v>-0.01865448402665061</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004687578173191595</v>
+        <v>0.0004687578173191596</v>
       </c>
       <c r="F4" t="n">
-        <v>1.871721832022097e-05</v>
+        <v>1.158956007599352e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4023,16 +4023,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>5.841707073472536e-05</v>
+        <v>4.771559464648694e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02793964636550583</v>
+        <v>0.02793964636550578</v>
       </c>
       <c r="E21" t="n">
         <v>8.455704873815684e-06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2747313769421321</v>
+        <v>0.2017410583187795</v>
       </c>
     </row>
     <row r="22">
@@ -4043,16 +4043,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>3.840364797683741e-05</v>
+        <v>3.006887837540136e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08166980414628418</v>
+        <v>0.08166980414628414</v>
       </c>
       <c r="E22" t="n">
         <v>1.444678408815227e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05310482179807211</v>
+        <v>0.03323846135630325</v>
       </c>
     </row>
     <row r="23">
@@ -4063,16 +4063,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001138344407656326</v>
+        <v>0.0001133478295625123</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05304527451919653</v>
+        <v>-0.05304527451919655</v>
       </c>
       <c r="E23" t="n">
-        <v>8.683201607625822e-06</v>
+        <v>8.683201607625811e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7105824183107697</v>
+        <v>0.7088172370745011</v>
       </c>
     </row>
     <row r="24">
@@ -4083,16 +4083,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003091315180507849</v>
+        <v>0.000307409743788936</v>
       </c>
       <c r="D24" t="n">
         <v>-0.02461473312831837</v>
       </c>
       <c r="E24" t="n">
-        <v>1.088068426801181e-05</v>
+        <v>1.08806842680118e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9276017680126061</v>
+        <v>0.9268479967489983</v>
       </c>
     </row>
     <row r="25">
@@ -4103,16 +4103,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0005568843463976056</v>
+        <v>0.0005538375783362274</v>
       </c>
       <c r="D25" t="n">
-        <v>0.008892111044252138</v>
+        <v>0.008892111044252027</v>
       </c>
       <c r="E25" t="n">
-        <v>1.605947635258048e-05</v>
+        <v>1.605947635258044e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9509668485978031</v>
+        <v>0.9504526863225732</v>
       </c>
     </row>
     <row r="26">
@@ -4123,16 +4123,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00119524503822301</v>
+        <v>0.001188530415482182</v>
       </c>
       <c r="D26" t="n">
         <v>0.03105000135364278</v>
       </c>
       <c r="E26" t="n">
-        <v>2.182279768726024e-05</v>
+        <v>2.182279768726008e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9797505076236224</v>
+        <v>0.9795257593511912</v>
       </c>
     </row>
     <row r="27">
@@ -4143,16 +4143,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001602510586547736</v>
+        <v>0.001593047949681326</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1297331596039857</v>
+        <v>0.1297331596039855</v>
       </c>
       <c r="E27" t="n">
-        <v>2.735607700717628e-05</v>
+        <v>2.735607700717546e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9822531635725102</v>
+        <v>0.9820455031117564</v>
       </c>
     </row>
     <row r="28">
@@ -4163,16 +4163,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001649730848031991</v>
+        <v>0.001639029371943754</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1762420858487194</v>
+        <v>0.176242085848719</v>
       </c>
       <c r="E28" t="n">
-        <v>4.304015868357963e-05</v>
+        <v>4.304015868357899e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9595086621369823</v>
+        <v>0.9589999370806921</v>
       </c>
     </row>
     <row r="29">
@@ -4183,16 +4183,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00123356452966503</v>
+        <v>0.001225229760063594</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3712608610961426</v>
+        <v>0.3712608610961429</v>
       </c>
       <c r="E29" t="n">
-        <v>6.907854173152866e-05</v>
+        <v>6.90785417315287e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.837222254479743</v>
+        <v>0.8353659358979393</v>
       </c>
     </row>
     <row r="30">
@@ -4203,7 +4203,7 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0002169590125286642</v>
+        <v>0.0002164724013255438</v>
       </c>
       <c r="D30" t="n">
         <v>-0.02312994496936484</v>
@@ -4212,7 +4212,7 @@
         <v>2.778622142736362e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6287405242407832</v>
+        <v>0.6276916550704235</v>
       </c>
     </row>
     <row r="31">
@@ -4223,16 +4223,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005411625823445241</v>
+        <v>0.0005394408080826754</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01447657274410084</v>
+        <v>-0.01447657274410086</v>
       </c>
       <c r="E31" t="n">
-        <v>3.329720479089532e-05</v>
+        <v>3.329720479089525e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8980089731275368</v>
+        <v>0.8974237594463876</v>
       </c>
     </row>
     <row r="32">
@@ -4243,16 +4243,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001130661768067174</v>
+        <v>0.001127615000005796</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0199268660181357</v>
+        <v>0.01992686601813576</v>
       </c>
       <c r="E32" t="n">
-        <v>3.243581544635475e-05</v>
+        <v>3.243581544635456e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9712255631754347</v>
+        <v>0.9710743623392512</v>
       </c>
     </row>
     <row r="33">
@@ -4263,16 +4263,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002580461028765706</v>
+        <v>0.002573746406024878</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03039212854245654</v>
+        <v>-0.03039212854245665</v>
       </c>
       <c r="E33" t="n">
-        <v>4.509442868406623e-05</v>
+        <v>4.509442868406492e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9900227629883557</v>
+        <v>0.9899711588138584</v>
       </c>
     </row>
     <row r="34">
@@ -4283,16 +4283,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003640070164553211</v>
+        <v>0.003630607527686801</v>
       </c>
       <c r="D34" t="n">
         <v>-0.04876481875227168</v>
       </c>
       <c r="E34" t="n">
-        <v>7.074424032412329e-05</v>
+        <v>7.074424032412185e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9887955530686745</v>
+        <v>0.9887377301525099</v>
       </c>
     </row>
     <row r="35">
@@ -4303,16 +4303,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003936269330027829</v>
+        <v>0.00392556785393959</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1397340326780001</v>
+        <v>0.1397340326780004</v>
       </c>
       <c r="E35" t="n">
-        <v>7.723375233912523e-05</v>
+        <v>7.723375233912787e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9885822970097361</v>
+        <v>0.9885206762210188</v>
       </c>
     </row>
     <row r="36">
@@ -4323,16 +4323,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003966366430596541</v>
+        <v>0.003958031660995106</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4223668254115965</v>
+        <v>0.4223668254115963</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001742125273988591</v>
+        <v>0.0001742125273988585</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9452908694491843</v>
+        <v>0.9450728845185142</v>
       </c>
     </row>
     <row r="37">
@@ -4343,16 +4343,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0003044431295810735</v>
+        <v>0.0003039565183779532</v>
       </c>
       <c r="D37" t="n">
         <v>-0.02061642189201445</v>
       </c>
       <c r="E37" t="n">
-        <v>7.600710702810579e-05</v>
+        <v>7.60071070281058e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.485529432998119</v>
+        <v>0.4847303187884887</v>
       </c>
     </row>
     <row r="38">
@@ -4363,16 +4363,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0008340423576132309</v>
+        <v>0.0008323205833513824</v>
       </c>
       <c r="D38" t="n">
-        <v>0.007916456960145951</v>
+        <v>0.007916456960145923</v>
       </c>
       <c r="E38" t="n">
-        <v>9.317908208822485e-05</v>
+        <v>9.317908208822467e-05</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8335409011876733</v>
+        <v>0.8329666529190727</v>
       </c>
     </row>
     <row r="39">
@@ -4383,16 +4383,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002081929245443514</v>
+        <v>0.002078882477382136</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.05527499604223168</v>
+        <v>-0.05527499604223174</v>
       </c>
       <c r="E39" t="n">
-        <v>5.536007018981986e-05</v>
+        <v>5.536007018981911e-05</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9812667901790803</v>
+        <v>0.9812128722732574</v>
       </c>
     </row>
     <row r="40">
@@ -4403,16 +4403,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003832119075500241</v>
+        <v>0.003825404452759413</v>
       </c>
       <c r="D40" t="n">
         <v>-0.02001476817256204</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000139777023302188</v>
+        <v>0.0001397770233021879</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9817145006150801</v>
+        <v>0.9816514311179255</v>
       </c>
     </row>
     <row r="41">
@@ -4423,16 +4423,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.007010183923754107</v>
+        <v>0.007000721286887697</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.105372339891018</v>
+        <v>-0.1053723398910182</v>
       </c>
       <c r="E41" t="n">
         <v>0.0002737843280597778</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9790921230003973</v>
+        <v>0.9790367495324085</v>
       </c>
     </row>
     <row r="42">
@@ -4443,16 +4443,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009140497616548705</v>
+        <v>0.009129796140460467</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09124461298845477</v>
+        <v>0.09124461298845454</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0002443552374749726</v>
+        <v>0.0002443552374749654</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9900937794618064</v>
+        <v>0.9900707734526768</v>
       </c>
     </row>
     <row r="43">
@@ -4463,16 +4463,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00852593470255722</v>
+        <v>0.008517599932955785</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2242968767163254</v>
+        <v>0.2242968767163251</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000498526847498899</v>
+        <v>0.0004985268474989012</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9543210976267368</v>
+        <v>0.9542357502584118</v>
       </c>
     </row>
     <row r="44">
@@ -4483,16 +4483,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00189755125068344</v>
+        <v>0.001897064639480319</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6698452446165497</v>
+        <v>-0.6698452446165494</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0002151749568812471</v>
+        <v>0.0002151749568812472</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4034294232388093</v>
+        <v>0.4033059757803295</v>
       </c>
     </row>
     <row r="45">
@@ -4503,16 +4503,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.001886390771283367</v>
+        <v>0.001884668997021518</v>
       </c>
       <c r="D45" t="n">
-        <v>0.008428579774468786</v>
+        <v>0.008428579774468772</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0002286462016275311</v>
+        <v>0.0002286462016275307</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9189920467719535</v>
+        <v>0.9188559823563341</v>
       </c>
     </row>
     <row r="46">
@@ -4523,16 +4523,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.006811664017456285</v>
+        <v>0.006808617249394907</v>
       </c>
       <c r="D46" t="n">
         <v>-0.02091444934690367</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0001518943030330381</v>
+        <v>0.0001518943030330377</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9950520836641094</v>
+        <v>0.9950476763513944</v>
       </c>
     </row>
     <row r="47">
@@ -4543,16 +4543,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.004200140324072199</v>
+        <v>0.004193425701331373</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02770520165756352</v>
+        <v>-0.02770520165756363</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001127556065449841</v>
+        <v>0.0001127556065449816</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9871937029230418</v>
+        <v>0.9871531858236836</v>
       </c>
     </row>
     <row r="48">
@@ -4563,16 +4563,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01344435241671748</v>
+        <v>0.01343488977985107</v>
       </c>
       <c r="D48" t="n">
-        <v>0.07774026503731113</v>
+        <v>0.07774026503731135</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000309605534064179</v>
+        <v>0.0003096055340641786</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9957753666883911</v>
+        <v>0.9957694386802508</v>
       </c>
     </row>
     <row r="49">
@@ -4583,16 +4583,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01434196314468077</v>
+        <v>0.01433126166859253</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1650798171161736</v>
+        <v>0.1650798171161735</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0009435105692509518</v>
+        <v>0.0009435105692509482</v>
       </c>
       <c r="F49" t="n">
-        <v>0.974689889213161</v>
+        <v>0.9746530342943172</v>
       </c>
     </row>
     <row r="50">
@@ -4603,16 +4603,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02242083742814161</v>
+        <v>0.02241250265854017</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2670648536675293</v>
+        <v>0.2670648536675291</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00128038967046422</v>
+        <v>0.001280389670464237</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9808081872722343</v>
+        <v>0.980794184698594</v>
       </c>
     </row>
     <row r="51">
@@ -4623,16 +4623,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001470232670998151</v>
+        <v>0.00146974605979503</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01244755319575571</v>
+        <v>-0.0124475531957557</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0002882865020748212</v>
+        <v>0.0002882865020748214</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8387564484856354</v>
+        <v>0.8386668885990413</v>
       </c>
     </row>
     <row r="52">
@@ -4643,16 +4643,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003877890819384896</v>
+        <v>0.003876169045123047</v>
       </c>
       <c r="D52" t="n">
-        <v>0.004893994910489502</v>
+        <v>0.004893994910489516</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0003365650515482842</v>
+        <v>0.0003365650515482841</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9851583253393086</v>
+        <v>0.9851453331256272</v>
       </c>
     </row>
     <row r="53">
@@ -4663,16 +4663,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.007708804706595662</v>
+        <v>0.007705757938534286</v>
       </c>
       <c r="D53" t="n">
-        <v>0.01677996470789395</v>
+        <v>0.01677996470789389</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0003270208055525401</v>
+        <v>0.0003270208055525347</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9893177257908006</v>
+        <v>0.9893093671488989</v>
       </c>
     </row>
     <row r="54">
@@ -4683,16 +4683,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01439059335998365</v>
+        <v>0.01438387873724283</v>
       </c>
       <c r="D54" t="n">
         <v>0.02688263342709823</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0008690972602726104</v>
+        <v>0.0008690972602725997</v>
       </c>
       <c r="F54" t="n">
-        <v>0.992758095524752</v>
+        <v>0.9927513816961858</v>
       </c>
     </row>
     <row r="55">
@@ -4703,16 +4703,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0243982194871796</v>
+        <v>0.02438875685031319</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.09294676114839329</v>
+        <v>-0.09294676114839318</v>
       </c>
       <c r="E55" t="n">
-        <v>0.001545801356702187</v>
+        <v>0.00154580135670218</v>
       </c>
       <c r="F55" t="n">
-        <v>0.984197229609965</v>
+        <v>0.9841851585115527</v>
       </c>
     </row>
     <row r="56">
@@ -4723,16 +4723,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02734090219302043</v>
+        <v>0.02733020071693219</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0928239550150719</v>
+        <v>-0.09282395501507179</v>
       </c>
       <c r="E56" t="n">
-        <v>0.003193502579456932</v>
+        <v>0.003193502579456943</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9606804040134669</v>
+        <v>0.9606508177253799</v>
       </c>
     </row>
     <row r="57">
@@ -4743,16 +4743,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03277010088543838</v>
+        <v>0.03276176611583693</v>
       </c>
       <c r="D57" t="n">
         <v>0.1266263403380211</v>
       </c>
       <c r="E57" t="n">
-        <v>0.003925990665577704</v>
+        <v>0.003925990665577705</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9720950220657318</v>
+        <v>0.9720812183577021</v>
       </c>
     </row>
   </sheetData>
@@ -4829,16 +4829,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>3.96147777934095e-05</v>
+        <v>3.789300353156071e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01742976881612861</v>
+        <v>0.0174297688161286</v>
       </c>
       <c r="E3" t="n">
         <v>9.452259926282807e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01157433087423384</v>
+        <v>0.01060051995619463</v>
       </c>
     </row>
     <row r="4">
@@ -4849,16 +4849,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>2.630229239460409e-05</v>
+        <v>2.325552433322578e-05</v>
       </c>
       <c r="D4" t="n">
         <v>0.02005965597976166</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002651227009577521</v>
+        <v>0.000265122700957752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001404058259057197</v>
+        <v>0.001097951873783914</v>
       </c>
     </row>
     <row r="5">
@@ -4869,7 +4869,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>9.564774715710905e-06</v>
+        <v>2.850151974883154e-06</v>
       </c>
       <c r="D5" t="n">
         <v>-0.02960570215510131</v>
@@ -4878,7 +4878,7 @@
         <v>0.0003216298385512677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001263234331311562</v>
+        <v>1.121812973980512e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4889,16 +4889,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>4.187125251007729e-05</v>
+        <v>3.240861564366699e-05</v>
       </c>
       <c r="D6" t="n">
         <v>0.03303995834466802</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003468475441218737</v>
+        <v>0.0003468475441218736</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001818336504716771</v>
+        <v>0.001090134359776419</v>
       </c>
     </row>
     <row r="7">
@@ -4909,7 +4909,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002651553647984774</v>
+        <v>0.0002544538887102391</v>
       </c>
       <c r="D7" t="n">
         <v>0.07166710075671846</v>
@@ -4918,7 +4918,7 @@
         <v>0.0005124772721494074</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04271134797218319</v>
+        <v>0.03946664119886448</v>
       </c>
     </row>
     <row r="8">
@@ -4929,16 +4929,16 @@
         <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00156631107282387</v>
+        <v>0.001557976303222434</v>
       </c>
       <c r="D8" t="n">
         <v>0.1294368865361486</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001630208462167612</v>
+        <v>0.001630208462167611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1875111749100075</v>
+        <v>0.1858908641341308</v>
       </c>
     </row>
     <row r="9">
@@ -5089,7 +5089,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003463800868727549</v>
+        <v>0.0003458934756696345</v>
       </c>
       <c r="D16" t="n">
         <v>-0.2363571896585102</v>
@@ -5098,7 +5098,7 @@
         <v>9.1362433176318e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1023963728112258</v>
+        <v>0.1021382371144791</v>
       </c>
     </row>
     <row r="17">
@@ -5109,16 +5109,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002628457095716966</v>
+        <v>0.0002611239353098478</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02550743242990919</v>
+        <v>-0.02550743242990927</v>
       </c>
       <c r="E17" t="n">
-        <v>5.757738593520059e-06</v>
+        <v>5.75773859352005e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9429864479890763</v>
+        <v>0.9422756518782931</v>
       </c>
     </row>
     <row r="18">
@@ -5129,16 +5129,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004773359709146446</v>
+        <v>0.0004742892028532665</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01584170365218074</v>
+        <v>-0.01584170365218085</v>
       </c>
       <c r="E18" t="n">
-        <v>5.039373098037401e-06</v>
+        <v>5.039373098037421e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9861509921462154</v>
+        <v>0.9859749959006766</v>
       </c>
     </row>
     <row r="19">
@@ -5149,16 +5149,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0008785928718929624</v>
+        <v>0.0008718782491521346</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09563378199727868</v>
+        <v>0.09563378199727879</v>
       </c>
       <c r="E19" t="n">
-        <v>8.540812178988862e-06</v>
+        <v>8.540812178988764e-06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9882333444459968</v>
+        <v>0.9880535822280023</v>
       </c>
     </row>
     <row r="20">
@@ -5169,16 +5169,16 @@
         <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00106489050037243</v>
+        <v>0.00105542786350602</v>
       </c>
       <c r="D20" t="n">
         <v>0.1566216433853278</v>
       </c>
       <c r="E20" t="n">
-        <v>1.233150954890351e-05</v>
+        <v>1.233150954890358e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9833843844771901</v>
+        <v>0.9830901687220807</v>
       </c>
     </row>
     <row r="21">
@@ -5189,16 +5189,16 @@
         <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008352099904884476</v>
+        <v>0.0008245085144002087</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2274544506157005</v>
+        <v>0.2274544506157009</v>
       </c>
       <c r="E21" t="n">
-        <v>1.906092535762537e-05</v>
+        <v>1.906092535762576e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9384167111924993</v>
+        <v>0.9369092427350538</v>
       </c>
     </row>
     <row r="22">
@@ -5209,16 +5209,16 @@
         <v>320</v>
       </c>
       <c r="C22" t="n">
-        <v>0.000428431586544102</v>
+        <v>0.0004200968169426658</v>
       </c>
       <c r="D22" t="n">
-        <v>0.500632576576187</v>
+        <v>0.5006325765761871</v>
       </c>
       <c r="E22" t="n">
         <v>2.637503362789632e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6768087523205976</v>
+        <v>0.6681551267910029</v>
       </c>
     </row>
     <row r="23">
@@ -5229,16 +5229,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001767969376464119</v>
+        <v>0.0001763103264432915</v>
       </c>
       <c r="D23" t="n">
         <v>0.02707568159980925</v>
       </c>
       <c r="E23" t="n">
-        <v>1.059598114613674e-05</v>
+        <v>1.059598114613676e-05</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8178606164523486</v>
+        <v>0.8170380340913774</v>
       </c>
     </row>
     <row r="24">
@@ -5249,16 +5249,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003830639061734199</v>
+        <v>0.0003813421319115711</v>
       </c>
       <c r="D24" t="n">
         <v>-0.005851735676311892</v>
       </c>
       <c r="E24" t="n">
-        <v>1.023087298202126e-05</v>
+        <v>1.023087298202133e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9530899495023613</v>
+        <v>0.9526854796221658</v>
       </c>
     </row>
     <row r="25">
@@ -5269,16 +5269,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0009517296847824525</v>
+        <v>0.0009486829167210741</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03034205238054988</v>
+        <v>0.03034205238055004</v>
       </c>
       <c r="E25" t="n">
         <v>1.24672210142826e-05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9894729256239529</v>
+        <v>0.9894059175198485</v>
       </c>
     </row>
     <row r="26">
@@ -5289,16 +5289,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001936979471988713</v>
+        <v>0.001930264849247884</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1140709143104868</v>
+        <v>0.114070914310487</v>
       </c>
       <c r="E26" t="n">
-        <v>1.825440679206847e-05</v>
+        <v>1.825440679206869e-05</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9945236372007654</v>
+        <v>0.9944856812242476</v>
       </c>
     </row>
     <row r="27">
@@ -5309,16 +5309,16 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002846568259417853</v>
+        <v>0.002837105622551443</v>
       </c>
       <c r="D27" t="n">
-        <v>0.054680835233202</v>
+        <v>0.05468083523320222</v>
       </c>
       <c r="E27" t="n">
-        <v>2.744343503787065e-05</v>
+        <v>2.744343503787041e-05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9942703261270693</v>
+        <v>0.9942322626839238</v>
       </c>
     </row>
     <row r="28">
@@ -5329,16 +5329,16 @@
         <v>160</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002954356910193798</v>
+        <v>0.002943655434105561</v>
       </c>
       <c r="D28" t="n">
         <v>0.3168630779095616</v>
       </c>
       <c r="E28" t="n">
-        <v>5.260475352421287e-05</v>
+        <v>5.260475352421195e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9807220134702338</v>
+        <v>0.9805843172457079</v>
       </c>
     </row>
     <row r="29">
@@ -5349,16 +5349,16 @@
         <v>320</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001698768122745412</v>
+        <v>0.001690433353143976</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3152736491388041</v>
+        <v>0.3152736491388037</v>
       </c>
       <c r="E29" t="n">
-        <v>5.016018936394834e-05</v>
+        <v>5.016018936394798e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9487164310993256</v>
+        <v>0.9482357141563359</v>
       </c>
     </row>
     <row r="30">
@@ -5369,16 +5369,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003419313421489506</v>
+        <v>0.0003414447309458301</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.02994439962111009</v>
+        <v>-0.02994439962111006</v>
       </c>
       <c r="E30" t="n">
-        <v>1.145836778641541e-05</v>
+        <v>1.145836778641549e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.946836601433323</v>
+        <v>0.9466930448992555</v>
       </c>
     </row>
     <row r="31">
@@ -5389,16 +5389,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0008561348468244264</v>
+        <v>0.0008544130725625773</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.04016631456982014</v>
+        <v>-0.04016631456982012</v>
       </c>
       <c r="E31" t="n">
-        <v>2.510856395115142e-05</v>
+        <v>2.510856395115173e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9683498842841248</v>
+        <v>0.9682262531526461</v>
       </c>
     </row>
     <row r="32">
@@ -5409,16 +5409,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001730293791019063</v>
+        <v>0.001727247022957685</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.07812430340777476</v>
+        <v>-0.07812430340777488</v>
       </c>
       <c r="E32" t="n">
-        <v>2.205728857591041e-05</v>
+        <v>2.205728857590921e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9925802713631882</v>
+        <v>0.9925542673674025</v>
       </c>
     </row>
     <row r="33">
@@ -5429,16 +5429,16 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003874476743890982</v>
+        <v>0.003867762121150155</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.05921568525371024</v>
+        <v>-0.05921568525371057</v>
       </c>
       <c r="E33" t="n">
-        <v>5.112393127973244e-05</v>
+        <v>5.112393127972891e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9948038571362766</v>
+        <v>0.9947858941154681</v>
       </c>
     </row>
     <row r="34">
@@ -5449,16 +5449,16 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006039379286361409</v>
+        <v>0.006029916649495001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06701695214931003</v>
+        <v>0.06701695214930936</v>
       </c>
       <c r="E34" t="n">
-        <v>7.728183641602217e-05</v>
+        <v>7.728183641601777e-05</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9949495160454805</v>
+        <v>0.9949337327152353</v>
       </c>
     </row>
     <row r="35">
@@ -5469,16 +5469,16 @@
         <v>160</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005502399823520278</v>
+        <v>0.00549169834743204</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1665030774040035</v>
+        <v>0.1665030774040031</v>
       </c>
       <c r="E35" t="n">
-        <v>9.718465744255904e-05</v>
+        <v>9.718465744255782e-05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9907281396783136</v>
+        <v>0.9906923056511422</v>
       </c>
     </row>
     <row r="36">
@@ -5489,16 +5489,16 @@
         <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005423152473174367</v>
+        <v>0.005414817703572931</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4709394932111828</v>
+        <v>0.470939493211183</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001551754947973401</v>
+        <v>0.0001551754947973416</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9760268195632278</v>
+        <v>0.9759547371693943</v>
       </c>
     </row>
     <row r="37">
@@ -5509,16 +5509,16 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0009320753009069319</v>
+        <v>0.0009315886897038117</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.01760381849093173</v>
+        <v>-0.01760381849093176</v>
       </c>
       <c r="E37" t="n">
         <v>4.806360337757931e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9471126753402288</v>
+        <v>0.9470603357221199</v>
       </c>
     </row>
     <row r="38">
@@ -5529,16 +5529,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001311544954860391</v>
+        <v>0.001309823180598542</v>
       </c>
       <c r="D38" t="n">
         <v>0.05132829098462732</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001081201987217719</v>
+        <v>0.0001081201987217718</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9131230346605573</v>
+        <v>0.9129143869724486</v>
       </c>
     </row>
     <row r="39">
@@ -5549,16 +5549,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003506310555601021</v>
+        <v>0.003503263787539643</v>
       </c>
       <c r="D39" t="n">
-        <v>0.05612625992168263</v>
+        <v>0.05612625992168258</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001730612195863432</v>
+        <v>0.0001730612195863444</v>
       </c>
       <c r="F39" t="n">
-        <v>0.967019147980731</v>
+        <v>0.9669636525302361</v>
       </c>
     </row>
     <row r="40">
@@ -5569,16 +5569,16 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.006856465632848347</v>
+        <v>0.006849751010107517</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07256592206157542</v>
+        <v>0.07256592206157575</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002263054854138223</v>
+        <v>0.0002263054854138285</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9849774424946618</v>
+        <v>0.9849484191805887</v>
       </c>
     </row>
     <row r="41">
@@ -5589,16 +5589,16 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0120431640066688</v>
+        <v>0.01203370136980239</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1338746188638102</v>
+        <v>0.1338746188638105</v>
       </c>
       <c r="E41" t="n">
-        <v>0.000257813658869609</v>
+        <v>0.0002578136588696003</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9936249854161406</v>
+        <v>0.9936150195972746</v>
       </c>
     </row>
     <row r="42">
@@ -5609,16 +5609,16 @@
         <v>160</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01578054203905483</v>
+        <v>0.01576984056296659</v>
       </c>
       <c r="D42" t="n">
-        <v>0.08539790635557543</v>
+        <v>0.08539790635557565</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0003690923810729367</v>
+        <v>0.0003690923810729451</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9923995219363606</v>
+        <v>0.9923892815419142</v>
       </c>
     </row>
     <row r="43">
@@ -5629,16 +5629,16 @@
         <v>320</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01594905944815261</v>
+        <v>0.01594072467855117</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3178511338104111</v>
+        <v>0.3178511338104109</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0004952967360718256</v>
+        <v>0.0004952967360718239</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9866781564869426</v>
+        <v>0.9866644077486083</v>
       </c>
     </row>
     <row r="44">
@@ -5649,16 +5649,16 @@
         <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001474435852459965</v>
+        <v>0.001473949241256844</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03211326862584467</v>
+        <v>0.03211326862584468</v>
       </c>
       <c r="E44" t="n">
         <v>0.0001400400911964733</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9172547672182512</v>
+        <v>0.9172046472851004</v>
       </c>
     </row>
     <row r="45">
@@ -5669,16 +5669,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>0.002887897605879234</v>
+        <v>0.002886175831617385</v>
       </c>
       <c r="D45" t="n">
-        <v>0.023904757622351</v>
+        <v>0.02390475762235103</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0002211063298614175</v>
+        <v>0.0002211063298614183</v>
       </c>
       <c r="F45" t="n">
-        <v>0.94988669077291</v>
+        <v>0.9498298824649086</v>
       </c>
     </row>
     <row r="46">
@@ -5689,16 +5689,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00617254182540551</v>
+        <v>0.006169495057344132</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.02598517829855385</v>
+        <v>-0.0259851782985539</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005471531215065217</v>
+        <v>0.0005471531215065212</v>
       </c>
       <c r="F46" t="n">
-        <v>0.95497705819388</v>
+        <v>0.9549345830867314</v>
       </c>
     </row>
     <row r="47">
@@ -5709,16 +5709,16 @@
         <v>40</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01291916048895058</v>
+        <v>0.01291244586620975</v>
       </c>
       <c r="D47" t="n">
         <v>0.03486138239678593</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0002018806486765827</v>
+        <v>0.0002018806486765842</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9982936145879031</v>
+        <v>0.9982918424779891</v>
       </c>
     </row>
     <row r="48">
@@ -5729,16 +5729,16 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02522975519413041</v>
+        <v>0.025220292557264</v>
       </c>
       <c r="D48" t="n">
         <v>0.1187802651414562</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001092006659187045</v>
+        <v>0.001092006659187053</v>
       </c>
       <c r="F48" t="n">
-        <v>0.988884694441608</v>
+        <v>0.9888764447644455</v>
       </c>
     </row>
     <row r="49">
@@ -5749,16 +5749,16 @@
         <v>160</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03180259585119757</v>
+        <v>0.03179189437510934</v>
       </c>
       <c r="D49" t="n">
         <v>0.2671041590146486</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001152745014829158</v>
+        <v>0.001152745014829157</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9921786362014935</v>
+        <v>0.9921734110313908</v>
       </c>
     </row>
     <row r="50">
@@ -5769,16 +5769,16 @@
         <v>320</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02971213513449341</v>
+        <v>0.02970380036489198</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1467384062244845</v>
+        <v>-0.146738406224485</v>
       </c>
       <c r="E50" t="n">
-        <v>0.004023188403594524</v>
+        <v>0.004023188403594521</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8862555938229987</v>
+        <v>0.886199017617592</v>
       </c>
     </row>
     <row r="51">
@@ -5789,16 +5789,16 @@
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.06745741520969262</v>
+        <v>0.06745692859848951</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8686380340892015</v>
+        <v>-0.868638034089201</v>
       </c>
       <c r="E51" t="n">
         <v>0.02532756985017048</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7027846798826166</v>
+        <v>0.7027816663304269</v>
       </c>
     </row>
     <row r="52">
@@ -5809,16 +5809,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003656237121307809</v>
+        <v>0.003654515347045961</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.01038823595157529</v>
+        <v>-0.01038823595157533</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0006600657748147589</v>
+        <v>0.0006600657748147601</v>
       </c>
       <c r="F52" t="n">
-        <v>0.910933637492361</v>
+        <v>0.9108571760104146</v>
       </c>
     </row>
     <row r="53">
@@ -5829,16 +5829,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>0.009060716042042997</v>
+        <v>0.009057669273981619</v>
       </c>
       <c r="D53" t="n">
         <v>-0.03983677626289989</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0005786260159466892</v>
+        <v>0.0005786260159466852</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9839489506233197</v>
+        <v>0.9839383239513497</v>
       </c>
     </row>
     <row r="54">
@@ -5849,16 +5849,16 @@
         <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0165925872445787</v>
+        <v>0.01658587262183787</v>
       </c>
       <c r="D54" t="n">
-        <v>0.04716230300838475</v>
+        <v>0.04716230300838481</v>
       </c>
       <c r="E54" t="n">
-        <v>0.002731475217005766</v>
+        <v>0.002731475217005774</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9485869407889898</v>
+        <v>0.9485474465551293</v>
       </c>
     </row>
     <row r="55">
@@ -5869,16 +5869,16 @@
         <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03982092787307945</v>
+        <v>0.03981146523621304</v>
       </c>
       <c r="D55" t="n">
-        <v>0.09123396912956527</v>
+        <v>0.09123396912956538</v>
       </c>
       <c r="E55" t="n">
-        <v>0.002893405540095763</v>
+        <v>0.002893405540095778</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9895512543854138</v>
+        <v>0.9895463386793066</v>
       </c>
     </row>
     <row r="56">
@@ -5889,16 +5889,16 @@
         <v>160</v>
       </c>
       <c r="C56" t="n">
-        <v>0.05164586408042905</v>
+        <v>0.05163516260434081</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2242748339227816</v>
+        <v>0.2242748339227814</v>
       </c>
       <c r="E56" t="n">
-        <v>0.006465582645996871</v>
+        <v>0.006465582645996858</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9696072438215457</v>
+        <v>0.9695950276928428</v>
       </c>
     </row>
     <row r="57">
@@ -5909,16 +5909,16 @@
         <v>320</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07447879482202589</v>
+        <v>0.07447046005242447</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01681928252113551</v>
+        <v>0.01681928252113529</v>
       </c>
       <c r="E57" t="n">
-        <v>0.005423048110431499</v>
+        <v>0.005423048110431572</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9895076974252245</v>
+        <v>0.9895053733358578</v>
       </c>
     </row>
   </sheetData>
